--- a/src/HTX586CONTRACT.Web/wwwroot/templates/Template_Import_Vehicle_HTX586.xlsx
+++ b/src/HTX586CONTRACT.Web/wwwroot/templates/Template_Import_Vehicle_HTX586.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="1" r:id="Rbfc3bf4d40014313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_VEHICLE" sheetId="2" r:id="R8cc547443f9649cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VI_DU" sheetId="3" r:id="Rf407179365304647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="1" r:id="Ra8d864bed6a14110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_VEHICLE" sheetId="2" r:id="Rf6c93ac23b484d17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VI_DU" sheetId="3" r:id="R04e6cf2243e14ece"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -262,9 +262,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -467,7 +467,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="2" t="str">
-        <x:v>VehicleOwnerUserName nếu có phải là tên đăng nhập của tài khoản Role Chủ xe đang hoạt động và đủ hồ sơ pháp lý.</x:v>
+        <x:v>VehicleOwnerUserName nếu có phải là tên đăng nhập của tài khoản Role Chủ xe đang hoạt động và đã được duyệt.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
@@ -491,7 +491,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B17" s="2" t="str">
-        <x:v>Khi đã chọn Chủ xe, họ tên, điện thoại, CCCD, địa chỉ và chân ký được lấy tự động từ tài khoản Chủ xe.</x:v>
+        <x:v>Khi đã chọn Chủ xe, thông tin Chủ xe và chân ký hợp đồng được lấy trực tiếp từ tài khoản Chủ xe; không quản lý chân ký riêng trên xe.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
@@ -500,6 +500,14 @@
       </x:c>
       <x:c r="B18" s="18" t="str">
         <x:v>PlateNumber phải duy nhất trong hệ thống. SeatCount là số nguyên từ 1 đến 100.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>PermitNumber (Số phù hiệu) là bắt buộc và được dùng để sinh số hợp đồng chính thức khi hoàn tất.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -528,6 +536,7 @@
     <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -567,6 +576,9 @@
       <x:c r="L1" s="24" t="str">
         <x:v>IsActive</x:v>
       </x:c>
+      <x:c r="M1" t="str">
+        <x:v>PermitNumber</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="36"/>
@@ -581,6 +593,7 @@
       <x:c r="J2" s="2"/>
       <x:c r="K2" s="2"/>
       <x:c r="L2" s="2"/>
+      <x:c r="M2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="36"/>
@@ -595,6 +608,7 @@
       <x:c r="J3" s="2"/>
       <x:c r="K3" s="2"/>
       <x:c r="L3" s="2"/>
+      <x:c r="M3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="36"/>
@@ -609,6 +623,7 @@
       <x:c r="J4" s="2"/>
       <x:c r="K4" s="2"/>
       <x:c r="L4" s="2"/>
+      <x:c r="M4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="36"/>
@@ -623,6 +638,7 @@
       <x:c r="J5" s="2"/>
       <x:c r="K5" s="2"/>
       <x:c r="L5" s="2"/>
+      <x:c r="M5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="36"/>
@@ -637,6 +653,7 @@
       <x:c r="J6" s="2"/>
       <x:c r="K6" s="2"/>
       <x:c r="L6" s="2"/>
+      <x:c r="M6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="36"/>
@@ -651,6 +668,7 @@
       <x:c r="J7" s="2"/>
       <x:c r="K7" s="2"/>
       <x:c r="L7" s="2"/>
+      <x:c r="M7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="36"/>
@@ -665,6 +683,7 @@
       <x:c r="J8" s="2"/>
       <x:c r="K8" s="2"/>
       <x:c r="L8" s="2"/>
+      <x:c r="M8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="36"/>
@@ -679,6 +698,7 @@
       <x:c r="J9" s="2"/>
       <x:c r="K9" s="2"/>
       <x:c r="L9" s="2"/>
+      <x:c r="M9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="36"/>
@@ -693,6 +713,7 @@
       <x:c r="J10" s="2"/>
       <x:c r="K10" s="2"/>
       <x:c r="L10" s="2"/>
+      <x:c r="M10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="36"/>
@@ -707,6 +728,7 @@
       <x:c r="J11" s="2"/>
       <x:c r="K11" s="2"/>
       <x:c r="L11" s="2"/>
+      <x:c r="M11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="36"/>
@@ -721,6 +743,7 @@
       <x:c r="J12" s="2"/>
       <x:c r="K12" s="2"/>
       <x:c r="L12" s="2"/>
+      <x:c r="M12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="36"/>
@@ -735,6 +758,7 @@
       <x:c r="J13" s="2"/>
       <x:c r="K13" s="2"/>
       <x:c r="L13" s="2"/>
+      <x:c r="M13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="36"/>
@@ -749,6 +773,7 @@
       <x:c r="J14" s="2"/>
       <x:c r="K14" s="2"/>
       <x:c r="L14" s="2"/>
+      <x:c r="M14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="36"/>
@@ -763,6 +788,7 @@
       <x:c r="J15" s="2"/>
       <x:c r="K15" s="2"/>
       <x:c r="L15" s="2"/>
+      <x:c r="M15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="36"/>
@@ -777,6 +803,7 @@
       <x:c r="J16" s="2"/>
       <x:c r="K16" s="2"/>
       <x:c r="L16" s="2"/>
+      <x:c r="M16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="36"/>
@@ -791,6 +818,7 @@
       <x:c r="J17" s="2"/>
       <x:c r="K17" s="2"/>
       <x:c r="L17" s="2"/>
+      <x:c r="M17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="36"/>
@@ -805,6 +833,7 @@
       <x:c r="J18" s="2"/>
       <x:c r="K18" s="2"/>
       <x:c r="L18" s="2"/>
+      <x:c r="M18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="36"/>
@@ -819,6 +848,7 @@
       <x:c r="J19" s="2"/>
       <x:c r="K19" s="2"/>
       <x:c r="L19" s="2"/>
+      <x:c r="M19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="36"/>
@@ -833,6 +863,7 @@
       <x:c r="J20" s="2"/>
       <x:c r="K20" s="2"/>
       <x:c r="L20" s="2"/>
+      <x:c r="M20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="36"/>
@@ -847,6 +878,7 @@
       <x:c r="J21" s="2"/>
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
+      <x:c r="M21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="36"/>
@@ -861,6 +893,7 @@
       <x:c r="J22" s="2"/>
       <x:c r="K22" s="2"/>
       <x:c r="L22" s="2"/>
+      <x:c r="M22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="36"/>
@@ -875,6 +908,7 @@
       <x:c r="J23" s="2"/>
       <x:c r="K23" s="2"/>
       <x:c r="L23" s="2"/>
+      <x:c r="M23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="36"/>
@@ -889,6 +923,7 @@
       <x:c r="J24" s="2"/>
       <x:c r="K24" s="2"/>
       <x:c r="L24" s="2"/>
+      <x:c r="M24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="36"/>
@@ -903,6 +938,7 @@
       <x:c r="J25" s="2"/>
       <x:c r="K25" s="2"/>
       <x:c r="L25" s="2"/>
+      <x:c r="M25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="36"/>
@@ -917,6 +953,7 @@
       <x:c r="J26" s="2"/>
       <x:c r="K26" s="2"/>
       <x:c r="L26" s="2"/>
+      <x:c r="M26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="36"/>
@@ -931,6 +968,7 @@
       <x:c r="J27" s="2"/>
       <x:c r="K27" s="2"/>
       <x:c r="L27" s="2"/>
+      <x:c r="M27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="36"/>
@@ -945,6 +983,7 @@
       <x:c r="J28" s="2"/>
       <x:c r="K28" s="2"/>
       <x:c r="L28" s="2"/>
+      <x:c r="M28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="36"/>
@@ -959,6 +998,7 @@
       <x:c r="J29" s="2"/>
       <x:c r="K29" s="2"/>
       <x:c r="L29" s="2"/>
+      <x:c r="M29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="36"/>
@@ -973,6 +1013,7 @@
       <x:c r="J30" s="2"/>
       <x:c r="K30" s="2"/>
       <x:c r="L30" s="2"/>
+      <x:c r="M30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="36"/>
@@ -987,6 +1028,7 @@
       <x:c r="J31" s="2"/>
       <x:c r="K31" s="2"/>
       <x:c r="L31" s="2"/>
+      <x:c r="M31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="36"/>
@@ -1001,6 +1043,7 @@
       <x:c r="J32" s="2"/>
       <x:c r="K32" s="2"/>
       <x:c r="L32" s="2"/>
+      <x:c r="M32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="36"/>
@@ -1015,6 +1058,7 @@
       <x:c r="J33" s="2"/>
       <x:c r="K33" s="2"/>
       <x:c r="L33" s="2"/>
+      <x:c r="M33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="36"/>
@@ -1029,6 +1073,7 @@
       <x:c r="J34" s="2"/>
       <x:c r="K34" s="2"/>
       <x:c r="L34" s="2"/>
+      <x:c r="M34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="36"/>
@@ -1043,6 +1088,7 @@
       <x:c r="J35" s="2"/>
       <x:c r="K35" s="2"/>
       <x:c r="L35" s="2"/>
+      <x:c r="M35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="36"/>
@@ -1057,6 +1103,7 @@
       <x:c r="J36" s="2"/>
       <x:c r="K36" s="2"/>
       <x:c r="L36" s="2"/>
+      <x:c r="M36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="36"/>
@@ -1071,6 +1118,7 @@
       <x:c r="J37" s="2"/>
       <x:c r="K37" s="2"/>
       <x:c r="L37" s="2"/>
+      <x:c r="M37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="36"/>
@@ -1085,6 +1133,7 @@
       <x:c r="J38" s="2"/>
       <x:c r="K38" s="2"/>
       <x:c r="L38" s="2"/>
+      <x:c r="M38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="36"/>
@@ -1099,6 +1148,7 @@
       <x:c r="J39" s="2"/>
       <x:c r="K39" s="2"/>
       <x:c r="L39" s="2"/>
+      <x:c r="M39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="36"/>
@@ -1113,6 +1163,7 @@
       <x:c r="J40" s="2"/>
       <x:c r="K40" s="2"/>
       <x:c r="L40" s="2"/>
+      <x:c r="M40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="36"/>
@@ -1127,6 +1178,7 @@
       <x:c r="J41" s="2"/>
       <x:c r="K41" s="2"/>
       <x:c r="L41" s="2"/>
+      <x:c r="M41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="36"/>
@@ -1141,6 +1193,7 @@
       <x:c r="J42" s="2"/>
       <x:c r="K42" s="2"/>
       <x:c r="L42" s="2"/>
+      <x:c r="M42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="36"/>
@@ -1155,6 +1208,7 @@
       <x:c r="J43" s="2"/>
       <x:c r="K43" s="2"/>
       <x:c r="L43" s="2"/>
+      <x:c r="M43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="36"/>
@@ -1169,6 +1223,7 @@
       <x:c r="J44" s="2"/>
       <x:c r="K44" s="2"/>
       <x:c r="L44" s="2"/>
+      <x:c r="M44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="36"/>
@@ -1183,6 +1238,7 @@
       <x:c r="J45" s="2"/>
       <x:c r="K45" s="2"/>
       <x:c r="L45" s="2"/>
+      <x:c r="M45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="36"/>
@@ -1197,6 +1253,7 @@
       <x:c r="J46" s="2"/>
       <x:c r="K46" s="2"/>
       <x:c r="L46" s="2"/>
+      <x:c r="M46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="36"/>
@@ -1211,6 +1268,7 @@
       <x:c r="J47" s="2"/>
       <x:c r="K47" s="2"/>
       <x:c r="L47" s="2"/>
+      <x:c r="M47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="36"/>
@@ -1225,6 +1283,7 @@
       <x:c r="J48" s="2"/>
       <x:c r="K48" s="2"/>
       <x:c r="L48" s="2"/>
+      <x:c r="M48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="36"/>
@@ -1239,6 +1298,7 @@
       <x:c r="J49" s="2"/>
       <x:c r="K49" s="2"/>
       <x:c r="L49" s="2"/>
+      <x:c r="M49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="36"/>
@@ -1253,6 +1313,7 @@
       <x:c r="J50" s="2"/>
       <x:c r="K50" s="2"/>
       <x:c r="L50" s="2"/>
+      <x:c r="M50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="36"/>
@@ -1267,6 +1328,7 @@
       <x:c r="J51" s="2"/>
       <x:c r="K51" s="2"/>
       <x:c r="L51" s="2"/>
+      <x:c r="M51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="36"/>
@@ -1281,6 +1343,7 @@
       <x:c r="J52" s="2"/>
       <x:c r="K52" s="2"/>
       <x:c r="L52" s="2"/>
+      <x:c r="M52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="36"/>
@@ -1295,6 +1358,7 @@
       <x:c r="J53" s="2"/>
       <x:c r="K53" s="2"/>
       <x:c r="L53" s="2"/>
+      <x:c r="M53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="36"/>
@@ -1309,6 +1373,7 @@
       <x:c r="J54" s="2"/>
       <x:c r="K54" s="2"/>
       <x:c r="L54" s="2"/>
+      <x:c r="M54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="36"/>
@@ -1323,6 +1388,7 @@
       <x:c r="J55" s="2"/>
       <x:c r="K55" s="2"/>
       <x:c r="L55" s="2"/>
+      <x:c r="M55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="36"/>
@@ -1337,6 +1403,7 @@
       <x:c r="J56" s="2"/>
       <x:c r="K56" s="2"/>
       <x:c r="L56" s="2"/>
+      <x:c r="M56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="36"/>
@@ -1351,6 +1418,7 @@
       <x:c r="J57" s="2"/>
       <x:c r="K57" s="2"/>
       <x:c r="L57" s="2"/>
+      <x:c r="M57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="36"/>
@@ -1365,6 +1433,7 @@
       <x:c r="J58" s="2"/>
       <x:c r="K58" s="2"/>
       <x:c r="L58" s="2"/>
+      <x:c r="M58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="36"/>
@@ -1379,6 +1448,7 @@
       <x:c r="J59" s="2"/>
       <x:c r="K59" s="2"/>
       <x:c r="L59" s="2"/>
+      <x:c r="M59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="36"/>
@@ -1393,6 +1463,7 @@
       <x:c r="J60" s="2"/>
       <x:c r="K60" s="2"/>
       <x:c r="L60" s="2"/>
+      <x:c r="M60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="36"/>
@@ -1407,6 +1478,7 @@
       <x:c r="J61" s="2"/>
       <x:c r="K61" s="2"/>
       <x:c r="L61" s="2"/>
+      <x:c r="M61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="36"/>
@@ -1421,6 +1493,7 @@
       <x:c r="J62" s="2"/>
       <x:c r="K62" s="2"/>
       <x:c r="L62" s="2"/>
+      <x:c r="M62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="36"/>
@@ -1435,6 +1508,7 @@
       <x:c r="J63" s="2"/>
       <x:c r="K63" s="2"/>
       <x:c r="L63" s="2"/>
+      <x:c r="M63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="36"/>
@@ -1449,6 +1523,7 @@
       <x:c r="J64" s="2"/>
       <x:c r="K64" s="2"/>
       <x:c r="L64" s="2"/>
+      <x:c r="M64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="36"/>
@@ -1463,6 +1538,7 @@
       <x:c r="J65" s="2"/>
       <x:c r="K65" s="2"/>
       <x:c r="L65" s="2"/>
+      <x:c r="M65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="36"/>
@@ -1477,6 +1553,7 @@
       <x:c r="J66" s="2"/>
       <x:c r="K66" s="2"/>
       <x:c r="L66" s="2"/>
+      <x:c r="M66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="36"/>
@@ -1491,6 +1568,7 @@
       <x:c r="J67" s="2"/>
       <x:c r="K67" s="2"/>
       <x:c r="L67" s="2"/>
+      <x:c r="M67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="36"/>
@@ -1505,6 +1583,7 @@
       <x:c r="J68" s="2"/>
       <x:c r="K68" s="2"/>
       <x:c r="L68" s="2"/>
+      <x:c r="M68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="36"/>
@@ -1519,6 +1598,7 @@
       <x:c r="J69" s="2"/>
       <x:c r="K69" s="2"/>
       <x:c r="L69" s="2"/>
+      <x:c r="M69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="36"/>
@@ -1533,6 +1613,7 @@
       <x:c r="J70" s="2"/>
       <x:c r="K70" s="2"/>
       <x:c r="L70" s="2"/>
+      <x:c r="M70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="36"/>
@@ -1547,6 +1628,7 @@
       <x:c r="J71" s="2"/>
       <x:c r="K71" s="2"/>
       <x:c r="L71" s="2"/>
+      <x:c r="M71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="36"/>
@@ -1561,6 +1643,7 @@
       <x:c r="J72" s="2"/>
       <x:c r="K72" s="2"/>
       <x:c r="L72" s="2"/>
+      <x:c r="M72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="36"/>
@@ -1575,6 +1658,7 @@
       <x:c r="J73" s="2"/>
       <x:c r="K73" s="2"/>
       <x:c r="L73" s="2"/>
+      <x:c r="M73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="36"/>
@@ -1589,6 +1673,7 @@
       <x:c r="J74" s="2"/>
       <x:c r="K74" s="2"/>
       <x:c r="L74" s="2"/>
+      <x:c r="M74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="36"/>
@@ -1603,6 +1688,7 @@
       <x:c r="J75" s="2"/>
       <x:c r="K75" s="2"/>
       <x:c r="L75" s="2"/>
+      <x:c r="M75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="36"/>
@@ -1617,6 +1703,7 @@
       <x:c r="J76" s="2"/>
       <x:c r="K76" s="2"/>
       <x:c r="L76" s="2"/>
+      <x:c r="M76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="36"/>
@@ -1631,6 +1718,7 @@
       <x:c r="J77" s="2"/>
       <x:c r="K77" s="2"/>
       <x:c r="L77" s="2"/>
+      <x:c r="M77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="36"/>
@@ -1645,6 +1733,7 @@
       <x:c r="J78" s="2"/>
       <x:c r="K78" s="2"/>
       <x:c r="L78" s="2"/>
+      <x:c r="M78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="36"/>
@@ -1659,6 +1748,7 @@
       <x:c r="J79" s="2"/>
       <x:c r="K79" s="2"/>
       <x:c r="L79" s="2"/>
+      <x:c r="M79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="36"/>
@@ -1673,6 +1763,7 @@
       <x:c r="J80" s="2"/>
       <x:c r="K80" s="2"/>
       <x:c r="L80" s="2"/>
+      <x:c r="M80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="36"/>
@@ -1687,6 +1778,7 @@
       <x:c r="J81" s="2"/>
       <x:c r="K81" s="2"/>
       <x:c r="L81" s="2"/>
+      <x:c r="M81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="36"/>
@@ -1701,6 +1793,7 @@
       <x:c r="J82" s="2"/>
       <x:c r="K82" s="2"/>
       <x:c r="L82" s="2"/>
+      <x:c r="M82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="36"/>
@@ -1715,6 +1808,7 @@
       <x:c r="J83" s="2"/>
       <x:c r="K83" s="2"/>
       <x:c r="L83" s="2"/>
+      <x:c r="M83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="36"/>
@@ -1729,6 +1823,7 @@
       <x:c r="J84" s="2"/>
       <x:c r="K84" s="2"/>
       <x:c r="L84" s="2"/>
+      <x:c r="M84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="36"/>
@@ -1743,6 +1838,7 @@
       <x:c r="J85" s="2"/>
       <x:c r="K85" s="2"/>
       <x:c r="L85" s="2"/>
+      <x:c r="M85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="36"/>
@@ -1757,6 +1853,7 @@
       <x:c r="J86" s="2"/>
       <x:c r="K86" s="2"/>
       <x:c r="L86" s="2"/>
+      <x:c r="M86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="36"/>
@@ -1771,6 +1868,7 @@
       <x:c r="J87" s="2"/>
       <x:c r="K87" s="2"/>
       <x:c r="L87" s="2"/>
+      <x:c r="M87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="36"/>
@@ -1785,6 +1883,7 @@
       <x:c r="J88" s="2"/>
       <x:c r="K88" s="2"/>
       <x:c r="L88" s="2"/>
+      <x:c r="M88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="36"/>
@@ -1799,6 +1898,7 @@
       <x:c r="J89" s="2"/>
       <x:c r="K89" s="2"/>
       <x:c r="L89" s="2"/>
+      <x:c r="M89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="36"/>
@@ -1813,6 +1913,7 @@
       <x:c r="J90" s="2"/>
       <x:c r="K90" s="2"/>
       <x:c r="L90" s="2"/>
+      <x:c r="M90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="36"/>
@@ -1827,6 +1928,7 @@
       <x:c r="J91" s="2"/>
       <x:c r="K91" s="2"/>
       <x:c r="L91" s="2"/>
+      <x:c r="M91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="36"/>
@@ -1841,6 +1943,7 @@
       <x:c r="J92" s="2"/>
       <x:c r="K92" s="2"/>
       <x:c r="L92" s="2"/>
+      <x:c r="M92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="36"/>
@@ -1855,6 +1958,7 @@
       <x:c r="J93" s="2"/>
       <x:c r="K93" s="2"/>
       <x:c r="L93" s="2"/>
+      <x:c r="M93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="36"/>
@@ -1869,6 +1973,7 @@
       <x:c r="J94" s="2"/>
       <x:c r="K94" s="2"/>
       <x:c r="L94" s="2"/>
+      <x:c r="M94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="36"/>
@@ -1883,6 +1988,7 @@
       <x:c r="J95" s="2"/>
       <x:c r="K95" s="2"/>
       <x:c r="L95" s="2"/>
+      <x:c r="M95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="36"/>
@@ -1897,6 +2003,7 @@
       <x:c r="J96" s="2"/>
       <x:c r="K96" s="2"/>
       <x:c r="L96" s="2"/>
+      <x:c r="M96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="36"/>
@@ -1911,6 +2018,7 @@
       <x:c r="J97" s="2"/>
       <x:c r="K97" s="2"/>
       <x:c r="L97" s="2"/>
+      <x:c r="M97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="36"/>
@@ -1925,6 +2033,7 @@
       <x:c r="J98" s="2"/>
       <x:c r="K98" s="2"/>
       <x:c r="L98" s="2"/>
+      <x:c r="M98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="36"/>
@@ -1939,6 +2048,7 @@
       <x:c r="J99" s="2"/>
       <x:c r="K99" s="2"/>
       <x:c r="L99" s="2"/>
+      <x:c r="M99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="36"/>
@@ -1953,6 +2063,7 @@
       <x:c r="J100" s="2"/>
       <x:c r="K100" s="2"/>
       <x:c r="L100" s="2"/>
+      <x:c r="M100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="36"/>
@@ -1967,6 +2078,7 @@
       <x:c r="J101" s="2"/>
       <x:c r="K101" s="2"/>
       <x:c r="L101" s="2"/>
+      <x:c r="M101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="36"/>
@@ -1981,6 +2093,7 @@
       <x:c r="J102" s="2"/>
       <x:c r="K102" s="2"/>
       <x:c r="L102" s="2"/>
+      <x:c r="M102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="36"/>
@@ -1995,6 +2108,7 @@
       <x:c r="J103" s="2"/>
       <x:c r="K103" s="2"/>
       <x:c r="L103" s="2"/>
+      <x:c r="M103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="36"/>
@@ -2009,6 +2123,7 @@
       <x:c r="J104" s="2"/>
       <x:c r="K104" s="2"/>
       <x:c r="L104" s="2"/>
+      <x:c r="M104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="36"/>
@@ -2023,6 +2138,7 @@
       <x:c r="J105" s="2"/>
       <x:c r="K105" s="2"/>
       <x:c r="L105" s="2"/>
+      <x:c r="M105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="36"/>
@@ -2037,6 +2153,7 @@
       <x:c r="J106" s="2"/>
       <x:c r="K106" s="2"/>
       <x:c r="L106" s="2"/>
+      <x:c r="M106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="36"/>
@@ -2051,6 +2168,7 @@
       <x:c r="J107" s="2"/>
       <x:c r="K107" s="2"/>
       <x:c r="L107" s="2"/>
+      <x:c r="M107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="36"/>
@@ -2065,6 +2183,7 @@
       <x:c r="J108" s="2"/>
       <x:c r="K108" s="2"/>
       <x:c r="L108" s="2"/>
+      <x:c r="M108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="36"/>
@@ -2079,6 +2198,7 @@
       <x:c r="J109" s="2"/>
       <x:c r="K109" s="2"/>
       <x:c r="L109" s="2"/>
+      <x:c r="M109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="36"/>
@@ -2093,6 +2213,7 @@
       <x:c r="J110" s="2"/>
       <x:c r="K110" s="2"/>
       <x:c r="L110" s="2"/>
+      <x:c r="M110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="36"/>
@@ -2107,6 +2228,7 @@
       <x:c r="J111" s="2"/>
       <x:c r="K111" s="2"/>
       <x:c r="L111" s="2"/>
+      <x:c r="M111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="36"/>
@@ -2121,6 +2243,7 @@
       <x:c r="J112" s="2"/>
       <x:c r="K112" s="2"/>
       <x:c r="L112" s="2"/>
+      <x:c r="M112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="36"/>
@@ -2135,6 +2258,7 @@
       <x:c r="J113" s="2"/>
       <x:c r="K113" s="2"/>
       <x:c r="L113" s="2"/>
+      <x:c r="M113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="36"/>
@@ -2149,6 +2273,7 @@
       <x:c r="J114" s="2"/>
       <x:c r="K114" s="2"/>
       <x:c r="L114" s="2"/>
+      <x:c r="M114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="36"/>
@@ -2163,6 +2288,7 @@
       <x:c r="J115" s="2"/>
       <x:c r="K115" s="2"/>
       <x:c r="L115" s="2"/>
+      <x:c r="M115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="36"/>
@@ -2177,6 +2303,7 @@
       <x:c r="J116" s="2"/>
       <x:c r="K116" s="2"/>
       <x:c r="L116" s="2"/>
+      <x:c r="M116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="36"/>
@@ -2191,6 +2318,7 @@
       <x:c r="J117" s="2"/>
       <x:c r="K117" s="2"/>
       <x:c r="L117" s="2"/>
+      <x:c r="M117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="36"/>
@@ -2205,6 +2333,7 @@
       <x:c r="J118" s="2"/>
       <x:c r="K118" s="2"/>
       <x:c r="L118" s="2"/>
+      <x:c r="M118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="36"/>
@@ -2219,6 +2348,7 @@
       <x:c r="J119" s="2"/>
       <x:c r="K119" s="2"/>
       <x:c r="L119" s="2"/>
+      <x:c r="M119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="36"/>
@@ -2233,6 +2363,7 @@
       <x:c r="J120" s="2"/>
       <x:c r="K120" s="2"/>
       <x:c r="L120" s="2"/>
+      <x:c r="M120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="36"/>
@@ -2247,6 +2378,7 @@
       <x:c r="J121" s="2"/>
       <x:c r="K121" s="2"/>
       <x:c r="L121" s="2"/>
+      <x:c r="M121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="36"/>
@@ -2261,6 +2393,7 @@
       <x:c r="J122" s="2"/>
       <x:c r="K122" s="2"/>
       <x:c r="L122" s="2"/>
+      <x:c r="M122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="36"/>
@@ -2275,6 +2408,7 @@
       <x:c r="J123" s="2"/>
       <x:c r="K123" s="2"/>
       <x:c r="L123" s="2"/>
+      <x:c r="M123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="36"/>
@@ -2289,6 +2423,7 @@
       <x:c r="J124" s="2"/>
       <x:c r="K124" s="2"/>
       <x:c r="L124" s="2"/>
+      <x:c r="M124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="36"/>
@@ -2303,6 +2438,7 @@
       <x:c r="J125" s="2"/>
       <x:c r="K125" s="2"/>
       <x:c r="L125" s="2"/>
+      <x:c r="M125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="36"/>
@@ -2317,6 +2453,7 @@
       <x:c r="J126" s="2"/>
       <x:c r="K126" s="2"/>
       <x:c r="L126" s="2"/>
+      <x:c r="M126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="36"/>
@@ -2331,6 +2468,7 @@
       <x:c r="J127" s="2"/>
       <x:c r="K127" s="2"/>
       <x:c r="L127" s="2"/>
+      <x:c r="M127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="36"/>
@@ -2345,6 +2483,7 @@
       <x:c r="J128" s="2"/>
       <x:c r="K128" s="2"/>
       <x:c r="L128" s="2"/>
+      <x:c r="M128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="36"/>
@@ -2359,6 +2498,7 @@
       <x:c r="J129" s="2"/>
       <x:c r="K129" s="2"/>
       <x:c r="L129" s="2"/>
+      <x:c r="M129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="36"/>
@@ -2373,6 +2513,7 @@
       <x:c r="J130" s="2"/>
       <x:c r="K130" s="2"/>
       <x:c r="L130" s="2"/>
+      <x:c r="M130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="36"/>
@@ -2387,6 +2528,7 @@
       <x:c r="J131" s="2"/>
       <x:c r="K131" s="2"/>
       <x:c r="L131" s="2"/>
+      <x:c r="M131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="36"/>
@@ -2401,6 +2543,7 @@
       <x:c r="J132" s="2"/>
       <x:c r="K132" s="2"/>
       <x:c r="L132" s="2"/>
+      <x:c r="M132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="36"/>
@@ -2415,6 +2558,7 @@
       <x:c r="J133" s="2"/>
       <x:c r="K133" s="2"/>
       <x:c r="L133" s="2"/>
+      <x:c r="M133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="36"/>
@@ -2429,6 +2573,7 @@
       <x:c r="J134" s="2"/>
       <x:c r="K134" s="2"/>
       <x:c r="L134" s="2"/>
+      <x:c r="M134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="36"/>
@@ -2443,6 +2588,7 @@
       <x:c r="J135" s="2"/>
       <x:c r="K135" s="2"/>
       <x:c r="L135" s="2"/>
+      <x:c r="M135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="36"/>
@@ -2457,6 +2603,7 @@
       <x:c r="J136" s="2"/>
       <x:c r="K136" s="2"/>
       <x:c r="L136" s="2"/>
+      <x:c r="M136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="36"/>
@@ -2471,6 +2618,7 @@
       <x:c r="J137" s="2"/>
       <x:c r="K137" s="2"/>
       <x:c r="L137" s="2"/>
+      <x:c r="M137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="36"/>
@@ -2485,6 +2633,7 @@
       <x:c r="J138" s="2"/>
       <x:c r="K138" s="2"/>
       <x:c r="L138" s="2"/>
+      <x:c r="M138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="36"/>
@@ -2499,6 +2648,7 @@
       <x:c r="J139" s="2"/>
       <x:c r="K139" s="2"/>
       <x:c r="L139" s="2"/>
+      <x:c r="M139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="36"/>
@@ -2513,6 +2663,7 @@
       <x:c r="J140" s="2"/>
       <x:c r="K140" s="2"/>
       <x:c r="L140" s="2"/>
+      <x:c r="M140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="36"/>
@@ -2527,6 +2678,7 @@
       <x:c r="J141" s="2"/>
       <x:c r="K141" s="2"/>
       <x:c r="L141" s="2"/>
+      <x:c r="M141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="36"/>
@@ -2541,6 +2693,7 @@
       <x:c r="J142" s="2"/>
       <x:c r="K142" s="2"/>
       <x:c r="L142" s="2"/>
+      <x:c r="M142"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="36"/>
@@ -2555,6 +2708,7 @@
       <x:c r="J143" s="2"/>
       <x:c r="K143" s="2"/>
       <x:c r="L143" s="2"/>
+      <x:c r="M143"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="36"/>
@@ -2569,6 +2723,7 @@
       <x:c r="J144" s="2"/>
       <x:c r="K144" s="2"/>
       <x:c r="L144" s="2"/>
+      <x:c r="M144"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="36"/>
@@ -2583,6 +2738,7 @@
       <x:c r="J145" s="2"/>
       <x:c r="K145" s="2"/>
       <x:c r="L145" s="2"/>
+      <x:c r="M145"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="36"/>
@@ -2597,6 +2753,7 @@
       <x:c r="J146" s="2"/>
       <x:c r="K146" s="2"/>
       <x:c r="L146" s="2"/>
+      <x:c r="M146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="36"/>
@@ -2611,6 +2768,7 @@
       <x:c r="J147" s="2"/>
       <x:c r="K147" s="2"/>
       <x:c r="L147" s="2"/>
+      <x:c r="M147"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="36"/>
@@ -2625,6 +2783,7 @@
       <x:c r="J148" s="2"/>
       <x:c r="K148" s="2"/>
       <x:c r="L148" s="2"/>
+      <x:c r="M148"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="36"/>
@@ -2639,6 +2798,7 @@
       <x:c r="J149" s="2"/>
       <x:c r="K149" s="2"/>
       <x:c r="L149" s="2"/>
+      <x:c r="M149"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="36"/>
@@ -2653,6 +2813,7 @@
       <x:c r="J150" s="2"/>
       <x:c r="K150" s="2"/>
       <x:c r="L150" s="2"/>
+      <x:c r="M150"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="36"/>
@@ -2667,6 +2828,7 @@
       <x:c r="J151" s="2"/>
       <x:c r="K151" s="2"/>
       <x:c r="L151" s="2"/>
+      <x:c r="M151"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="36"/>
@@ -2681,6 +2843,7 @@
       <x:c r="J152" s="2"/>
       <x:c r="K152" s="2"/>
       <x:c r="L152" s="2"/>
+      <x:c r="M152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="36"/>
@@ -2695,6 +2858,7 @@
       <x:c r="J153" s="2"/>
       <x:c r="K153" s="2"/>
       <x:c r="L153" s="2"/>
+      <x:c r="M153"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="36"/>
@@ -2709,6 +2873,7 @@
       <x:c r="J154" s="2"/>
       <x:c r="K154" s="2"/>
       <x:c r="L154" s="2"/>
+      <x:c r="M154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="36"/>
@@ -2723,6 +2888,7 @@
       <x:c r="J155" s="2"/>
       <x:c r="K155" s="2"/>
       <x:c r="L155" s="2"/>
+      <x:c r="M155"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="36"/>
@@ -2737,6 +2903,7 @@
       <x:c r="J156" s="2"/>
       <x:c r="K156" s="2"/>
       <x:c r="L156" s="2"/>
+      <x:c r="M156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="36"/>
@@ -2751,6 +2918,7 @@
       <x:c r="J157" s="2"/>
       <x:c r="K157" s="2"/>
       <x:c r="L157" s="2"/>
+      <x:c r="M157"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="36"/>
@@ -2765,6 +2933,7 @@
       <x:c r="J158" s="2"/>
       <x:c r="K158" s="2"/>
       <x:c r="L158" s="2"/>
+      <x:c r="M158"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="36"/>
@@ -2779,6 +2948,7 @@
       <x:c r="J159" s="2"/>
       <x:c r="K159" s="2"/>
       <x:c r="L159" s="2"/>
+      <x:c r="M159"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="36"/>
@@ -2793,6 +2963,7 @@
       <x:c r="J160" s="2"/>
       <x:c r="K160" s="2"/>
       <x:c r="L160" s="2"/>
+      <x:c r="M160"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="36"/>
@@ -2807,6 +2978,7 @@
       <x:c r="J161" s="2"/>
       <x:c r="K161" s="2"/>
       <x:c r="L161" s="2"/>
+      <x:c r="M161"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="36"/>
@@ -2821,6 +2993,7 @@
       <x:c r="J162" s="2"/>
       <x:c r="K162" s="2"/>
       <x:c r="L162" s="2"/>
+      <x:c r="M162"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="36"/>
@@ -2835,6 +3008,7 @@
       <x:c r="J163" s="2"/>
       <x:c r="K163" s="2"/>
       <x:c r="L163" s="2"/>
+      <x:c r="M163"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="36"/>
@@ -2849,6 +3023,7 @@
       <x:c r="J164" s="2"/>
       <x:c r="K164" s="2"/>
       <x:c r="L164" s="2"/>
+      <x:c r="M164"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="36"/>
@@ -2863,6 +3038,7 @@
       <x:c r="J165" s="2"/>
       <x:c r="K165" s="2"/>
       <x:c r="L165" s="2"/>
+      <x:c r="M165"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="36"/>
@@ -2877,6 +3053,7 @@
       <x:c r="J166" s="2"/>
       <x:c r="K166" s="2"/>
       <x:c r="L166" s="2"/>
+      <x:c r="M166"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="36"/>
@@ -2891,6 +3068,7 @@
       <x:c r="J167" s="2"/>
       <x:c r="K167" s="2"/>
       <x:c r="L167" s="2"/>
+      <x:c r="M167"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="36"/>
@@ -2905,6 +3083,7 @@
       <x:c r="J168" s="2"/>
       <x:c r="K168" s="2"/>
       <x:c r="L168" s="2"/>
+      <x:c r="M168"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="36"/>
@@ -2919,6 +3098,7 @@
       <x:c r="J169" s="2"/>
       <x:c r="K169" s="2"/>
       <x:c r="L169" s="2"/>
+      <x:c r="M169"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="36"/>
@@ -2933,6 +3113,7 @@
       <x:c r="J170" s="2"/>
       <x:c r="K170" s="2"/>
       <x:c r="L170" s="2"/>
+      <x:c r="M170"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="36"/>
@@ -2947,6 +3128,7 @@
       <x:c r="J171" s="2"/>
       <x:c r="K171" s="2"/>
       <x:c r="L171" s="2"/>
+      <x:c r="M171"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="36"/>
@@ -2961,6 +3143,7 @@
       <x:c r="J172" s="2"/>
       <x:c r="K172" s="2"/>
       <x:c r="L172" s="2"/>
+      <x:c r="M172"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="36"/>
@@ -2975,6 +3158,7 @@
       <x:c r="J173" s="2"/>
       <x:c r="K173" s="2"/>
       <x:c r="L173" s="2"/>
+      <x:c r="M173"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="36"/>
@@ -2989,6 +3173,7 @@
       <x:c r="J174" s="2"/>
       <x:c r="K174" s="2"/>
       <x:c r="L174" s="2"/>
+      <x:c r="M174"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="36"/>
@@ -3003,6 +3188,7 @@
       <x:c r="J175" s="2"/>
       <x:c r="K175" s="2"/>
       <x:c r="L175" s="2"/>
+      <x:c r="M175"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="36"/>
@@ -3017,6 +3203,7 @@
       <x:c r="J176" s="2"/>
       <x:c r="K176" s="2"/>
       <x:c r="L176" s="2"/>
+      <x:c r="M176"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="36"/>
@@ -3031,6 +3218,7 @@
       <x:c r="J177" s="2"/>
       <x:c r="K177" s="2"/>
       <x:c r="L177" s="2"/>
+      <x:c r="M177"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="36"/>
@@ -3045,6 +3233,7 @@
       <x:c r="J178" s="2"/>
       <x:c r="K178" s="2"/>
       <x:c r="L178" s="2"/>
+      <x:c r="M178"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="36"/>
@@ -3059,6 +3248,7 @@
       <x:c r="J179" s="2"/>
       <x:c r="K179" s="2"/>
       <x:c r="L179" s="2"/>
+      <x:c r="M179"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="36"/>
@@ -3073,6 +3263,7 @@
       <x:c r="J180" s="2"/>
       <x:c r="K180" s="2"/>
       <x:c r="L180" s="2"/>
+      <x:c r="M180"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="36"/>
@@ -3087,6 +3278,7 @@
       <x:c r="J181" s="2"/>
       <x:c r="K181" s="2"/>
       <x:c r="L181" s="2"/>
+      <x:c r="M181"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="36"/>
@@ -3101,6 +3293,7 @@
       <x:c r="J182" s="2"/>
       <x:c r="K182" s="2"/>
       <x:c r="L182" s="2"/>
+      <x:c r="M182"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="36"/>
@@ -3115,6 +3308,7 @@
       <x:c r="J183" s="2"/>
       <x:c r="K183" s="2"/>
       <x:c r="L183" s="2"/>
+      <x:c r="M183"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="36"/>
@@ -3129,6 +3323,7 @@
       <x:c r="J184" s="2"/>
       <x:c r="K184" s="2"/>
       <x:c r="L184" s="2"/>
+      <x:c r="M184"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="36"/>
@@ -3143,6 +3338,7 @@
       <x:c r="J185" s="2"/>
       <x:c r="K185" s="2"/>
       <x:c r="L185" s="2"/>
+      <x:c r="M185"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="36"/>
@@ -3157,6 +3353,7 @@
       <x:c r="J186" s="2"/>
       <x:c r="K186" s="2"/>
       <x:c r="L186" s="2"/>
+      <x:c r="M186"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="36"/>
@@ -3171,6 +3368,7 @@
       <x:c r="J187" s="2"/>
       <x:c r="K187" s="2"/>
       <x:c r="L187" s="2"/>
+      <x:c r="M187"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="36"/>
@@ -3185,6 +3383,7 @@
       <x:c r="J188" s="2"/>
       <x:c r="K188" s="2"/>
       <x:c r="L188" s="2"/>
+      <x:c r="M188"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="36"/>
@@ -3199,6 +3398,7 @@
       <x:c r="J189" s="2"/>
       <x:c r="K189" s="2"/>
       <x:c r="L189" s="2"/>
+      <x:c r="M189"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="36"/>
@@ -3213,6 +3413,7 @@
       <x:c r="J190" s="2"/>
       <x:c r="K190" s="2"/>
       <x:c r="L190" s="2"/>
+      <x:c r="M190"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="36"/>
@@ -3227,6 +3428,7 @@
       <x:c r="J191" s="2"/>
       <x:c r="K191" s="2"/>
       <x:c r="L191" s="2"/>
+      <x:c r="M191"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="36"/>
@@ -3241,6 +3443,7 @@
       <x:c r="J192" s="2"/>
       <x:c r="K192" s="2"/>
       <x:c r="L192" s="2"/>
+      <x:c r="M192"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="36"/>
@@ -3255,6 +3458,7 @@
       <x:c r="J193" s="2"/>
       <x:c r="K193" s="2"/>
       <x:c r="L193" s="2"/>
+      <x:c r="M193"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="36"/>
@@ -3269,6 +3473,7 @@
       <x:c r="J194" s="2"/>
       <x:c r="K194" s="2"/>
       <x:c r="L194" s="2"/>
+      <x:c r="M194"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="36"/>
@@ -3283,6 +3488,7 @@
       <x:c r="J195" s="2"/>
       <x:c r="K195" s="2"/>
       <x:c r="L195" s="2"/>
+      <x:c r="M195"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="36"/>
@@ -3297,6 +3503,7 @@
       <x:c r="J196" s="2"/>
       <x:c r="K196" s="2"/>
       <x:c r="L196" s="2"/>
+      <x:c r="M196"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="36"/>
@@ -3311,6 +3518,7 @@
       <x:c r="J197" s="2"/>
       <x:c r="K197" s="2"/>
       <x:c r="L197" s="2"/>
+      <x:c r="M197"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="36"/>
@@ -3325,6 +3533,7 @@
       <x:c r="J198" s="2"/>
       <x:c r="K198" s="2"/>
       <x:c r="L198" s="2"/>
+      <x:c r="M198"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="36"/>
@@ -3339,6 +3548,7 @@
       <x:c r="J199" s="2"/>
       <x:c r="K199" s="2"/>
       <x:c r="L199" s="2"/>
+      <x:c r="M199"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="36"/>
@@ -3353,6 +3563,7 @@
       <x:c r="J200" s="2"/>
       <x:c r="K200" s="2"/>
       <x:c r="L200" s="2"/>
+      <x:c r="M200"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="36"/>
@@ -3367,6 +3578,7 @@
       <x:c r="J201" s="2"/>
       <x:c r="K201" s="2"/>
       <x:c r="L201" s="2"/>
+      <x:c r="M201"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="36"/>
@@ -3381,6 +3593,7 @@
       <x:c r="J202" s="2"/>
       <x:c r="K202" s="2"/>
       <x:c r="L202" s="2"/>
+      <x:c r="M202"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="36"/>
@@ -3395,6 +3608,7 @@
       <x:c r="J203" s="2"/>
       <x:c r="K203" s="2"/>
       <x:c r="L203" s="2"/>
+      <x:c r="M203"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="36"/>
@@ -3409,6 +3623,7 @@
       <x:c r="J204" s="2"/>
       <x:c r="K204" s="2"/>
       <x:c r="L204" s="2"/>
+      <x:c r="M204"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="36"/>
@@ -3423,6 +3638,7 @@
       <x:c r="J205" s="2"/>
       <x:c r="K205" s="2"/>
       <x:c r="L205" s="2"/>
+      <x:c r="M205"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="36"/>
@@ -3437,6 +3653,7 @@
       <x:c r="J206" s="2"/>
       <x:c r="K206" s="2"/>
       <x:c r="L206" s="2"/>
+      <x:c r="M206"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="36"/>
@@ -3451,6 +3668,7 @@
       <x:c r="J207" s="2"/>
       <x:c r="K207" s="2"/>
       <x:c r="L207" s="2"/>
+      <x:c r="M207"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="36"/>
@@ -3465,6 +3683,7 @@
       <x:c r="J208" s="2"/>
       <x:c r="K208" s="2"/>
       <x:c r="L208" s="2"/>
+      <x:c r="M208"/>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="36"/>
@@ -3479,6 +3698,7 @@
       <x:c r="J209" s="2"/>
       <x:c r="K209" s="2"/>
       <x:c r="L209" s="2"/>
+      <x:c r="M209"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="36"/>
@@ -3493,6 +3713,7 @@
       <x:c r="J210" s="2"/>
       <x:c r="K210" s="2"/>
       <x:c r="L210" s="2"/>
+      <x:c r="M210"/>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="36"/>
@@ -3507,6 +3728,7 @@
       <x:c r="J211" s="2"/>
       <x:c r="K211" s="2"/>
       <x:c r="L211" s="2"/>
+      <x:c r="M211"/>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="36"/>
@@ -3521,6 +3743,7 @@
       <x:c r="J212" s="2"/>
       <x:c r="K212" s="2"/>
       <x:c r="L212" s="2"/>
+      <x:c r="M212"/>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="36"/>
@@ -3535,6 +3758,7 @@
       <x:c r="J213" s="2"/>
       <x:c r="K213" s="2"/>
       <x:c r="L213" s="2"/>
+      <x:c r="M213"/>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="36"/>
@@ -3549,6 +3773,7 @@
       <x:c r="J214" s="2"/>
       <x:c r="K214" s="2"/>
       <x:c r="L214" s="2"/>
+      <x:c r="M214"/>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="36"/>
@@ -3563,6 +3788,7 @@
       <x:c r="J215" s="2"/>
       <x:c r="K215" s="2"/>
       <x:c r="L215" s="2"/>
+      <x:c r="M215"/>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="36"/>
@@ -3577,6 +3803,7 @@
       <x:c r="J216" s="2"/>
       <x:c r="K216" s="2"/>
       <x:c r="L216" s="2"/>
+      <x:c r="M216"/>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="36"/>
@@ -3591,6 +3818,7 @@
       <x:c r="J217" s="2"/>
       <x:c r="K217" s="2"/>
       <x:c r="L217" s="2"/>
+      <x:c r="M217"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="36"/>
@@ -3605,6 +3833,7 @@
       <x:c r="J218" s="2"/>
       <x:c r="K218" s="2"/>
       <x:c r="L218" s="2"/>
+      <x:c r="M218"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="36"/>
@@ -3619,6 +3848,7 @@
       <x:c r="J219" s="2"/>
       <x:c r="K219" s="2"/>
       <x:c r="L219" s="2"/>
+      <x:c r="M219"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="36"/>
@@ -3633,6 +3863,7 @@
       <x:c r="J220" s="2"/>
       <x:c r="K220" s="2"/>
       <x:c r="L220" s="2"/>
+      <x:c r="M220"/>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="36"/>
@@ -3647,6 +3878,7 @@
       <x:c r="J221" s="2"/>
       <x:c r="K221" s="2"/>
       <x:c r="L221" s="2"/>
+      <x:c r="M221"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="36"/>
@@ -3661,6 +3893,7 @@
       <x:c r="J222" s="2"/>
       <x:c r="K222" s="2"/>
       <x:c r="L222" s="2"/>
+      <x:c r="M222"/>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="36"/>
@@ -3675,6 +3908,7 @@
       <x:c r="J223" s="2"/>
       <x:c r="K223" s="2"/>
       <x:c r="L223" s="2"/>
+      <x:c r="M223"/>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="36"/>
@@ -3689,6 +3923,7 @@
       <x:c r="J224" s="2"/>
       <x:c r="K224" s="2"/>
       <x:c r="L224" s="2"/>
+      <x:c r="M224"/>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="36"/>
@@ -3703,6 +3938,7 @@
       <x:c r="J225" s="2"/>
       <x:c r="K225" s="2"/>
       <x:c r="L225" s="2"/>
+      <x:c r="M225"/>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="36"/>
@@ -3717,6 +3953,7 @@
       <x:c r="J226" s="2"/>
       <x:c r="K226" s="2"/>
       <x:c r="L226" s="2"/>
+      <x:c r="M226"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="36"/>
@@ -3731,6 +3968,7 @@
       <x:c r="J227" s="2"/>
       <x:c r="K227" s="2"/>
       <x:c r="L227" s="2"/>
+      <x:c r="M227"/>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="36"/>
@@ -3745,6 +3983,7 @@
       <x:c r="J228" s="2"/>
       <x:c r="K228" s="2"/>
       <x:c r="L228" s="2"/>
+      <x:c r="M228"/>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="36"/>
@@ -3759,6 +3998,7 @@
       <x:c r="J229" s="2"/>
       <x:c r="K229" s="2"/>
       <x:c r="L229" s="2"/>
+      <x:c r="M229"/>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="36"/>
@@ -3773,6 +4013,7 @@
       <x:c r="J230" s="2"/>
       <x:c r="K230" s="2"/>
       <x:c r="L230" s="2"/>
+      <x:c r="M230"/>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="36"/>
@@ -3787,6 +4028,7 @@
       <x:c r="J231" s="2"/>
       <x:c r="K231" s="2"/>
       <x:c r="L231" s="2"/>
+      <x:c r="M231"/>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="36"/>
@@ -3801,6 +4043,7 @@
       <x:c r="J232" s="2"/>
       <x:c r="K232" s="2"/>
       <x:c r="L232" s="2"/>
+      <x:c r="M232"/>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="36"/>
@@ -3815,6 +4058,7 @@
       <x:c r="J233" s="2"/>
       <x:c r="K233" s="2"/>
       <x:c r="L233" s="2"/>
+      <x:c r="M233"/>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="36"/>
@@ -3829,6 +4073,7 @@
       <x:c r="J234" s="2"/>
       <x:c r="K234" s="2"/>
       <x:c r="L234" s="2"/>
+      <x:c r="M234"/>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="36"/>
@@ -3843,6 +4088,7 @@
       <x:c r="J235" s="2"/>
       <x:c r="K235" s="2"/>
       <x:c r="L235" s="2"/>
+      <x:c r="M235"/>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="36"/>
@@ -3857,6 +4103,7 @@
       <x:c r="J236" s="2"/>
       <x:c r="K236" s="2"/>
       <x:c r="L236" s="2"/>
+      <x:c r="M236"/>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="36"/>
@@ -3871,6 +4118,7 @@
       <x:c r="J237" s="2"/>
       <x:c r="K237" s="2"/>
       <x:c r="L237" s="2"/>
+      <x:c r="M237"/>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="36"/>
@@ -3885,6 +4133,7 @@
       <x:c r="J238" s="2"/>
       <x:c r="K238" s="2"/>
       <x:c r="L238" s="2"/>
+      <x:c r="M238"/>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="36"/>
@@ -3899,6 +4148,7 @@
       <x:c r="J239" s="2"/>
       <x:c r="K239" s="2"/>
       <x:c r="L239" s="2"/>
+      <x:c r="M239"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="36"/>
@@ -3913,6 +4163,7 @@
       <x:c r="J240" s="2"/>
       <x:c r="K240" s="2"/>
       <x:c r="L240" s="2"/>
+      <x:c r="M240"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="36"/>
@@ -3927,6 +4178,7 @@
       <x:c r="J241" s="2"/>
       <x:c r="K241" s="2"/>
       <x:c r="L241" s="2"/>
+      <x:c r="M241"/>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="36"/>
@@ -3941,6 +4193,7 @@
       <x:c r="J242" s="2"/>
       <x:c r="K242" s="2"/>
       <x:c r="L242" s="2"/>
+      <x:c r="M242"/>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="36"/>
@@ -3955,6 +4208,7 @@
       <x:c r="J243" s="2"/>
       <x:c r="K243" s="2"/>
       <x:c r="L243" s="2"/>
+      <x:c r="M243"/>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="36"/>
@@ -3969,6 +4223,7 @@
       <x:c r="J244" s="2"/>
       <x:c r="K244" s="2"/>
       <x:c r="L244" s="2"/>
+      <x:c r="M244"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="36"/>
@@ -3983,6 +4238,7 @@
       <x:c r="J245" s="2"/>
       <x:c r="K245" s="2"/>
       <x:c r="L245" s="2"/>
+      <x:c r="M245"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="36"/>
@@ -3997,6 +4253,7 @@
       <x:c r="J246" s="2"/>
       <x:c r="K246" s="2"/>
       <x:c r="L246" s="2"/>
+      <x:c r="M246"/>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="36"/>
@@ -4011,6 +4268,7 @@
       <x:c r="J247" s="2"/>
       <x:c r="K247" s="2"/>
       <x:c r="L247" s="2"/>
+      <x:c r="M247"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="36"/>
@@ -4025,6 +4283,7 @@
       <x:c r="J248" s="2"/>
       <x:c r="K248" s="2"/>
       <x:c r="L248" s="2"/>
+      <x:c r="M248"/>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="36"/>
@@ -4039,6 +4298,7 @@
       <x:c r="J249" s="2"/>
       <x:c r="K249" s="2"/>
       <x:c r="L249" s="2"/>
+      <x:c r="M249"/>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="36"/>
@@ -4053,6 +4313,7 @@
       <x:c r="J250" s="2"/>
       <x:c r="K250" s="2"/>
       <x:c r="L250" s="2"/>
+      <x:c r="M250"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="36"/>
@@ -4067,6 +4328,7 @@
       <x:c r="J251" s="2"/>
       <x:c r="K251" s="2"/>
       <x:c r="L251" s="2"/>
+      <x:c r="M251"/>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="36"/>
@@ -4081,6 +4343,7 @@
       <x:c r="J252" s="2"/>
       <x:c r="K252" s="2"/>
       <x:c r="L252" s="2"/>
+      <x:c r="M252"/>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="36"/>
@@ -4095,6 +4358,7 @@
       <x:c r="J253" s="2"/>
       <x:c r="K253" s="2"/>
       <x:c r="L253" s="2"/>
+      <x:c r="M253"/>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="36"/>
@@ -4109,6 +4373,7 @@
       <x:c r="J254" s="2"/>
       <x:c r="K254" s="2"/>
       <x:c r="L254" s="2"/>
+      <x:c r="M254"/>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="36"/>
@@ -4123,6 +4388,7 @@
       <x:c r="J255" s="2"/>
       <x:c r="K255" s="2"/>
       <x:c r="L255" s="2"/>
+      <x:c r="M255"/>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="36"/>
@@ -4137,6 +4403,7 @@
       <x:c r="J256" s="2"/>
       <x:c r="K256" s="2"/>
       <x:c r="L256" s="2"/>
+      <x:c r="M256"/>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="36"/>
@@ -4151,6 +4418,7 @@
       <x:c r="J257" s="2"/>
       <x:c r="K257" s="2"/>
       <x:c r="L257" s="2"/>
+      <x:c r="M257"/>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="36"/>
@@ -4165,6 +4433,7 @@
       <x:c r="J258" s="2"/>
       <x:c r="K258" s="2"/>
       <x:c r="L258" s="2"/>
+      <x:c r="M258"/>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="36"/>
@@ -4179,6 +4448,7 @@
       <x:c r="J259" s="2"/>
       <x:c r="K259" s="2"/>
       <x:c r="L259" s="2"/>
+      <x:c r="M259"/>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="36"/>
@@ -4193,6 +4463,7 @@
       <x:c r="J260" s="2"/>
       <x:c r="K260" s="2"/>
       <x:c r="L260" s="2"/>
+      <x:c r="M260"/>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="36"/>
@@ -4207,6 +4478,7 @@
       <x:c r="J261" s="2"/>
       <x:c r="K261" s="2"/>
       <x:c r="L261" s="2"/>
+      <x:c r="M261"/>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="36"/>
@@ -4221,6 +4493,7 @@
       <x:c r="J262" s="2"/>
       <x:c r="K262" s="2"/>
       <x:c r="L262" s="2"/>
+      <x:c r="M262"/>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="36"/>
@@ -4235,6 +4508,7 @@
       <x:c r="J263" s="2"/>
       <x:c r="K263" s="2"/>
       <x:c r="L263" s="2"/>
+      <x:c r="M263"/>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="36"/>
@@ -4249,6 +4523,7 @@
       <x:c r="J264" s="2"/>
       <x:c r="K264" s="2"/>
       <x:c r="L264" s="2"/>
+      <x:c r="M264"/>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="36"/>
@@ -4263,6 +4538,7 @@
       <x:c r="J265" s="2"/>
       <x:c r="K265" s="2"/>
       <x:c r="L265" s="2"/>
+      <x:c r="M265"/>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="36"/>
@@ -4277,6 +4553,7 @@
       <x:c r="J266" s="2"/>
       <x:c r="K266" s="2"/>
       <x:c r="L266" s="2"/>
+      <x:c r="M266"/>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="36"/>
@@ -4291,6 +4568,7 @@
       <x:c r="J267" s="2"/>
       <x:c r="K267" s="2"/>
       <x:c r="L267" s="2"/>
+      <x:c r="M267"/>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="36"/>
@@ -4305,6 +4583,7 @@
       <x:c r="J268" s="2"/>
       <x:c r="K268" s="2"/>
       <x:c r="L268" s="2"/>
+      <x:c r="M268"/>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="36"/>
@@ -4319,6 +4598,7 @@
       <x:c r="J269" s="2"/>
       <x:c r="K269" s="2"/>
       <x:c r="L269" s="2"/>
+      <x:c r="M269"/>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="36"/>
@@ -4333,6 +4613,7 @@
       <x:c r="J270" s="2"/>
       <x:c r="K270" s="2"/>
       <x:c r="L270" s="2"/>
+      <x:c r="M270"/>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="36"/>
@@ -4347,6 +4628,7 @@
       <x:c r="J271" s="2"/>
       <x:c r="K271" s="2"/>
       <x:c r="L271" s="2"/>
+      <x:c r="M271"/>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="36"/>
@@ -4361,6 +4643,7 @@
       <x:c r="J272" s="2"/>
       <x:c r="K272" s="2"/>
       <x:c r="L272" s="2"/>
+      <x:c r="M272"/>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="36"/>
@@ -4375,6 +4658,7 @@
       <x:c r="J273" s="2"/>
       <x:c r="K273" s="2"/>
       <x:c r="L273" s="2"/>
+      <x:c r="M273"/>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="36"/>
@@ -4389,6 +4673,7 @@
       <x:c r="J274" s="2"/>
       <x:c r="K274" s="2"/>
       <x:c r="L274" s="2"/>
+      <x:c r="M274"/>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="36"/>
@@ -4403,6 +4688,7 @@
       <x:c r="J275" s="2"/>
       <x:c r="K275" s="2"/>
       <x:c r="L275" s="2"/>
+      <x:c r="M275"/>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="36"/>
@@ -4417,6 +4703,7 @@
       <x:c r="J276" s="2"/>
       <x:c r="K276" s="2"/>
       <x:c r="L276" s="2"/>
+      <x:c r="M276"/>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="36"/>
@@ -4431,6 +4718,7 @@
       <x:c r="J277" s="2"/>
       <x:c r="K277" s="2"/>
       <x:c r="L277" s="2"/>
+      <x:c r="M277"/>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="36"/>
@@ -4445,6 +4733,7 @@
       <x:c r="J278" s="2"/>
       <x:c r="K278" s="2"/>
       <x:c r="L278" s="2"/>
+      <x:c r="M278"/>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="36"/>
@@ -4459,6 +4748,7 @@
       <x:c r="J279" s="2"/>
       <x:c r="K279" s="2"/>
       <x:c r="L279" s="2"/>
+      <x:c r="M279"/>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="36"/>
@@ -4473,6 +4763,7 @@
       <x:c r="J280" s="2"/>
       <x:c r="K280" s="2"/>
       <x:c r="L280" s="2"/>
+      <x:c r="M280"/>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="36"/>
@@ -4487,6 +4778,7 @@
       <x:c r="J281" s="2"/>
       <x:c r="K281" s="2"/>
       <x:c r="L281" s="2"/>
+      <x:c r="M281"/>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="36"/>
@@ -4501,6 +4793,7 @@
       <x:c r="J282" s="2"/>
       <x:c r="K282" s="2"/>
       <x:c r="L282" s="2"/>
+      <x:c r="M282"/>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="36"/>
@@ -4515,6 +4808,7 @@
       <x:c r="J283" s="2"/>
       <x:c r="K283" s="2"/>
       <x:c r="L283" s="2"/>
+      <x:c r="M283"/>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="36"/>
@@ -4529,6 +4823,7 @@
       <x:c r="J284" s="2"/>
       <x:c r="K284" s="2"/>
       <x:c r="L284" s="2"/>
+      <x:c r="M284"/>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="36"/>
@@ -4543,6 +4838,7 @@
       <x:c r="J285" s="2"/>
       <x:c r="K285" s="2"/>
       <x:c r="L285" s="2"/>
+      <x:c r="M285"/>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="36"/>
@@ -4557,6 +4853,7 @@
       <x:c r="J286" s="2"/>
       <x:c r="K286" s="2"/>
       <x:c r="L286" s="2"/>
+      <x:c r="M286"/>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="36"/>
@@ -4571,6 +4868,7 @@
       <x:c r="J287" s="2"/>
       <x:c r="K287" s="2"/>
       <x:c r="L287" s="2"/>
+      <x:c r="M287"/>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="36"/>
@@ -4585,6 +4883,7 @@
       <x:c r="J288" s="2"/>
       <x:c r="K288" s="2"/>
       <x:c r="L288" s="2"/>
+      <x:c r="M288"/>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="36"/>
@@ -4599,6 +4898,7 @@
       <x:c r="J289" s="2"/>
       <x:c r="K289" s="2"/>
       <x:c r="L289" s="2"/>
+      <x:c r="M289"/>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="36"/>
@@ -4613,6 +4913,7 @@
       <x:c r="J290" s="2"/>
       <x:c r="K290" s="2"/>
       <x:c r="L290" s="2"/>
+      <x:c r="M290"/>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="36"/>
@@ -4627,6 +4928,7 @@
       <x:c r="J291" s="2"/>
       <x:c r="K291" s="2"/>
       <x:c r="L291" s="2"/>
+      <x:c r="M291"/>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="36"/>
@@ -4641,6 +4943,7 @@
       <x:c r="J292" s="2"/>
       <x:c r="K292" s="2"/>
       <x:c r="L292" s="2"/>
+      <x:c r="M292"/>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="36"/>
@@ -4655,6 +4958,7 @@
       <x:c r="J293" s="2"/>
       <x:c r="K293" s="2"/>
       <x:c r="L293" s="2"/>
+      <x:c r="M293"/>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="36"/>
@@ -4669,6 +4973,7 @@
       <x:c r="J294" s="2"/>
       <x:c r="K294" s="2"/>
       <x:c r="L294" s="2"/>
+      <x:c r="M294"/>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="36"/>
@@ -4683,6 +4988,7 @@
       <x:c r="J295" s="2"/>
       <x:c r="K295" s="2"/>
       <x:c r="L295" s="2"/>
+      <x:c r="M295"/>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="36"/>
@@ -4697,6 +5003,7 @@
       <x:c r="J296" s="2"/>
       <x:c r="K296" s="2"/>
       <x:c r="L296" s="2"/>
+      <x:c r="M296"/>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="36"/>
@@ -4711,6 +5018,7 @@
       <x:c r="J297" s="2"/>
       <x:c r="K297" s="2"/>
       <x:c r="L297" s="2"/>
+      <x:c r="M297"/>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="36"/>
@@ -4725,6 +5033,7 @@
       <x:c r="J298" s="2"/>
       <x:c r="K298" s="2"/>
       <x:c r="L298" s="2"/>
+      <x:c r="M298"/>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="36"/>
@@ -4739,6 +5048,7 @@
       <x:c r="J299" s="2"/>
       <x:c r="K299" s="2"/>
       <x:c r="L299" s="2"/>
+      <x:c r="M299"/>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="36"/>
@@ -4753,6 +5063,7 @@
       <x:c r="J300" s="2"/>
       <x:c r="K300" s="2"/>
       <x:c r="L300" s="2"/>
+      <x:c r="M300"/>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="36"/>
@@ -4767,6 +5078,7 @@
       <x:c r="J301" s="2"/>
       <x:c r="K301" s="2"/>
       <x:c r="L301" s="2"/>
+      <x:c r="M301"/>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="36"/>
@@ -4781,6 +5093,7 @@
       <x:c r="J302" s="2"/>
       <x:c r="K302" s="2"/>
       <x:c r="L302" s="2"/>
+      <x:c r="M302"/>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="36"/>
@@ -4795,6 +5108,7 @@
       <x:c r="J303" s="2"/>
       <x:c r="K303" s="2"/>
       <x:c r="L303" s="2"/>
+      <x:c r="M303"/>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="36"/>
@@ -4809,6 +5123,7 @@
       <x:c r="J304" s="2"/>
       <x:c r="K304" s="2"/>
       <x:c r="L304" s="2"/>
+      <x:c r="M304"/>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="36"/>
@@ -4823,6 +5138,7 @@
       <x:c r="J305" s="2"/>
       <x:c r="K305" s="2"/>
       <x:c r="L305" s="2"/>
+      <x:c r="M305"/>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="36"/>
@@ -4837,6 +5153,7 @@
       <x:c r="J306" s="2"/>
       <x:c r="K306" s="2"/>
       <x:c r="L306" s="2"/>
+      <x:c r="M306"/>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="36"/>
@@ -4851,6 +5168,7 @@
       <x:c r="J307" s="2"/>
       <x:c r="K307" s="2"/>
       <x:c r="L307" s="2"/>
+      <x:c r="M307"/>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="36"/>
@@ -4865,6 +5183,7 @@
       <x:c r="J308" s="2"/>
       <x:c r="K308" s="2"/>
       <x:c r="L308" s="2"/>
+      <x:c r="M308"/>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="36"/>
@@ -4879,6 +5198,7 @@
       <x:c r="J309" s="2"/>
       <x:c r="K309" s="2"/>
       <x:c r="L309" s="2"/>
+      <x:c r="M309"/>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="36"/>
@@ -4893,6 +5213,7 @@
       <x:c r="J310" s="2"/>
       <x:c r="K310" s="2"/>
       <x:c r="L310" s="2"/>
+      <x:c r="M310"/>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="36"/>
@@ -4907,6 +5228,7 @@
       <x:c r="J311" s="2"/>
       <x:c r="K311" s="2"/>
       <x:c r="L311" s="2"/>
+      <x:c r="M311"/>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="36"/>
@@ -4921,6 +5243,7 @@
       <x:c r="J312" s="2"/>
       <x:c r="K312" s="2"/>
       <x:c r="L312" s="2"/>
+      <x:c r="M312"/>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="36"/>
@@ -4935,6 +5258,7 @@
       <x:c r="J313" s="2"/>
       <x:c r="K313" s="2"/>
       <x:c r="L313" s="2"/>
+      <x:c r="M313"/>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="36"/>
@@ -4949,6 +5273,7 @@
       <x:c r="J314" s="2"/>
       <x:c r="K314" s="2"/>
       <x:c r="L314" s="2"/>
+      <x:c r="M314"/>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="36"/>
@@ -4963,6 +5288,7 @@
       <x:c r="J315" s="2"/>
       <x:c r="K315" s="2"/>
       <x:c r="L315" s="2"/>
+      <x:c r="M315"/>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="36"/>
@@ -4977,6 +5303,7 @@
       <x:c r="J316" s="2"/>
       <x:c r="K316" s="2"/>
       <x:c r="L316" s="2"/>
+      <x:c r="M316"/>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="36"/>
@@ -4991,6 +5318,7 @@
       <x:c r="J317" s="2"/>
       <x:c r="K317" s="2"/>
       <x:c r="L317" s="2"/>
+      <x:c r="M317"/>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="36"/>
@@ -5005,6 +5333,7 @@
       <x:c r="J318" s="2"/>
       <x:c r="K318" s="2"/>
       <x:c r="L318" s="2"/>
+      <x:c r="M318"/>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="36"/>
@@ -5019,6 +5348,7 @@
       <x:c r="J319" s="2"/>
       <x:c r="K319" s="2"/>
       <x:c r="L319" s="2"/>
+      <x:c r="M319"/>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="36"/>
@@ -5033,6 +5363,7 @@
       <x:c r="J320" s="2"/>
       <x:c r="K320" s="2"/>
       <x:c r="L320" s="2"/>
+      <x:c r="M320"/>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="36"/>
@@ -5047,6 +5378,7 @@
       <x:c r="J321" s="2"/>
       <x:c r="K321" s="2"/>
       <x:c r="L321" s="2"/>
+      <x:c r="M321"/>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="36"/>
@@ -5061,6 +5393,7 @@
       <x:c r="J322" s="2"/>
       <x:c r="K322" s="2"/>
       <x:c r="L322" s="2"/>
+      <x:c r="M322"/>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="36"/>
@@ -5075,6 +5408,7 @@
       <x:c r="J323" s="2"/>
       <x:c r="K323" s="2"/>
       <x:c r="L323" s="2"/>
+      <x:c r="M323"/>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="36"/>
@@ -5089,6 +5423,7 @@
       <x:c r="J324" s="2"/>
       <x:c r="K324" s="2"/>
       <x:c r="L324" s="2"/>
+      <x:c r="M324"/>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="36"/>
@@ -5103,6 +5438,7 @@
       <x:c r="J325" s="2"/>
       <x:c r="K325" s="2"/>
       <x:c r="L325" s="2"/>
+      <x:c r="M325"/>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="36"/>
@@ -5117,6 +5453,7 @@
       <x:c r="J326" s="2"/>
       <x:c r="K326" s="2"/>
       <x:c r="L326" s="2"/>
+      <x:c r="M326"/>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="36"/>
@@ -5131,6 +5468,7 @@
       <x:c r="J327" s="2"/>
       <x:c r="K327" s="2"/>
       <x:c r="L327" s="2"/>
+      <x:c r="M327"/>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="36"/>
@@ -5145,6 +5483,7 @@
       <x:c r="J328" s="2"/>
       <x:c r="K328" s="2"/>
       <x:c r="L328" s="2"/>
+      <x:c r="M328"/>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="36"/>
@@ -5159,6 +5498,7 @@
       <x:c r="J329" s="2"/>
       <x:c r="K329" s="2"/>
       <x:c r="L329" s="2"/>
+      <x:c r="M329"/>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="36"/>
@@ -5173,6 +5513,7 @@
       <x:c r="J330" s="2"/>
       <x:c r="K330" s="2"/>
       <x:c r="L330" s="2"/>
+      <x:c r="M330"/>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="36"/>
@@ -5187,6 +5528,7 @@
       <x:c r="J331" s="2"/>
       <x:c r="K331" s="2"/>
       <x:c r="L331" s="2"/>
+      <x:c r="M331"/>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="36"/>
@@ -5201,6 +5543,7 @@
       <x:c r="J332" s="2"/>
       <x:c r="K332" s="2"/>
       <x:c r="L332" s="2"/>
+      <x:c r="M332"/>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="36"/>
@@ -5215,6 +5558,7 @@
       <x:c r="J333" s="2"/>
       <x:c r="K333" s="2"/>
       <x:c r="L333" s="2"/>
+      <x:c r="M333"/>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="36"/>
@@ -5229,6 +5573,7 @@
       <x:c r="J334" s="2"/>
       <x:c r="K334" s="2"/>
       <x:c r="L334" s="2"/>
+      <x:c r="M334"/>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="36"/>
@@ -5243,6 +5588,7 @@
       <x:c r="J335" s="2"/>
       <x:c r="K335" s="2"/>
       <x:c r="L335" s="2"/>
+      <x:c r="M335"/>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="36"/>
@@ -5257,6 +5603,7 @@
       <x:c r="J336" s="2"/>
       <x:c r="K336" s="2"/>
       <x:c r="L336" s="2"/>
+      <x:c r="M336"/>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="36"/>
@@ -5271,6 +5618,7 @@
       <x:c r="J337" s="2"/>
       <x:c r="K337" s="2"/>
       <x:c r="L337" s="2"/>
+      <x:c r="M337"/>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="36"/>
@@ -5285,6 +5633,7 @@
       <x:c r="J338" s="2"/>
       <x:c r="K338" s="2"/>
       <x:c r="L338" s="2"/>
+      <x:c r="M338"/>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="36"/>
@@ -5299,6 +5648,7 @@
       <x:c r="J339" s="2"/>
       <x:c r="K339" s="2"/>
       <x:c r="L339" s="2"/>
+      <x:c r="M339"/>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="36"/>
@@ -5313,6 +5663,7 @@
       <x:c r="J340" s="2"/>
       <x:c r="K340" s="2"/>
       <x:c r="L340" s="2"/>
+      <x:c r="M340"/>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="36"/>
@@ -5327,6 +5678,7 @@
       <x:c r="J341" s="2"/>
       <x:c r="K341" s="2"/>
       <x:c r="L341" s="2"/>
+      <x:c r="M341"/>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="36"/>
@@ -5341,6 +5693,7 @@
       <x:c r="J342" s="2"/>
       <x:c r="K342" s="2"/>
       <x:c r="L342" s="2"/>
+      <x:c r="M342"/>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="36"/>
@@ -5355,6 +5708,7 @@
       <x:c r="J343" s="2"/>
       <x:c r="K343" s="2"/>
       <x:c r="L343" s="2"/>
+      <x:c r="M343"/>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="36"/>
@@ -5369,6 +5723,7 @@
       <x:c r="J344" s="2"/>
       <x:c r="K344" s="2"/>
       <x:c r="L344" s="2"/>
+      <x:c r="M344"/>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="36"/>
@@ -5383,6 +5738,7 @@
       <x:c r="J345" s="2"/>
       <x:c r="K345" s="2"/>
       <x:c r="L345" s="2"/>
+      <x:c r="M345"/>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="36"/>
@@ -5397,6 +5753,7 @@
       <x:c r="J346" s="2"/>
       <x:c r="K346" s="2"/>
       <x:c r="L346" s="2"/>
+      <x:c r="M346"/>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="36"/>
@@ -5411,6 +5768,7 @@
       <x:c r="J347" s="2"/>
       <x:c r="K347" s="2"/>
       <x:c r="L347" s="2"/>
+      <x:c r="M347"/>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="36"/>
@@ -5425,6 +5783,7 @@
       <x:c r="J348" s="2"/>
       <x:c r="K348" s="2"/>
       <x:c r="L348" s="2"/>
+      <x:c r="M348"/>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="36"/>
@@ -5439,6 +5798,7 @@
       <x:c r="J349" s="2"/>
       <x:c r="K349" s="2"/>
       <x:c r="L349" s="2"/>
+      <x:c r="M349"/>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="36"/>
@@ -5453,6 +5813,7 @@
       <x:c r="J350" s="2"/>
       <x:c r="K350" s="2"/>
       <x:c r="L350" s="2"/>
+      <x:c r="M350"/>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="36"/>
@@ -5467,6 +5828,7 @@
       <x:c r="J351" s="2"/>
       <x:c r="K351" s="2"/>
       <x:c r="L351" s="2"/>
+      <x:c r="M351"/>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="36"/>
@@ -5481,6 +5843,7 @@
       <x:c r="J352" s="2"/>
       <x:c r="K352" s="2"/>
       <x:c r="L352" s="2"/>
+      <x:c r="M352"/>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="36"/>
@@ -5495,6 +5858,7 @@
       <x:c r="J353" s="2"/>
       <x:c r="K353" s="2"/>
       <x:c r="L353" s="2"/>
+      <x:c r="M353"/>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="36"/>
@@ -5509,6 +5873,7 @@
       <x:c r="J354" s="2"/>
       <x:c r="K354" s="2"/>
       <x:c r="L354" s="2"/>
+      <x:c r="M354"/>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="36"/>
@@ -5523,6 +5888,7 @@
       <x:c r="J355" s="2"/>
       <x:c r="K355" s="2"/>
       <x:c r="L355" s="2"/>
+      <x:c r="M355"/>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="36"/>
@@ -5537,6 +5903,7 @@
       <x:c r="J356" s="2"/>
       <x:c r="K356" s="2"/>
       <x:c r="L356" s="2"/>
+      <x:c r="M356"/>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="36"/>
@@ -5551,6 +5918,7 @@
       <x:c r="J357" s="2"/>
       <x:c r="K357" s="2"/>
       <x:c r="L357" s="2"/>
+      <x:c r="M357"/>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="36"/>
@@ -5565,6 +5933,7 @@
       <x:c r="J358" s="2"/>
       <x:c r="K358" s="2"/>
       <x:c r="L358" s="2"/>
+      <x:c r="M358"/>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="36"/>
@@ -5579,6 +5948,7 @@
       <x:c r="J359" s="2"/>
       <x:c r="K359" s="2"/>
       <x:c r="L359" s="2"/>
+      <x:c r="M359"/>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="36"/>
@@ -5593,6 +5963,7 @@
       <x:c r="J360" s="2"/>
       <x:c r="K360" s="2"/>
       <x:c r="L360" s="2"/>
+      <x:c r="M360"/>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="36"/>
@@ -5607,6 +5978,7 @@
       <x:c r="J361" s="2"/>
       <x:c r="K361" s="2"/>
       <x:c r="L361" s="2"/>
+      <x:c r="M361"/>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="36"/>
@@ -5621,6 +5993,7 @@
       <x:c r="J362" s="2"/>
       <x:c r="K362" s="2"/>
       <x:c r="L362" s="2"/>
+      <x:c r="M362"/>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="36"/>
@@ -5635,6 +6008,7 @@
       <x:c r="J363" s="2"/>
       <x:c r="K363" s="2"/>
       <x:c r="L363" s="2"/>
+      <x:c r="M363"/>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="36"/>
@@ -5649,6 +6023,7 @@
       <x:c r="J364" s="2"/>
       <x:c r="K364" s="2"/>
       <x:c r="L364" s="2"/>
+      <x:c r="M364"/>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="36"/>
@@ -5663,6 +6038,7 @@
       <x:c r="J365" s="2"/>
       <x:c r="K365" s="2"/>
       <x:c r="L365" s="2"/>
+      <x:c r="M365"/>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="36"/>
@@ -5677,6 +6053,7 @@
       <x:c r="J366" s="2"/>
       <x:c r="K366" s="2"/>
       <x:c r="L366" s="2"/>
+      <x:c r="M366"/>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="36"/>
@@ -5691,6 +6068,7 @@
       <x:c r="J367" s="2"/>
       <x:c r="K367" s="2"/>
       <x:c r="L367" s="2"/>
+      <x:c r="M367"/>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="36"/>
@@ -5705,6 +6083,7 @@
       <x:c r="J368" s="2"/>
       <x:c r="K368" s="2"/>
       <x:c r="L368" s="2"/>
+      <x:c r="M368"/>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="36"/>
@@ -5719,6 +6098,7 @@
       <x:c r="J369" s="2"/>
       <x:c r="K369" s="2"/>
       <x:c r="L369" s="2"/>
+      <x:c r="M369"/>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="36"/>
@@ -5733,6 +6113,7 @@
       <x:c r="J370" s="2"/>
       <x:c r="K370" s="2"/>
       <x:c r="L370" s="2"/>
+      <x:c r="M370"/>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="36"/>
@@ -5747,6 +6128,7 @@
       <x:c r="J371" s="2"/>
       <x:c r="K371" s="2"/>
       <x:c r="L371" s="2"/>
+      <x:c r="M371"/>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="36"/>
@@ -5761,6 +6143,7 @@
       <x:c r="J372" s="2"/>
       <x:c r="K372" s="2"/>
       <x:c r="L372" s="2"/>
+      <x:c r="M372"/>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="36"/>
@@ -5775,6 +6158,7 @@
       <x:c r="J373" s="2"/>
       <x:c r="K373" s="2"/>
       <x:c r="L373" s="2"/>
+      <x:c r="M373"/>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="36"/>
@@ -5789,6 +6173,7 @@
       <x:c r="J374" s="2"/>
       <x:c r="K374" s="2"/>
       <x:c r="L374" s="2"/>
+      <x:c r="M374"/>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="36"/>
@@ -5803,6 +6188,7 @@
       <x:c r="J375" s="2"/>
       <x:c r="K375" s="2"/>
       <x:c r="L375" s="2"/>
+      <x:c r="M375"/>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="36"/>
@@ -5817,6 +6203,7 @@
       <x:c r="J376" s="2"/>
       <x:c r="K376" s="2"/>
       <x:c r="L376" s="2"/>
+      <x:c r="M376"/>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="36"/>
@@ -5831,6 +6218,7 @@
       <x:c r="J377" s="2"/>
       <x:c r="K377" s="2"/>
       <x:c r="L377" s="2"/>
+      <x:c r="M377"/>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="36"/>
@@ -5845,6 +6233,7 @@
       <x:c r="J378" s="2"/>
       <x:c r="K378" s="2"/>
       <x:c r="L378" s="2"/>
+      <x:c r="M378"/>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="36"/>
@@ -5859,6 +6248,7 @@
       <x:c r="J379" s="2"/>
       <x:c r="K379" s="2"/>
       <x:c r="L379" s="2"/>
+      <x:c r="M379"/>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="36"/>
@@ -5873,6 +6263,7 @@
       <x:c r="J380" s="2"/>
       <x:c r="K380" s="2"/>
       <x:c r="L380" s="2"/>
+      <x:c r="M380"/>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="36"/>
@@ -5887,6 +6278,7 @@
       <x:c r="J381" s="2"/>
       <x:c r="K381" s="2"/>
       <x:c r="L381" s="2"/>
+      <x:c r="M381"/>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="36"/>
@@ -5901,6 +6293,7 @@
       <x:c r="J382" s="2"/>
       <x:c r="K382" s="2"/>
       <x:c r="L382" s="2"/>
+      <x:c r="M382"/>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="36"/>
@@ -5915,6 +6308,7 @@
       <x:c r="J383" s="2"/>
       <x:c r="K383" s="2"/>
       <x:c r="L383" s="2"/>
+      <x:c r="M383"/>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="36"/>
@@ -5929,6 +6323,7 @@
       <x:c r="J384" s="2"/>
       <x:c r="K384" s="2"/>
       <x:c r="L384" s="2"/>
+      <x:c r="M384"/>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="36"/>
@@ -5943,6 +6338,7 @@
       <x:c r="J385" s="2"/>
       <x:c r="K385" s="2"/>
       <x:c r="L385" s="2"/>
+      <x:c r="M385"/>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="36"/>
@@ -5957,6 +6353,7 @@
       <x:c r="J386" s="2"/>
       <x:c r="K386" s="2"/>
       <x:c r="L386" s="2"/>
+      <x:c r="M386"/>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="36"/>
@@ -5971,6 +6368,7 @@
       <x:c r="J387" s="2"/>
       <x:c r="K387" s="2"/>
       <x:c r="L387" s="2"/>
+      <x:c r="M387"/>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="36"/>
@@ -5985,6 +6383,7 @@
       <x:c r="J388" s="2"/>
       <x:c r="K388" s="2"/>
       <x:c r="L388" s="2"/>
+      <x:c r="M388"/>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="36"/>
@@ -5999,6 +6398,7 @@
       <x:c r="J389" s="2"/>
       <x:c r="K389" s="2"/>
       <x:c r="L389" s="2"/>
+      <x:c r="M389"/>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="36"/>
@@ -6013,6 +6413,7 @@
       <x:c r="J390" s="2"/>
       <x:c r="K390" s="2"/>
       <x:c r="L390" s="2"/>
+      <x:c r="M390"/>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="36"/>
@@ -6027,6 +6428,7 @@
       <x:c r="J391" s="2"/>
       <x:c r="K391" s="2"/>
       <x:c r="L391" s="2"/>
+      <x:c r="M391"/>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="36"/>
@@ -6041,6 +6443,7 @@
       <x:c r="J392" s="2"/>
       <x:c r="K392" s="2"/>
       <x:c r="L392" s="2"/>
+      <x:c r="M392"/>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="36"/>
@@ -6055,6 +6458,7 @@
       <x:c r="J393" s="2"/>
       <x:c r="K393" s="2"/>
       <x:c r="L393" s="2"/>
+      <x:c r="M393"/>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="36"/>
@@ -6069,6 +6473,7 @@
       <x:c r="J394" s="2"/>
       <x:c r="K394" s="2"/>
       <x:c r="L394" s="2"/>
+      <x:c r="M394"/>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="36"/>
@@ -6083,6 +6488,7 @@
       <x:c r="J395" s="2"/>
       <x:c r="K395" s="2"/>
       <x:c r="L395" s="2"/>
+      <x:c r="M395"/>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="36"/>
@@ -6097,6 +6503,7 @@
       <x:c r="J396" s="2"/>
       <x:c r="K396" s="2"/>
       <x:c r="L396" s="2"/>
+      <x:c r="M396"/>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="36"/>
@@ -6111,6 +6518,7 @@
       <x:c r="J397" s="2"/>
       <x:c r="K397" s="2"/>
       <x:c r="L397" s="2"/>
+      <x:c r="M397"/>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="36"/>
@@ -6125,6 +6533,7 @@
       <x:c r="J398" s="2"/>
       <x:c r="K398" s="2"/>
       <x:c r="L398" s="2"/>
+      <x:c r="M398"/>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="36"/>
@@ -6139,6 +6548,7 @@
       <x:c r="J399" s="2"/>
       <x:c r="K399" s="2"/>
       <x:c r="L399" s="2"/>
+      <x:c r="M399"/>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="36"/>
@@ -6153,6 +6563,7 @@
       <x:c r="J400" s="2"/>
       <x:c r="K400" s="2"/>
       <x:c r="L400" s="2"/>
+      <x:c r="M400"/>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="36"/>
@@ -6167,6 +6578,7 @@
       <x:c r="J401" s="2"/>
       <x:c r="K401" s="2"/>
       <x:c r="L401" s="2"/>
+      <x:c r="M401"/>
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="36"/>
@@ -6181,6 +6593,7 @@
       <x:c r="J402" s="2"/>
       <x:c r="K402" s="2"/>
       <x:c r="L402" s="2"/>
+      <x:c r="M402"/>
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="36"/>
@@ -6195,6 +6608,7 @@
       <x:c r="J403" s="2"/>
       <x:c r="K403" s="2"/>
       <x:c r="L403" s="2"/>
+      <x:c r="M403"/>
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="36"/>
@@ -6209,6 +6623,7 @@
       <x:c r="J404" s="2"/>
       <x:c r="K404" s="2"/>
       <x:c r="L404" s="2"/>
+      <x:c r="M404"/>
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="36"/>
@@ -6223,6 +6638,7 @@
       <x:c r="J405" s="2"/>
       <x:c r="K405" s="2"/>
       <x:c r="L405" s="2"/>
+      <x:c r="M405"/>
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="36"/>
@@ -6237,6 +6653,7 @@
       <x:c r="J406" s="2"/>
       <x:c r="K406" s="2"/>
       <x:c r="L406" s="2"/>
+      <x:c r="M406"/>
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="36"/>
@@ -6251,6 +6668,7 @@
       <x:c r="J407" s="2"/>
       <x:c r="K407" s="2"/>
       <x:c r="L407" s="2"/>
+      <x:c r="M407"/>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="36"/>
@@ -6265,6 +6683,7 @@
       <x:c r="J408" s="2"/>
       <x:c r="K408" s="2"/>
       <x:c r="L408" s="2"/>
+      <x:c r="M408"/>
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="36"/>
@@ -6279,6 +6698,7 @@
       <x:c r="J409" s="2"/>
       <x:c r="K409" s="2"/>
       <x:c r="L409" s="2"/>
+      <x:c r="M409"/>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="36"/>
@@ -6293,6 +6713,7 @@
       <x:c r="J410" s="2"/>
       <x:c r="K410" s="2"/>
       <x:c r="L410" s="2"/>
+      <x:c r="M410"/>
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="36"/>
@@ -6307,6 +6728,7 @@
       <x:c r="J411" s="2"/>
       <x:c r="K411" s="2"/>
       <x:c r="L411" s="2"/>
+      <x:c r="M411"/>
     </x:row>
     <x:row r="412">
       <x:c r="A412" s="36"/>
@@ -6321,6 +6743,7 @@
       <x:c r="J412" s="2"/>
       <x:c r="K412" s="2"/>
       <x:c r="L412" s="2"/>
+      <x:c r="M412"/>
     </x:row>
     <x:row r="413">
       <x:c r="A413" s="36"/>
@@ -6335,6 +6758,7 @@
       <x:c r="J413" s="2"/>
       <x:c r="K413" s="2"/>
       <x:c r="L413" s="2"/>
+      <x:c r="M413"/>
     </x:row>
     <x:row r="414">
       <x:c r="A414" s="36"/>
@@ -6349,6 +6773,7 @@
       <x:c r="J414" s="2"/>
       <x:c r="K414" s="2"/>
       <x:c r="L414" s="2"/>
+      <x:c r="M414"/>
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="36"/>
@@ -6363,6 +6788,7 @@
       <x:c r="J415" s="2"/>
       <x:c r="K415" s="2"/>
       <x:c r="L415" s="2"/>
+      <x:c r="M415"/>
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="36"/>
@@ -6377,6 +6803,7 @@
       <x:c r="J416" s="2"/>
       <x:c r="K416" s="2"/>
       <x:c r="L416" s="2"/>
+      <x:c r="M416"/>
     </x:row>
     <x:row r="417">
       <x:c r="A417" s="36"/>
@@ -6391,6 +6818,7 @@
       <x:c r="J417" s="2"/>
       <x:c r="K417" s="2"/>
       <x:c r="L417" s="2"/>
+      <x:c r="M417"/>
     </x:row>
     <x:row r="418">
       <x:c r="A418" s="36"/>
@@ -6405,6 +6833,7 @@
       <x:c r="J418" s="2"/>
       <x:c r="K418" s="2"/>
       <x:c r="L418" s="2"/>
+      <x:c r="M418"/>
     </x:row>
     <x:row r="419">
       <x:c r="A419" s="36"/>
@@ -6419,6 +6848,7 @@
       <x:c r="J419" s="2"/>
       <x:c r="K419" s="2"/>
       <x:c r="L419" s="2"/>
+      <x:c r="M419"/>
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="36"/>
@@ -6433,6 +6863,7 @@
       <x:c r="J420" s="2"/>
       <x:c r="K420" s="2"/>
       <x:c r="L420" s="2"/>
+      <x:c r="M420"/>
     </x:row>
     <x:row r="421">
       <x:c r="A421" s="36"/>
@@ -6447,6 +6878,7 @@
       <x:c r="J421" s="2"/>
       <x:c r="K421" s="2"/>
       <x:c r="L421" s="2"/>
+      <x:c r="M421"/>
     </x:row>
     <x:row r="422">
       <x:c r="A422" s="36"/>
@@ -6461,6 +6893,7 @@
       <x:c r="J422" s="2"/>
       <x:c r="K422" s="2"/>
       <x:c r="L422" s="2"/>
+      <x:c r="M422"/>
     </x:row>
     <x:row r="423">
       <x:c r="A423" s="36"/>
@@ -6475,6 +6908,7 @@
       <x:c r="J423" s="2"/>
       <x:c r="K423" s="2"/>
       <x:c r="L423" s="2"/>
+      <x:c r="M423"/>
     </x:row>
     <x:row r="424">
       <x:c r="A424" s="36"/>
@@ -6489,6 +6923,7 @@
       <x:c r="J424" s="2"/>
       <x:c r="K424" s="2"/>
       <x:c r="L424" s="2"/>
+      <x:c r="M424"/>
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="36"/>
@@ -6503,6 +6938,7 @@
       <x:c r="J425" s="2"/>
       <x:c r="K425" s="2"/>
       <x:c r="L425" s="2"/>
+      <x:c r="M425"/>
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="36"/>
@@ -6517,6 +6953,7 @@
       <x:c r="J426" s="2"/>
       <x:c r="K426" s="2"/>
       <x:c r="L426" s="2"/>
+      <x:c r="M426"/>
     </x:row>
     <x:row r="427">
       <x:c r="A427" s="36"/>
@@ -6531,6 +6968,7 @@
       <x:c r="J427" s="2"/>
       <x:c r="K427" s="2"/>
       <x:c r="L427" s="2"/>
+      <x:c r="M427"/>
     </x:row>
     <x:row r="428">
       <x:c r="A428" s="36"/>
@@ -6545,6 +6983,7 @@
       <x:c r="J428" s="2"/>
       <x:c r="K428" s="2"/>
       <x:c r="L428" s="2"/>
+      <x:c r="M428"/>
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="36"/>
@@ -6559,6 +6998,7 @@
       <x:c r="J429" s="2"/>
       <x:c r="K429" s="2"/>
       <x:c r="L429" s="2"/>
+      <x:c r="M429"/>
     </x:row>
     <x:row r="430">
       <x:c r="A430" s="36"/>
@@ -6573,6 +7013,7 @@
       <x:c r="J430" s="2"/>
       <x:c r="K430" s="2"/>
       <x:c r="L430" s="2"/>
+      <x:c r="M430"/>
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="36"/>
@@ -6587,6 +7028,7 @@
       <x:c r="J431" s="2"/>
       <x:c r="K431" s="2"/>
       <x:c r="L431" s="2"/>
+      <x:c r="M431"/>
     </x:row>
     <x:row r="432">
       <x:c r="A432" s="36"/>
@@ -6601,6 +7043,7 @@
       <x:c r="J432" s="2"/>
       <x:c r="K432" s="2"/>
       <x:c r="L432" s="2"/>
+      <x:c r="M432"/>
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="36"/>
@@ -6615,6 +7058,7 @@
       <x:c r="J433" s="2"/>
       <x:c r="K433" s="2"/>
       <x:c r="L433" s="2"/>
+      <x:c r="M433"/>
     </x:row>
     <x:row r="434">
       <x:c r="A434" s="36"/>
@@ -6629,6 +7073,7 @@
       <x:c r="J434" s="2"/>
       <x:c r="K434" s="2"/>
       <x:c r="L434" s="2"/>
+      <x:c r="M434"/>
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="36"/>
@@ -6643,6 +7088,7 @@
       <x:c r="J435" s="2"/>
       <x:c r="K435" s="2"/>
       <x:c r="L435" s="2"/>
+      <x:c r="M435"/>
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="36"/>
@@ -6657,6 +7103,7 @@
       <x:c r="J436" s="2"/>
       <x:c r="K436" s="2"/>
       <x:c r="L436" s="2"/>
+      <x:c r="M436"/>
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="36"/>
@@ -6671,6 +7118,7 @@
       <x:c r="J437" s="2"/>
       <x:c r="K437" s="2"/>
       <x:c r="L437" s="2"/>
+      <x:c r="M437"/>
     </x:row>
     <x:row r="438">
       <x:c r="A438" s="36"/>
@@ -6685,6 +7133,7 @@
       <x:c r="J438" s="2"/>
       <x:c r="K438" s="2"/>
       <x:c r="L438" s="2"/>
+      <x:c r="M438"/>
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="36"/>
@@ -6699,6 +7148,7 @@
       <x:c r="J439" s="2"/>
       <x:c r="K439" s="2"/>
       <x:c r="L439" s="2"/>
+      <x:c r="M439"/>
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="36"/>
@@ -6713,6 +7163,7 @@
       <x:c r="J440" s="2"/>
       <x:c r="K440" s="2"/>
       <x:c r="L440" s="2"/>
+      <x:c r="M440"/>
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="36"/>
@@ -6727,6 +7178,7 @@
       <x:c r="J441" s="2"/>
       <x:c r="K441" s="2"/>
       <x:c r="L441" s="2"/>
+      <x:c r="M441"/>
     </x:row>
     <x:row r="442">
       <x:c r="A442" s="36"/>
@@ -6741,6 +7193,7 @@
       <x:c r="J442" s="2"/>
       <x:c r="K442" s="2"/>
       <x:c r="L442" s="2"/>
+      <x:c r="M442"/>
     </x:row>
     <x:row r="443">
       <x:c r="A443" s="36"/>
@@ -6755,6 +7208,7 @@
       <x:c r="J443" s="2"/>
       <x:c r="K443" s="2"/>
       <x:c r="L443" s="2"/>
+      <x:c r="M443"/>
     </x:row>
     <x:row r="444">
       <x:c r="A444" s="36"/>
@@ -6769,6 +7223,7 @@
       <x:c r="J444" s="2"/>
       <x:c r="K444" s="2"/>
       <x:c r="L444" s="2"/>
+      <x:c r="M444"/>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="36"/>
@@ -6783,6 +7238,7 @@
       <x:c r="J445" s="2"/>
       <x:c r="K445" s="2"/>
       <x:c r="L445" s="2"/>
+      <x:c r="M445"/>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="36"/>
@@ -6797,6 +7253,7 @@
       <x:c r="J446" s="2"/>
       <x:c r="K446" s="2"/>
       <x:c r="L446" s="2"/>
+      <x:c r="M446"/>
     </x:row>
     <x:row r="447">
       <x:c r="A447" s="36"/>
@@ -6811,6 +7268,7 @@
       <x:c r="J447" s="2"/>
       <x:c r="K447" s="2"/>
       <x:c r="L447" s="2"/>
+      <x:c r="M447"/>
     </x:row>
     <x:row r="448">
       <x:c r="A448" s="36"/>
@@ -6825,6 +7283,7 @@
       <x:c r="J448" s="2"/>
       <x:c r="K448" s="2"/>
       <x:c r="L448" s="2"/>
+      <x:c r="M448"/>
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="36"/>
@@ -6839,6 +7298,7 @@
       <x:c r="J449" s="2"/>
       <x:c r="K449" s="2"/>
       <x:c r="L449" s="2"/>
+      <x:c r="M449"/>
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="36"/>
@@ -6853,6 +7313,7 @@
       <x:c r="J450" s="2"/>
       <x:c r="K450" s="2"/>
       <x:c r="L450" s="2"/>
+      <x:c r="M450"/>
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="36"/>
@@ -6867,6 +7328,7 @@
       <x:c r="J451" s="2"/>
       <x:c r="K451" s="2"/>
       <x:c r="L451" s="2"/>
+      <x:c r="M451"/>
     </x:row>
     <x:row r="452">
       <x:c r="A452" s="36"/>
@@ -6881,6 +7343,7 @@
       <x:c r="J452" s="2"/>
       <x:c r="K452" s="2"/>
       <x:c r="L452" s="2"/>
+      <x:c r="M452"/>
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="36"/>
@@ -6895,6 +7358,7 @@
       <x:c r="J453" s="2"/>
       <x:c r="K453" s="2"/>
       <x:c r="L453" s="2"/>
+      <x:c r="M453"/>
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="36"/>
@@ -6909,6 +7373,7 @@
       <x:c r="J454" s="2"/>
       <x:c r="K454" s="2"/>
       <x:c r="L454" s="2"/>
+      <x:c r="M454"/>
     </x:row>
     <x:row r="455">
       <x:c r="A455" s="36"/>
@@ -6923,6 +7388,7 @@
       <x:c r="J455" s="2"/>
       <x:c r="K455" s="2"/>
       <x:c r="L455" s="2"/>
+      <x:c r="M455"/>
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="36"/>
@@ -6937,6 +7403,7 @@
       <x:c r="J456" s="2"/>
       <x:c r="K456" s="2"/>
       <x:c r="L456" s="2"/>
+      <x:c r="M456"/>
     </x:row>
     <x:row r="457">
       <x:c r="A457" s="36"/>
@@ -6951,6 +7418,7 @@
       <x:c r="J457" s="2"/>
       <x:c r="K457" s="2"/>
       <x:c r="L457" s="2"/>
+      <x:c r="M457"/>
     </x:row>
     <x:row r="458">
       <x:c r="A458" s="36"/>
@@ -6965,6 +7433,7 @@
       <x:c r="J458" s="2"/>
       <x:c r="K458" s="2"/>
       <x:c r="L458" s="2"/>
+      <x:c r="M458"/>
     </x:row>
     <x:row r="459">
       <x:c r="A459" s="36"/>
@@ -6979,6 +7448,7 @@
       <x:c r="J459" s="2"/>
       <x:c r="K459" s="2"/>
       <x:c r="L459" s="2"/>
+      <x:c r="M459"/>
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="36"/>
@@ -6993,6 +7463,7 @@
       <x:c r="J460" s="2"/>
       <x:c r="K460" s="2"/>
       <x:c r="L460" s="2"/>
+      <x:c r="M460"/>
     </x:row>
     <x:row r="461">
       <x:c r="A461" s="36"/>
@@ -7007,6 +7478,7 @@
       <x:c r="J461" s="2"/>
       <x:c r="K461" s="2"/>
       <x:c r="L461" s="2"/>
+      <x:c r="M461"/>
     </x:row>
     <x:row r="462">
       <x:c r="A462" s="36"/>
@@ -7021,6 +7493,7 @@
       <x:c r="J462" s="2"/>
       <x:c r="K462" s="2"/>
       <x:c r="L462" s="2"/>
+      <x:c r="M462"/>
     </x:row>
     <x:row r="463">
       <x:c r="A463" s="36"/>
@@ -7035,6 +7508,7 @@
       <x:c r="J463" s="2"/>
       <x:c r="K463" s="2"/>
       <x:c r="L463" s="2"/>
+      <x:c r="M463"/>
     </x:row>
     <x:row r="464">
       <x:c r="A464" s="36"/>
@@ -7049,6 +7523,7 @@
       <x:c r="J464" s="2"/>
       <x:c r="K464" s="2"/>
       <x:c r="L464" s="2"/>
+      <x:c r="M464"/>
     </x:row>
     <x:row r="465">
       <x:c r="A465" s="36"/>
@@ -7063,6 +7538,7 @@
       <x:c r="J465" s="2"/>
       <x:c r="K465" s="2"/>
       <x:c r="L465" s="2"/>
+      <x:c r="M465"/>
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="36"/>
@@ -7077,6 +7553,7 @@
       <x:c r="J466" s="2"/>
       <x:c r="K466" s="2"/>
       <x:c r="L466" s="2"/>
+      <x:c r="M466"/>
     </x:row>
     <x:row r="467">
       <x:c r="A467" s="36"/>
@@ -7091,6 +7568,7 @@
       <x:c r="J467" s="2"/>
       <x:c r="K467" s="2"/>
       <x:c r="L467" s="2"/>
+      <x:c r="M467"/>
     </x:row>
     <x:row r="468">
       <x:c r="A468" s="36"/>
@@ -7105,6 +7583,7 @@
       <x:c r="J468" s="2"/>
       <x:c r="K468" s="2"/>
       <x:c r="L468" s="2"/>
+      <x:c r="M468"/>
     </x:row>
     <x:row r="469">
       <x:c r="A469" s="36"/>
@@ -7119,6 +7598,7 @@
       <x:c r="J469" s="2"/>
       <x:c r="K469" s="2"/>
       <x:c r="L469" s="2"/>
+      <x:c r="M469"/>
     </x:row>
     <x:row r="470">
       <x:c r="A470" s="36"/>
@@ -7133,6 +7613,7 @@
       <x:c r="J470" s="2"/>
       <x:c r="K470" s="2"/>
       <x:c r="L470" s="2"/>
+      <x:c r="M470"/>
     </x:row>
     <x:row r="471">
       <x:c r="A471" s="36"/>
@@ -7147,6 +7628,7 @@
       <x:c r="J471" s="2"/>
       <x:c r="K471" s="2"/>
       <x:c r="L471" s="2"/>
+      <x:c r="M471"/>
     </x:row>
     <x:row r="472">
       <x:c r="A472" s="36"/>
@@ -7161,6 +7643,7 @@
       <x:c r="J472" s="2"/>
       <x:c r="K472" s="2"/>
       <x:c r="L472" s="2"/>
+      <x:c r="M472"/>
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="36"/>
@@ -7175,6 +7658,7 @@
       <x:c r="J473" s="2"/>
       <x:c r="K473" s="2"/>
       <x:c r="L473" s="2"/>
+      <x:c r="M473"/>
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="36"/>
@@ -7189,6 +7673,7 @@
       <x:c r="J474" s="2"/>
       <x:c r="K474" s="2"/>
       <x:c r="L474" s="2"/>
+      <x:c r="M474"/>
     </x:row>
     <x:row r="475">
       <x:c r="A475" s="36"/>
@@ -7203,6 +7688,7 @@
       <x:c r="J475" s="2"/>
       <x:c r="K475" s="2"/>
       <x:c r="L475" s="2"/>
+      <x:c r="M475"/>
     </x:row>
     <x:row r="476">
       <x:c r="A476" s="36"/>
@@ -7217,6 +7703,7 @@
       <x:c r="J476" s="2"/>
       <x:c r="K476" s="2"/>
       <x:c r="L476" s="2"/>
+      <x:c r="M476"/>
     </x:row>
     <x:row r="477">
       <x:c r="A477" s="36"/>
@@ -7231,6 +7718,7 @@
       <x:c r="J477" s="2"/>
       <x:c r="K477" s="2"/>
       <x:c r="L477" s="2"/>
+      <x:c r="M477"/>
     </x:row>
     <x:row r="478">
       <x:c r="A478" s="36"/>
@@ -7245,6 +7733,7 @@
       <x:c r="J478" s="2"/>
       <x:c r="K478" s="2"/>
       <x:c r="L478" s="2"/>
+      <x:c r="M478"/>
     </x:row>
     <x:row r="479">
       <x:c r="A479" s="36"/>
@@ -7259,6 +7748,7 @@
       <x:c r="J479" s="2"/>
       <x:c r="K479" s="2"/>
       <x:c r="L479" s="2"/>
+      <x:c r="M479"/>
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="36"/>
@@ -7273,6 +7763,7 @@
       <x:c r="J480" s="2"/>
       <x:c r="K480" s="2"/>
       <x:c r="L480" s="2"/>
+      <x:c r="M480"/>
     </x:row>
     <x:row r="481">
       <x:c r="A481" s="36"/>
@@ -7287,6 +7778,7 @@
       <x:c r="J481" s="2"/>
       <x:c r="K481" s="2"/>
       <x:c r="L481" s="2"/>
+      <x:c r="M481"/>
     </x:row>
     <x:row r="482">
       <x:c r="A482" s="36"/>
@@ -7301,6 +7793,7 @@
       <x:c r="J482" s="2"/>
       <x:c r="K482" s="2"/>
       <x:c r="L482" s="2"/>
+      <x:c r="M482"/>
     </x:row>
     <x:row r="483">
       <x:c r="A483" s="36"/>
@@ -7315,6 +7808,7 @@
       <x:c r="J483" s="2"/>
       <x:c r="K483" s="2"/>
       <x:c r="L483" s="2"/>
+      <x:c r="M483"/>
     </x:row>
     <x:row r="484">
       <x:c r="A484" s="36"/>
@@ -7329,6 +7823,7 @@
       <x:c r="J484" s="2"/>
       <x:c r="K484" s="2"/>
       <x:c r="L484" s="2"/>
+      <x:c r="M484"/>
     </x:row>
     <x:row r="485">
       <x:c r="A485" s="36"/>
@@ -7343,6 +7838,7 @@
       <x:c r="J485" s="2"/>
       <x:c r="K485" s="2"/>
       <x:c r="L485" s="2"/>
+      <x:c r="M485"/>
     </x:row>
     <x:row r="486">
       <x:c r="A486" s="36"/>
@@ -7357,6 +7853,7 @@
       <x:c r="J486" s="2"/>
       <x:c r="K486" s="2"/>
       <x:c r="L486" s="2"/>
+      <x:c r="M486"/>
     </x:row>
     <x:row r="487">
       <x:c r="A487" s="36"/>
@@ -7371,6 +7868,7 @@
       <x:c r="J487" s="2"/>
       <x:c r="K487" s="2"/>
       <x:c r="L487" s="2"/>
+      <x:c r="M487"/>
     </x:row>
     <x:row r="488">
       <x:c r="A488" s="36"/>
@@ -7385,6 +7883,7 @@
       <x:c r="J488" s="2"/>
       <x:c r="K488" s="2"/>
       <x:c r="L488" s="2"/>
+      <x:c r="M488"/>
     </x:row>
     <x:row r="489">
       <x:c r="A489" s="36"/>
@@ -7399,6 +7898,7 @@
       <x:c r="J489" s="2"/>
       <x:c r="K489" s="2"/>
       <x:c r="L489" s="2"/>
+      <x:c r="M489"/>
     </x:row>
     <x:row r="490">
       <x:c r="A490" s="36"/>
@@ -7413,6 +7913,7 @@
       <x:c r="J490" s="2"/>
       <x:c r="K490" s="2"/>
       <x:c r="L490" s="2"/>
+      <x:c r="M490"/>
     </x:row>
     <x:row r="491">
       <x:c r="A491" s="36"/>
@@ -7427,6 +7928,7 @@
       <x:c r="J491" s="2"/>
       <x:c r="K491" s="2"/>
       <x:c r="L491" s="2"/>
+      <x:c r="M491"/>
     </x:row>
     <x:row r="492">
       <x:c r="A492" s="36"/>
@@ -7441,6 +7943,7 @@
       <x:c r="J492" s="2"/>
       <x:c r="K492" s="2"/>
       <x:c r="L492" s="2"/>
+      <x:c r="M492"/>
     </x:row>
     <x:row r="493">
       <x:c r="A493" s="36"/>
@@ -7455,6 +7958,7 @@
       <x:c r="J493" s="2"/>
       <x:c r="K493" s="2"/>
       <x:c r="L493" s="2"/>
+      <x:c r="M493"/>
     </x:row>
     <x:row r="494">
       <x:c r="A494" s="36"/>
@@ -7469,6 +7973,7 @@
       <x:c r="J494" s="2"/>
       <x:c r="K494" s="2"/>
       <x:c r="L494" s="2"/>
+      <x:c r="M494"/>
     </x:row>
     <x:row r="495">
       <x:c r="A495" s="36"/>
@@ -7483,6 +7988,7 @@
       <x:c r="J495" s="2"/>
       <x:c r="K495" s="2"/>
       <x:c r="L495" s="2"/>
+      <x:c r="M495"/>
     </x:row>
     <x:row r="496">
       <x:c r="A496" s="36"/>
@@ -7497,6 +8003,7 @@
       <x:c r="J496" s="2"/>
       <x:c r="K496" s="2"/>
       <x:c r="L496" s="2"/>
+      <x:c r="M496"/>
     </x:row>
     <x:row r="497">
       <x:c r="A497" s="36"/>
@@ -7511,6 +8018,7 @@
       <x:c r="J497" s="2"/>
       <x:c r="K497" s="2"/>
       <x:c r="L497" s="2"/>
+      <x:c r="M497"/>
     </x:row>
     <x:row r="498">
       <x:c r="A498" s="36"/>
@@ -7525,6 +8033,7 @@
       <x:c r="J498" s="2"/>
       <x:c r="K498" s="2"/>
       <x:c r="L498" s="2"/>
+      <x:c r="M498"/>
     </x:row>
     <x:row r="499">
       <x:c r="A499" s="36"/>
@@ -7539,6 +8048,7 @@
       <x:c r="J499" s="2"/>
       <x:c r="K499" s="2"/>
       <x:c r="L499" s="2"/>
+      <x:c r="M499"/>
     </x:row>
     <x:row r="500">
       <x:c r="A500" s="36"/>
@@ -7553,6 +8063,7 @@
       <x:c r="J500" s="2"/>
       <x:c r="K500" s="2"/>
       <x:c r="L500" s="2"/>
+      <x:c r="M500"/>
     </x:row>
     <x:row r="501">
       <x:c r="A501" s="36"/>
@@ -7567,6 +8078,7 @@
       <x:c r="J501" s="2"/>
       <x:c r="K501" s="2"/>
       <x:c r="L501" s="2"/>
+      <x:c r="M501"/>
     </x:row>
     <x:row r="502">
       <x:c r="A502" s="36"/>
@@ -7581,6 +8093,7 @@
       <x:c r="J502" s="2"/>
       <x:c r="K502" s="2"/>
       <x:c r="L502" s="2"/>
+      <x:c r="M502"/>
     </x:row>
     <x:row r="503">
       <x:c r="A503" s="36"/>
@@ -7595,6 +8108,7 @@
       <x:c r="J503" s="2"/>
       <x:c r="K503" s="2"/>
       <x:c r="L503" s="2"/>
+      <x:c r="M503"/>
     </x:row>
     <x:row r="504">
       <x:c r="A504" s="36"/>
@@ -7609,6 +8123,7 @@
       <x:c r="J504" s="2"/>
       <x:c r="K504" s="2"/>
       <x:c r="L504" s="2"/>
+      <x:c r="M504"/>
     </x:row>
     <x:row r="505">
       <x:c r="A505" s="36"/>
@@ -7623,6 +8138,7 @@
       <x:c r="J505" s="2"/>
       <x:c r="K505" s="2"/>
       <x:c r="L505" s="2"/>
+      <x:c r="M505"/>
     </x:row>
     <x:row r="506">
       <x:c r="A506" s="36"/>
@@ -7637,6 +8153,7 @@
       <x:c r="J506" s="2"/>
       <x:c r="K506" s="2"/>
       <x:c r="L506" s="2"/>
+      <x:c r="M506"/>
     </x:row>
     <x:row r="507">
       <x:c r="A507" s="36"/>
@@ -7651,6 +8168,7 @@
       <x:c r="J507" s="2"/>
       <x:c r="K507" s="2"/>
       <x:c r="L507" s="2"/>
+      <x:c r="M507"/>
     </x:row>
     <x:row r="508">
       <x:c r="A508" s="36"/>
@@ -7665,6 +8183,7 @@
       <x:c r="J508" s="2"/>
       <x:c r="K508" s="2"/>
       <x:c r="L508" s="2"/>
+      <x:c r="M508"/>
     </x:row>
     <x:row r="509">
       <x:c r="A509" s="36"/>
@@ -7679,6 +8198,7 @@
       <x:c r="J509" s="2"/>
       <x:c r="K509" s="2"/>
       <x:c r="L509" s="2"/>
+      <x:c r="M509"/>
     </x:row>
     <x:row r="510">
       <x:c r="A510" s="36"/>
@@ -7693,6 +8213,7 @@
       <x:c r="J510" s="2"/>
       <x:c r="K510" s="2"/>
       <x:c r="L510" s="2"/>
+      <x:c r="M510"/>
     </x:row>
     <x:row r="511">
       <x:c r="A511" s="36"/>
@@ -7707,6 +8228,7 @@
       <x:c r="J511" s="2"/>
       <x:c r="K511" s="2"/>
       <x:c r="L511" s="2"/>
+      <x:c r="M511"/>
     </x:row>
     <x:row r="512">
       <x:c r="A512" s="36"/>
@@ -7721,6 +8243,7 @@
       <x:c r="J512" s="2"/>
       <x:c r="K512" s="2"/>
       <x:c r="L512" s="2"/>
+      <x:c r="M512"/>
     </x:row>
     <x:row r="513">
       <x:c r="A513" s="36"/>
@@ -7735,6 +8258,7 @@
       <x:c r="J513" s="2"/>
       <x:c r="K513" s="2"/>
       <x:c r="L513" s="2"/>
+      <x:c r="M513"/>
     </x:row>
     <x:row r="514">
       <x:c r="A514" s="36"/>
@@ -7749,6 +8273,7 @@
       <x:c r="J514" s="2"/>
       <x:c r="K514" s="2"/>
       <x:c r="L514" s="2"/>
+      <x:c r="M514"/>
     </x:row>
     <x:row r="515">
       <x:c r="A515" s="36"/>
@@ -7763,6 +8288,7 @@
       <x:c r="J515" s="2"/>
       <x:c r="K515" s="2"/>
       <x:c r="L515" s="2"/>
+      <x:c r="M515"/>
     </x:row>
     <x:row r="516">
       <x:c r="A516" s="36"/>
@@ -7777,6 +8303,7 @@
       <x:c r="J516" s="2"/>
       <x:c r="K516" s="2"/>
       <x:c r="L516" s="2"/>
+      <x:c r="M516"/>
     </x:row>
     <x:row r="517">
       <x:c r="A517" s="36"/>
@@ -7791,6 +8318,7 @@
       <x:c r="J517" s="2"/>
       <x:c r="K517" s="2"/>
       <x:c r="L517" s="2"/>
+      <x:c r="M517"/>
     </x:row>
     <x:row r="518">
       <x:c r="A518" s="36"/>
@@ -7805,6 +8333,7 @@
       <x:c r="J518" s="2"/>
       <x:c r="K518" s="2"/>
       <x:c r="L518" s="2"/>
+      <x:c r="M518"/>
     </x:row>
     <x:row r="519">
       <x:c r="A519" s="36"/>
@@ -7819,6 +8348,7 @@
       <x:c r="J519" s="2"/>
       <x:c r="K519" s="2"/>
       <x:c r="L519" s="2"/>
+      <x:c r="M519"/>
     </x:row>
     <x:row r="520">
       <x:c r="A520" s="36"/>
@@ -7833,6 +8363,7 @@
       <x:c r="J520" s="2"/>
       <x:c r="K520" s="2"/>
       <x:c r="L520" s="2"/>
+      <x:c r="M520"/>
     </x:row>
     <x:row r="521">
       <x:c r="A521" s="36"/>
@@ -7847,6 +8378,7 @@
       <x:c r="J521" s="2"/>
       <x:c r="K521" s="2"/>
       <x:c r="L521" s="2"/>
+      <x:c r="M521"/>
     </x:row>
     <x:row r="522">
       <x:c r="A522" s="36"/>
@@ -7861,6 +8393,7 @@
       <x:c r="J522" s="2"/>
       <x:c r="K522" s="2"/>
       <x:c r="L522" s="2"/>
+      <x:c r="M522"/>
     </x:row>
     <x:row r="523">
       <x:c r="A523" s="36"/>
@@ -7875,6 +8408,7 @@
       <x:c r="J523" s="2"/>
       <x:c r="K523" s="2"/>
       <x:c r="L523" s="2"/>
+      <x:c r="M523"/>
     </x:row>
     <x:row r="524">
       <x:c r="A524" s="36"/>
@@ -7889,6 +8423,7 @@
       <x:c r="J524" s="2"/>
       <x:c r="K524" s="2"/>
       <x:c r="L524" s="2"/>
+      <x:c r="M524"/>
     </x:row>
     <x:row r="525">
       <x:c r="A525" s="36"/>
@@ -7903,6 +8438,7 @@
       <x:c r="J525" s="2"/>
       <x:c r="K525" s="2"/>
       <x:c r="L525" s="2"/>
+      <x:c r="M525"/>
     </x:row>
     <x:row r="526">
       <x:c r="A526" s="36"/>
@@ -7917,6 +8453,7 @@
       <x:c r="J526" s="2"/>
       <x:c r="K526" s="2"/>
       <x:c r="L526" s="2"/>
+      <x:c r="M526"/>
     </x:row>
     <x:row r="527">
       <x:c r="A527" s="36"/>
@@ -7931,6 +8468,7 @@
       <x:c r="J527" s="2"/>
       <x:c r="K527" s="2"/>
       <x:c r="L527" s="2"/>
+      <x:c r="M527"/>
     </x:row>
     <x:row r="528">
       <x:c r="A528" s="36"/>
@@ -7945,6 +8483,7 @@
       <x:c r="J528" s="2"/>
       <x:c r="K528" s="2"/>
       <x:c r="L528" s="2"/>
+      <x:c r="M528"/>
     </x:row>
     <x:row r="529">
       <x:c r="A529" s="36"/>
@@ -7959,6 +8498,7 @@
       <x:c r="J529" s="2"/>
       <x:c r="K529" s="2"/>
       <x:c r="L529" s="2"/>
+      <x:c r="M529"/>
     </x:row>
     <x:row r="530">
       <x:c r="A530" s="36"/>
@@ -7973,6 +8513,7 @@
       <x:c r="J530" s="2"/>
       <x:c r="K530" s="2"/>
       <x:c r="L530" s="2"/>
+      <x:c r="M530"/>
     </x:row>
     <x:row r="531">
       <x:c r="A531" s="36"/>
@@ -7987,6 +8528,7 @@
       <x:c r="J531" s="2"/>
       <x:c r="K531" s="2"/>
       <x:c r="L531" s="2"/>
+      <x:c r="M531"/>
     </x:row>
     <x:row r="532">
       <x:c r="A532" s="36"/>
@@ -8001,6 +8543,7 @@
       <x:c r="J532" s="2"/>
       <x:c r="K532" s="2"/>
       <x:c r="L532" s="2"/>
+      <x:c r="M532"/>
     </x:row>
     <x:row r="533">
       <x:c r="A533" s="36"/>
@@ -8015,6 +8558,7 @@
       <x:c r="J533" s="2"/>
       <x:c r="K533" s="2"/>
       <x:c r="L533" s="2"/>
+      <x:c r="M533"/>
     </x:row>
     <x:row r="534">
       <x:c r="A534" s="36"/>
@@ -8029,6 +8573,7 @@
       <x:c r="J534" s="2"/>
       <x:c r="K534" s="2"/>
       <x:c r="L534" s="2"/>
+      <x:c r="M534"/>
     </x:row>
     <x:row r="535">
       <x:c r="A535" s="36"/>
@@ -8043,6 +8588,7 @@
       <x:c r="J535" s="2"/>
       <x:c r="K535" s="2"/>
       <x:c r="L535" s="2"/>
+      <x:c r="M535"/>
     </x:row>
     <x:row r="536">
       <x:c r="A536" s="36"/>
@@ -8057,6 +8603,7 @@
       <x:c r="J536" s="2"/>
       <x:c r="K536" s="2"/>
       <x:c r="L536" s="2"/>
+      <x:c r="M536"/>
     </x:row>
     <x:row r="537">
       <x:c r="A537" s="36"/>
@@ -8071,6 +8618,7 @@
       <x:c r="J537" s="2"/>
       <x:c r="K537" s="2"/>
       <x:c r="L537" s="2"/>
+      <x:c r="M537"/>
     </x:row>
     <x:row r="538">
       <x:c r="A538" s="36"/>
@@ -8085,6 +8633,7 @@
       <x:c r="J538" s="2"/>
       <x:c r="K538" s="2"/>
       <x:c r="L538" s="2"/>
+      <x:c r="M538"/>
     </x:row>
     <x:row r="539">
       <x:c r="A539" s="36"/>
@@ -8099,6 +8648,7 @@
       <x:c r="J539" s="2"/>
       <x:c r="K539" s="2"/>
       <x:c r="L539" s="2"/>
+      <x:c r="M539"/>
     </x:row>
     <x:row r="540">
       <x:c r="A540" s="36"/>
@@ -8113,6 +8663,7 @@
       <x:c r="J540" s="2"/>
       <x:c r="K540" s="2"/>
       <x:c r="L540" s="2"/>
+      <x:c r="M540"/>
     </x:row>
     <x:row r="541">
       <x:c r="A541" s="36"/>
@@ -8127,6 +8678,7 @@
       <x:c r="J541" s="2"/>
       <x:c r="K541" s="2"/>
       <x:c r="L541" s="2"/>
+      <x:c r="M541"/>
     </x:row>
     <x:row r="542">
       <x:c r="A542" s="36"/>
@@ -8141,6 +8693,7 @@
       <x:c r="J542" s="2"/>
       <x:c r="K542" s="2"/>
       <x:c r="L542" s="2"/>
+      <x:c r="M542"/>
     </x:row>
     <x:row r="543">
       <x:c r="A543" s="36"/>
@@ -8155,6 +8708,7 @@
       <x:c r="J543" s="2"/>
       <x:c r="K543" s="2"/>
       <x:c r="L543" s="2"/>
+      <x:c r="M543"/>
     </x:row>
     <x:row r="544">
       <x:c r="A544" s="36"/>
@@ -8169,6 +8723,7 @@
       <x:c r="J544" s="2"/>
       <x:c r="K544" s="2"/>
       <x:c r="L544" s="2"/>
+      <x:c r="M544"/>
     </x:row>
     <x:row r="545">
       <x:c r="A545" s="36"/>
@@ -8183,6 +8738,7 @@
       <x:c r="J545" s="2"/>
       <x:c r="K545" s="2"/>
       <x:c r="L545" s="2"/>
+      <x:c r="M545"/>
     </x:row>
     <x:row r="546">
       <x:c r="A546" s="36"/>
@@ -8197,6 +8753,7 @@
       <x:c r="J546" s="2"/>
       <x:c r="K546" s="2"/>
       <x:c r="L546" s="2"/>
+      <x:c r="M546"/>
     </x:row>
     <x:row r="547">
       <x:c r="A547" s="36"/>
@@ -8211,6 +8768,7 @@
       <x:c r="J547" s="2"/>
       <x:c r="K547" s="2"/>
       <x:c r="L547" s="2"/>
+      <x:c r="M547"/>
     </x:row>
     <x:row r="548">
       <x:c r="A548" s="36"/>
@@ -8225,6 +8783,7 @@
       <x:c r="J548" s="2"/>
       <x:c r="K548" s="2"/>
       <x:c r="L548" s="2"/>
+      <x:c r="M548"/>
     </x:row>
     <x:row r="549">
       <x:c r="A549" s="36"/>
@@ -8239,6 +8798,7 @@
       <x:c r="J549" s="2"/>
       <x:c r="K549" s="2"/>
       <x:c r="L549" s="2"/>
+      <x:c r="M549"/>
     </x:row>
     <x:row r="550">
       <x:c r="A550" s="36"/>
@@ -8253,6 +8813,7 @@
       <x:c r="J550" s="2"/>
       <x:c r="K550" s="2"/>
       <x:c r="L550" s="2"/>
+      <x:c r="M550"/>
     </x:row>
     <x:row r="551">
       <x:c r="A551" s="36"/>
@@ -8267,6 +8828,7 @@
       <x:c r="J551" s="2"/>
       <x:c r="K551" s="2"/>
       <x:c r="L551" s="2"/>
+      <x:c r="M551"/>
     </x:row>
     <x:row r="552">
       <x:c r="A552" s="36"/>
@@ -8281,6 +8843,7 @@
       <x:c r="J552" s="2"/>
       <x:c r="K552" s="2"/>
       <x:c r="L552" s="2"/>
+      <x:c r="M552"/>
     </x:row>
     <x:row r="553">
       <x:c r="A553" s="36"/>
@@ -8295,6 +8858,7 @@
       <x:c r="J553" s="2"/>
       <x:c r="K553" s="2"/>
       <x:c r="L553" s="2"/>
+      <x:c r="M553"/>
     </x:row>
     <x:row r="554">
       <x:c r="A554" s="36"/>
@@ -8309,6 +8873,7 @@
       <x:c r="J554" s="2"/>
       <x:c r="K554" s="2"/>
       <x:c r="L554" s="2"/>
+      <x:c r="M554"/>
     </x:row>
     <x:row r="555">
       <x:c r="A555" s="36"/>
@@ -8323,6 +8888,7 @@
       <x:c r="J555" s="2"/>
       <x:c r="K555" s="2"/>
       <x:c r="L555" s="2"/>
+      <x:c r="M555"/>
     </x:row>
     <x:row r="556">
       <x:c r="A556" s="36"/>
@@ -8337,6 +8903,7 @@
       <x:c r="J556" s="2"/>
       <x:c r="K556" s="2"/>
       <x:c r="L556" s="2"/>
+      <x:c r="M556"/>
     </x:row>
     <x:row r="557">
       <x:c r="A557" s="36"/>
@@ -8351,6 +8918,7 @@
       <x:c r="J557" s="2"/>
       <x:c r="K557" s="2"/>
       <x:c r="L557" s="2"/>
+      <x:c r="M557"/>
     </x:row>
     <x:row r="558">
       <x:c r="A558" s="36"/>
@@ -8365,6 +8933,7 @@
       <x:c r="J558" s="2"/>
       <x:c r="K558" s="2"/>
       <x:c r="L558" s="2"/>
+      <x:c r="M558"/>
     </x:row>
     <x:row r="559">
       <x:c r="A559" s="36"/>
@@ -8379,6 +8948,7 @@
       <x:c r="J559" s="2"/>
       <x:c r="K559" s="2"/>
       <x:c r="L559" s="2"/>
+      <x:c r="M559"/>
     </x:row>
     <x:row r="560">
       <x:c r="A560" s="36"/>
@@ -8393,6 +8963,7 @@
       <x:c r="J560" s="2"/>
       <x:c r="K560" s="2"/>
       <x:c r="L560" s="2"/>
+      <x:c r="M560"/>
     </x:row>
     <x:row r="561">
       <x:c r="A561" s="36"/>
@@ -8407,6 +8978,7 @@
       <x:c r="J561" s="2"/>
       <x:c r="K561" s="2"/>
       <x:c r="L561" s="2"/>
+      <x:c r="M561"/>
     </x:row>
     <x:row r="562">
       <x:c r="A562" s="36"/>
@@ -8421,6 +8993,7 @@
       <x:c r="J562" s="2"/>
       <x:c r="K562" s="2"/>
       <x:c r="L562" s="2"/>
+      <x:c r="M562"/>
     </x:row>
     <x:row r="563">
       <x:c r="A563" s="36"/>
@@ -8435,6 +9008,7 @@
       <x:c r="J563" s="2"/>
       <x:c r="K563" s="2"/>
       <x:c r="L563" s="2"/>
+      <x:c r="M563"/>
     </x:row>
     <x:row r="564">
       <x:c r="A564" s="36"/>
@@ -8449,6 +9023,7 @@
       <x:c r="J564" s="2"/>
       <x:c r="K564" s="2"/>
       <x:c r="L564" s="2"/>
+      <x:c r="M564"/>
     </x:row>
     <x:row r="565">
       <x:c r="A565" s="36"/>
@@ -8463,6 +9038,7 @@
       <x:c r="J565" s="2"/>
       <x:c r="K565" s="2"/>
       <x:c r="L565" s="2"/>
+      <x:c r="M565"/>
     </x:row>
     <x:row r="566">
       <x:c r="A566" s="36"/>
@@ -8477,6 +9053,7 @@
       <x:c r="J566" s="2"/>
       <x:c r="K566" s="2"/>
       <x:c r="L566" s="2"/>
+      <x:c r="M566"/>
     </x:row>
     <x:row r="567">
       <x:c r="A567" s="36"/>
@@ -8491,6 +9068,7 @@
       <x:c r="J567" s="2"/>
       <x:c r="K567" s="2"/>
       <x:c r="L567" s="2"/>
+      <x:c r="M567"/>
     </x:row>
     <x:row r="568">
       <x:c r="A568" s="36"/>
@@ -8505,6 +9083,7 @@
       <x:c r="J568" s="2"/>
       <x:c r="K568" s="2"/>
       <x:c r="L568" s="2"/>
+      <x:c r="M568"/>
     </x:row>
     <x:row r="569">
       <x:c r="A569" s="36"/>
@@ -8519,6 +9098,7 @@
       <x:c r="J569" s="2"/>
       <x:c r="K569" s="2"/>
       <x:c r="L569" s="2"/>
+      <x:c r="M569"/>
     </x:row>
     <x:row r="570">
       <x:c r="A570" s="36"/>
@@ -8533,6 +9113,7 @@
       <x:c r="J570" s="2"/>
       <x:c r="K570" s="2"/>
       <x:c r="L570" s="2"/>
+      <x:c r="M570"/>
     </x:row>
     <x:row r="571">
       <x:c r="A571" s="36"/>
@@ -8547,6 +9128,7 @@
       <x:c r="J571" s="2"/>
       <x:c r="K571" s="2"/>
       <x:c r="L571" s="2"/>
+      <x:c r="M571"/>
     </x:row>
     <x:row r="572">
       <x:c r="A572" s="36"/>
@@ -8561,6 +9143,7 @@
       <x:c r="J572" s="2"/>
       <x:c r="K572" s="2"/>
       <x:c r="L572" s="2"/>
+      <x:c r="M572"/>
     </x:row>
     <x:row r="573">
       <x:c r="A573" s="36"/>
@@ -8575,6 +9158,7 @@
       <x:c r="J573" s="2"/>
       <x:c r="K573" s="2"/>
       <x:c r="L573" s="2"/>
+      <x:c r="M573"/>
     </x:row>
     <x:row r="574">
       <x:c r="A574" s="36"/>
@@ -8589,6 +9173,7 @@
       <x:c r="J574" s="2"/>
       <x:c r="K574" s="2"/>
       <x:c r="L574" s="2"/>
+      <x:c r="M574"/>
     </x:row>
     <x:row r="575">
       <x:c r="A575" s="36"/>
@@ -8603,6 +9188,7 @@
       <x:c r="J575" s="2"/>
       <x:c r="K575" s="2"/>
       <x:c r="L575" s="2"/>
+      <x:c r="M575"/>
     </x:row>
     <x:row r="576">
       <x:c r="A576" s="36"/>
@@ -8617,6 +9203,7 @@
       <x:c r="J576" s="2"/>
       <x:c r="K576" s="2"/>
       <x:c r="L576" s="2"/>
+      <x:c r="M576"/>
     </x:row>
     <x:row r="577">
       <x:c r="A577" s="36"/>
@@ -8631,6 +9218,7 @@
       <x:c r="J577" s="2"/>
       <x:c r="K577" s="2"/>
       <x:c r="L577" s="2"/>
+      <x:c r="M577"/>
     </x:row>
     <x:row r="578">
       <x:c r="A578" s="36"/>
@@ -8645,6 +9233,7 @@
       <x:c r="J578" s="2"/>
       <x:c r="K578" s="2"/>
       <x:c r="L578" s="2"/>
+      <x:c r="M578"/>
     </x:row>
     <x:row r="579">
       <x:c r="A579" s="36"/>
@@ -8659,6 +9248,7 @@
       <x:c r="J579" s="2"/>
       <x:c r="K579" s="2"/>
       <x:c r="L579" s="2"/>
+      <x:c r="M579"/>
     </x:row>
     <x:row r="580">
       <x:c r="A580" s="36"/>
@@ -8673,6 +9263,7 @@
       <x:c r="J580" s="2"/>
       <x:c r="K580" s="2"/>
       <x:c r="L580" s="2"/>
+      <x:c r="M580"/>
     </x:row>
     <x:row r="581">
       <x:c r="A581" s="36"/>
@@ -8687,6 +9278,7 @@
       <x:c r="J581" s="2"/>
       <x:c r="K581" s="2"/>
       <x:c r="L581" s="2"/>
+      <x:c r="M581"/>
     </x:row>
     <x:row r="582">
       <x:c r="A582" s="36"/>
@@ -8701,6 +9293,7 @@
       <x:c r="J582" s="2"/>
       <x:c r="K582" s="2"/>
       <x:c r="L582" s="2"/>
+      <x:c r="M582"/>
     </x:row>
     <x:row r="583">
       <x:c r="A583" s="36"/>
@@ -8715,6 +9308,7 @@
       <x:c r="J583" s="2"/>
       <x:c r="K583" s="2"/>
       <x:c r="L583" s="2"/>
+      <x:c r="M583"/>
     </x:row>
     <x:row r="584">
       <x:c r="A584" s="36"/>
@@ -8729,6 +9323,7 @@
       <x:c r="J584" s="2"/>
       <x:c r="K584" s="2"/>
       <x:c r="L584" s="2"/>
+      <x:c r="M584"/>
     </x:row>
     <x:row r="585">
       <x:c r="A585" s="36"/>
@@ -8743,6 +9338,7 @@
       <x:c r="J585" s="2"/>
       <x:c r="K585" s="2"/>
       <x:c r="L585" s="2"/>
+      <x:c r="M585"/>
     </x:row>
     <x:row r="586">
       <x:c r="A586" s="36"/>
@@ -8757,6 +9353,7 @@
       <x:c r="J586" s="2"/>
       <x:c r="K586" s="2"/>
       <x:c r="L586" s="2"/>
+      <x:c r="M586"/>
     </x:row>
     <x:row r="587">
       <x:c r="A587" s="36"/>
@@ -8771,6 +9368,7 @@
       <x:c r="J587" s="2"/>
       <x:c r="K587" s="2"/>
       <x:c r="L587" s="2"/>
+      <x:c r="M587"/>
     </x:row>
     <x:row r="588">
       <x:c r="A588" s="36"/>
@@ -8785,6 +9383,7 @@
       <x:c r="J588" s="2"/>
       <x:c r="K588" s="2"/>
       <x:c r="L588" s="2"/>
+      <x:c r="M588"/>
     </x:row>
     <x:row r="589">
       <x:c r="A589" s="36"/>
@@ -8799,6 +9398,7 @@
       <x:c r="J589" s="2"/>
       <x:c r="K589" s="2"/>
       <x:c r="L589" s="2"/>
+      <x:c r="M589"/>
     </x:row>
     <x:row r="590">
       <x:c r="A590" s="36"/>
@@ -8813,6 +9413,7 @@
       <x:c r="J590" s="2"/>
       <x:c r="K590" s="2"/>
       <x:c r="L590" s="2"/>
+      <x:c r="M590"/>
     </x:row>
     <x:row r="591">
       <x:c r="A591" s="36"/>
@@ -8827,6 +9428,7 @@
       <x:c r="J591" s="2"/>
       <x:c r="K591" s="2"/>
       <x:c r="L591" s="2"/>
+      <x:c r="M591"/>
     </x:row>
     <x:row r="592">
       <x:c r="A592" s="36"/>
@@ -8841,6 +9443,7 @@
       <x:c r="J592" s="2"/>
       <x:c r="K592" s="2"/>
       <x:c r="L592" s="2"/>
+      <x:c r="M592"/>
     </x:row>
     <x:row r="593">
       <x:c r="A593" s="36"/>
@@ -8855,6 +9458,7 @@
       <x:c r="J593" s="2"/>
       <x:c r="K593" s="2"/>
       <x:c r="L593" s="2"/>
+      <x:c r="M593"/>
     </x:row>
     <x:row r="594">
       <x:c r="A594" s="36"/>
@@ -8869,6 +9473,7 @@
       <x:c r="J594" s="2"/>
       <x:c r="K594" s="2"/>
       <x:c r="L594" s="2"/>
+      <x:c r="M594"/>
     </x:row>
     <x:row r="595">
       <x:c r="A595" s="36"/>
@@ -8883,6 +9488,7 @@
       <x:c r="J595" s="2"/>
       <x:c r="K595" s="2"/>
       <x:c r="L595" s="2"/>
+      <x:c r="M595"/>
     </x:row>
     <x:row r="596">
       <x:c r="A596" s="36"/>
@@ -8897,6 +9503,7 @@
       <x:c r="J596" s="2"/>
       <x:c r="K596" s="2"/>
       <x:c r="L596" s="2"/>
+      <x:c r="M596"/>
     </x:row>
     <x:row r="597">
       <x:c r="A597" s="36"/>
@@ -8911,6 +9518,7 @@
       <x:c r="J597" s="2"/>
       <x:c r="K597" s="2"/>
       <x:c r="L597" s="2"/>
+      <x:c r="M597"/>
     </x:row>
     <x:row r="598">
       <x:c r="A598" s="36"/>
@@ -8925,6 +9533,7 @@
       <x:c r="J598" s="2"/>
       <x:c r="K598" s="2"/>
       <x:c r="L598" s="2"/>
+      <x:c r="M598"/>
     </x:row>
     <x:row r="599">
       <x:c r="A599" s="36"/>
@@ -8939,6 +9548,7 @@
       <x:c r="J599" s="2"/>
       <x:c r="K599" s="2"/>
       <x:c r="L599" s="2"/>
+      <x:c r="M599"/>
     </x:row>
     <x:row r="600">
       <x:c r="A600" s="36"/>
@@ -8953,6 +9563,7 @@
       <x:c r="J600" s="2"/>
       <x:c r="K600" s="2"/>
       <x:c r="L600" s="2"/>
+      <x:c r="M600"/>
     </x:row>
     <x:row r="601">
       <x:c r="A601" s="36"/>
@@ -8967,6 +9578,7 @@
       <x:c r="J601" s="2"/>
       <x:c r="K601" s="2"/>
       <x:c r="L601" s="2"/>
+      <x:c r="M601"/>
     </x:row>
     <x:row r="602">
       <x:c r="A602" s="36"/>
@@ -8981,6 +9593,7 @@
       <x:c r="J602" s="2"/>
       <x:c r="K602" s="2"/>
       <x:c r="L602" s="2"/>
+      <x:c r="M602"/>
     </x:row>
     <x:row r="603">
       <x:c r="A603" s="36"/>
@@ -8995,6 +9608,7 @@
       <x:c r="J603" s="2"/>
       <x:c r="K603" s="2"/>
       <x:c r="L603" s="2"/>
+      <x:c r="M603"/>
     </x:row>
     <x:row r="604">
       <x:c r="A604" s="36"/>
@@ -9009,6 +9623,7 @@
       <x:c r="J604" s="2"/>
       <x:c r="K604" s="2"/>
       <x:c r="L604" s="2"/>
+      <x:c r="M604"/>
     </x:row>
     <x:row r="605">
       <x:c r="A605" s="36"/>
@@ -9023,6 +9638,7 @@
       <x:c r="J605" s="2"/>
       <x:c r="K605" s="2"/>
       <x:c r="L605" s="2"/>
+      <x:c r="M605"/>
     </x:row>
     <x:row r="606">
       <x:c r="A606" s="36"/>
@@ -9037,6 +9653,7 @@
       <x:c r="J606" s="2"/>
       <x:c r="K606" s="2"/>
       <x:c r="L606" s="2"/>
+      <x:c r="M606"/>
     </x:row>
     <x:row r="607">
       <x:c r="A607" s="36"/>
@@ -9051,6 +9668,7 @@
       <x:c r="J607" s="2"/>
       <x:c r="K607" s="2"/>
       <x:c r="L607" s="2"/>
+      <x:c r="M607"/>
     </x:row>
     <x:row r="608">
       <x:c r="A608" s="36"/>
@@ -9065,6 +9683,7 @@
       <x:c r="J608" s="2"/>
       <x:c r="K608" s="2"/>
       <x:c r="L608" s="2"/>
+      <x:c r="M608"/>
     </x:row>
     <x:row r="609">
       <x:c r="A609" s="36"/>
@@ -9079,6 +9698,7 @@
       <x:c r="J609" s="2"/>
       <x:c r="K609" s="2"/>
       <x:c r="L609" s="2"/>
+      <x:c r="M609"/>
     </x:row>
     <x:row r="610">
       <x:c r="A610" s="36"/>
@@ -9093,6 +9713,7 @@
       <x:c r="J610" s="2"/>
       <x:c r="K610" s="2"/>
       <x:c r="L610" s="2"/>
+      <x:c r="M610"/>
     </x:row>
     <x:row r="611">
       <x:c r="A611" s="36"/>
@@ -9107,6 +9728,7 @@
       <x:c r="J611" s="2"/>
       <x:c r="K611" s="2"/>
       <x:c r="L611" s="2"/>
+      <x:c r="M611"/>
     </x:row>
     <x:row r="612">
       <x:c r="A612" s="36"/>
@@ -9121,6 +9743,7 @@
       <x:c r="J612" s="2"/>
       <x:c r="K612" s="2"/>
       <x:c r="L612" s="2"/>
+      <x:c r="M612"/>
     </x:row>
     <x:row r="613">
       <x:c r="A613" s="36"/>
@@ -9135,6 +9758,7 @@
       <x:c r="J613" s="2"/>
       <x:c r="K613" s="2"/>
       <x:c r="L613" s="2"/>
+      <x:c r="M613"/>
     </x:row>
     <x:row r="614">
       <x:c r="A614" s="36"/>
@@ -9149,6 +9773,7 @@
       <x:c r="J614" s="2"/>
       <x:c r="K614" s="2"/>
       <x:c r="L614" s="2"/>
+      <x:c r="M614"/>
     </x:row>
     <x:row r="615">
       <x:c r="A615" s="36"/>
@@ -9163,6 +9788,7 @@
       <x:c r="J615" s="2"/>
       <x:c r="K615" s="2"/>
       <x:c r="L615" s="2"/>
+      <x:c r="M615"/>
     </x:row>
     <x:row r="616">
       <x:c r="A616" s="36"/>
@@ -9177,6 +9803,7 @@
       <x:c r="J616" s="2"/>
       <x:c r="K616" s="2"/>
       <x:c r="L616" s="2"/>
+      <x:c r="M616"/>
     </x:row>
     <x:row r="617">
       <x:c r="A617" s="36"/>
@@ -9191,6 +9818,7 @@
       <x:c r="J617" s="2"/>
       <x:c r="K617" s="2"/>
       <x:c r="L617" s="2"/>
+      <x:c r="M617"/>
     </x:row>
     <x:row r="618">
       <x:c r="A618" s="36"/>
@@ -9205,6 +9833,7 @@
       <x:c r="J618" s="2"/>
       <x:c r="K618" s="2"/>
       <x:c r="L618" s="2"/>
+      <x:c r="M618"/>
     </x:row>
     <x:row r="619">
       <x:c r="A619" s="36"/>
@@ -9219,6 +9848,7 @@
       <x:c r="J619" s="2"/>
       <x:c r="K619" s="2"/>
       <x:c r="L619" s="2"/>
+      <x:c r="M619"/>
     </x:row>
     <x:row r="620">
       <x:c r="A620" s="36"/>
@@ -9233,6 +9863,7 @@
       <x:c r="J620" s="2"/>
       <x:c r="K620" s="2"/>
       <x:c r="L620" s="2"/>
+      <x:c r="M620"/>
     </x:row>
     <x:row r="621">
       <x:c r="A621" s="36"/>
@@ -9247,6 +9878,7 @@
       <x:c r="J621" s="2"/>
       <x:c r="K621" s="2"/>
       <x:c r="L621" s="2"/>
+      <x:c r="M621"/>
     </x:row>
     <x:row r="622">
       <x:c r="A622" s="36"/>
@@ -9261,6 +9893,7 @@
       <x:c r="J622" s="2"/>
       <x:c r="K622" s="2"/>
       <x:c r="L622" s="2"/>
+      <x:c r="M622"/>
     </x:row>
     <x:row r="623">
       <x:c r="A623" s="36"/>
@@ -9275,6 +9908,7 @@
       <x:c r="J623" s="2"/>
       <x:c r="K623" s="2"/>
       <x:c r="L623" s="2"/>
+      <x:c r="M623"/>
     </x:row>
     <x:row r="624">
       <x:c r="A624" s="36"/>
@@ -9289,6 +9923,7 @@
       <x:c r="J624" s="2"/>
       <x:c r="K624" s="2"/>
       <x:c r="L624" s="2"/>
+      <x:c r="M624"/>
     </x:row>
     <x:row r="625">
       <x:c r="A625" s="36"/>
@@ -9303,6 +9938,7 @@
       <x:c r="J625" s="2"/>
       <x:c r="K625" s="2"/>
       <x:c r="L625" s="2"/>
+      <x:c r="M625"/>
     </x:row>
     <x:row r="626">
       <x:c r="A626" s="36"/>
@@ -9317,6 +9953,7 @@
       <x:c r="J626" s="2"/>
       <x:c r="K626" s="2"/>
       <x:c r="L626" s="2"/>
+      <x:c r="M626"/>
     </x:row>
     <x:row r="627">
       <x:c r="A627" s="36"/>
@@ -9331,6 +9968,7 @@
       <x:c r="J627" s="2"/>
       <x:c r="K627" s="2"/>
       <x:c r="L627" s="2"/>
+      <x:c r="M627"/>
     </x:row>
     <x:row r="628">
       <x:c r="A628" s="36"/>
@@ -9345,6 +9983,7 @@
       <x:c r="J628" s="2"/>
       <x:c r="K628" s="2"/>
       <x:c r="L628" s="2"/>
+      <x:c r="M628"/>
     </x:row>
     <x:row r="629">
       <x:c r="A629" s="36"/>
@@ -9359,6 +9998,7 @@
       <x:c r="J629" s="2"/>
       <x:c r="K629" s="2"/>
       <x:c r="L629" s="2"/>
+      <x:c r="M629"/>
     </x:row>
     <x:row r="630">
       <x:c r="A630" s="36"/>
@@ -9373,6 +10013,7 @@
       <x:c r="J630" s="2"/>
       <x:c r="K630" s="2"/>
       <x:c r="L630" s="2"/>
+      <x:c r="M630"/>
     </x:row>
     <x:row r="631">
       <x:c r="A631" s="36"/>
@@ -9387,6 +10028,7 @@
       <x:c r="J631" s="2"/>
       <x:c r="K631" s="2"/>
       <x:c r="L631" s="2"/>
+      <x:c r="M631"/>
     </x:row>
     <x:row r="632">
       <x:c r="A632" s="36"/>
@@ -9401,6 +10043,7 @@
       <x:c r="J632" s="2"/>
       <x:c r="K632" s="2"/>
       <x:c r="L632" s="2"/>
+      <x:c r="M632"/>
     </x:row>
     <x:row r="633">
       <x:c r="A633" s="36"/>
@@ -9415,6 +10058,7 @@
       <x:c r="J633" s="2"/>
       <x:c r="K633" s="2"/>
       <x:c r="L633" s="2"/>
+      <x:c r="M633"/>
     </x:row>
     <x:row r="634">
       <x:c r="A634" s="36"/>
@@ -9429,6 +10073,7 @@
       <x:c r="J634" s="2"/>
       <x:c r="K634" s="2"/>
       <x:c r="L634" s="2"/>
+      <x:c r="M634"/>
     </x:row>
     <x:row r="635">
       <x:c r="A635" s="36"/>
@@ -9443,6 +10088,7 @@
       <x:c r="J635" s="2"/>
       <x:c r="K635" s="2"/>
       <x:c r="L635" s="2"/>
+      <x:c r="M635"/>
     </x:row>
     <x:row r="636">
       <x:c r="A636" s="36"/>
@@ -9457,6 +10103,7 @@
       <x:c r="J636" s="2"/>
       <x:c r="K636" s="2"/>
       <x:c r="L636" s="2"/>
+      <x:c r="M636"/>
     </x:row>
     <x:row r="637">
       <x:c r="A637" s="36"/>
@@ -9471,6 +10118,7 @@
       <x:c r="J637" s="2"/>
       <x:c r="K637" s="2"/>
       <x:c r="L637" s="2"/>
+      <x:c r="M637"/>
     </x:row>
     <x:row r="638">
       <x:c r="A638" s="36"/>
@@ -9485,6 +10133,7 @@
       <x:c r="J638" s="2"/>
       <x:c r="K638" s="2"/>
       <x:c r="L638" s="2"/>
+      <x:c r="M638"/>
     </x:row>
     <x:row r="639">
       <x:c r="A639" s="36"/>
@@ -9499,6 +10148,7 @@
       <x:c r="J639" s="2"/>
       <x:c r="K639" s="2"/>
       <x:c r="L639" s="2"/>
+      <x:c r="M639"/>
     </x:row>
     <x:row r="640">
       <x:c r="A640" s="36"/>
@@ -9513,6 +10163,7 @@
       <x:c r="J640" s="2"/>
       <x:c r="K640" s="2"/>
       <x:c r="L640" s="2"/>
+      <x:c r="M640"/>
     </x:row>
     <x:row r="641">
       <x:c r="A641" s="36"/>
@@ -9527,6 +10178,7 @@
       <x:c r="J641" s="2"/>
       <x:c r="K641" s="2"/>
       <x:c r="L641" s="2"/>
+      <x:c r="M641"/>
     </x:row>
     <x:row r="642">
       <x:c r="A642" s="36"/>
@@ -9541,6 +10193,7 @@
       <x:c r="J642" s="2"/>
       <x:c r="K642" s="2"/>
       <x:c r="L642" s="2"/>
+      <x:c r="M642"/>
     </x:row>
     <x:row r="643">
       <x:c r="A643" s="36"/>
@@ -9555,6 +10208,7 @@
       <x:c r="J643" s="2"/>
       <x:c r="K643" s="2"/>
       <x:c r="L643" s="2"/>
+      <x:c r="M643"/>
     </x:row>
     <x:row r="644">
       <x:c r="A644" s="36"/>
@@ -9569,6 +10223,7 @@
       <x:c r="J644" s="2"/>
       <x:c r="K644" s="2"/>
       <x:c r="L644" s="2"/>
+      <x:c r="M644"/>
     </x:row>
     <x:row r="645">
       <x:c r="A645" s="36"/>
@@ -9583,6 +10238,7 @@
       <x:c r="J645" s="2"/>
       <x:c r="K645" s="2"/>
       <x:c r="L645" s="2"/>
+      <x:c r="M645"/>
     </x:row>
     <x:row r="646">
       <x:c r="A646" s="36"/>
@@ -9597,6 +10253,7 @@
       <x:c r="J646" s="2"/>
       <x:c r="K646" s="2"/>
       <x:c r="L646" s="2"/>
+      <x:c r="M646"/>
     </x:row>
     <x:row r="647">
       <x:c r="A647" s="36"/>
@@ -9611,6 +10268,7 @@
       <x:c r="J647" s="2"/>
       <x:c r="K647" s="2"/>
       <x:c r="L647" s="2"/>
+      <x:c r="M647"/>
     </x:row>
     <x:row r="648">
       <x:c r="A648" s="36"/>
@@ -9625,6 +10283,7 @@
       <x:c r="J648" s="2"/>
       <x:c r="K648" s="2"/>
       <x:c r="L648" s="2"/>
+      <x:c r="M648"/>
     </x:row>
     <x:row r="649">
       <x:c r="A649" s="36"/>
@@ -9639,6 +10298,7 @@
       <x:c r="J649" s="2"/>
       <x:c r="K649" s="2"/>
       <x:c r="L649" s="2"/>
+      <x:c r="M649"/>
     </x:row>
     <x:row r="650">
       <x:c r="A650" s="36"/>
@@ -9653,6 +10313,7 @@
       <x:c r="J650" s="2"/>
       <x:c r="K650" s="2"/>
       <x:c r="L650" s="2"/>
+      <x:c r="M650"/>
     </x:row>
     <x:row r="651">
       <x:c r="A651" s="36"/>
@@ -9667,6 +10328,7 @@
       <x:c r="J651" s="2"/>
       <x:c r="K651" s="2"/>
       <x:c r="L651" s="2"/>
+      <x:c r="M651"/>
     </x:row>
     <x:row r="652">
       <x:c r="A652" s="36"/>
@@ -9681,6 +10343,7 @@
       <x:c r="J652" s="2"/>
       <x:c r="K652" s="2"/>
       <x:c r="L652" s="2"/>
+      <x:c r="M652"/>
     </x:row>
     <x:row r="653">
       <x:c r="A653" s="36"/>
@@ -9695,6 +10358,7 @@
       <x:c r="J653" s="2"/>
       <x:c r="K653" s="2"/>
       <x:c r="L653" s="2"/>
+      <x:c r="M653"/>
     </x:row>
     <x:row r="654">
       <x:c r="A654" s="36"/>
@@ -9709,6 +10373,7 @@
       <x:c r="J654" s="2"/>
       <x:c r="K654" s="2"/>
       <x:c r="L654" s="2"/>
+      <x:c r="M654"/>
     </x:row>
     <x:row r="655">
       <x:c r="A655" s="36"/>
@@ -9723,6 +10388,7 @@
       <x:c r="J655" s="2"/>
       <x:c r="K655" s="2"/>
       <x:c r="L655" s="2"/>
+      <x:c r="M655"/>
     </x:row>
     <x:row r="656">
       <x:c r="A656" s="36"/>
@@ -9737,6 +10403,7 @@
       <x:c r="J656" s="2"/>
       <x:c r="K656" s="2"/>
       <x:c r="L656" s="2"/>
+      <x:c r="M656"/>
     </x:row>
     <x:row r="657">
       <x:c r="A657" s="36"/>
@@ -9751,6 +10418,7 @@
       <x:c r="J657" s="2"/>
       <x:c r="K657" s="2"/>
       <x:c r="L657" s="2"/>
+      <x:c r="M657"/>
     </x:row>
     <x:row r="658">
       <x:c r="A658" s="36"/>
@@ -9765,6 +10433,7 @@
       <x:c r="J658" s="2"/>
       <x:c r="K658" s="2"/>
       <x:c r="L658" s="2"/>
+      <x:c r="M658"/>
     </x:row>
     <x:row r="659">
       <x:c r="A659" s="36"/>
@@ -9779,6 +10448,7 @@
       <x:c r="J659" s="2"/>
       <x:c r="K659" s="2"/>
       <x:c r="L659" s="2"/>
+      <x:c r="M659"/>
     </x:row>
     <x:row r="660">
       <x:c r="A660" s="36"/>
@@ -9793,6 +10463,7 @@
       <x:c r="J660" s="2"/>
       <x:c r="K660" s="2"/>
       <x:c r="L660" s="2"/>
+      <x:c r="M660"/>
     </x:row>
     <x:row r="661">
       <x:c r="A661" s="36"/>
@@ -9807,6 +10478,7 @@
       <x:c r="J661" s="2"/>
       <x:c r="K661" s="2"/>
       <x:c r="L661" s="2"/>
+      <x:c r="M661"/>
     </x:row>
     <x:row r="662">
       <x:c r="A662" s="36"/>
@@ -9821,6 +10493,7 @@
       <x:c r="J662" s="2"/>
       <x:c r="K662" s="2"/>
       <x:c r="L662" s="2"/>
+      <x:c r="M662"/>
     </x:row>
     <x:row r="663">
       <x:c r="A663" s="36"/>
@@ -9835,6 +10508,7 @@
       <x:c r="J663" s="2"/>
       <x:c r="K663" s="2"/>
       <x:c r="L663" s="2"/>
+      <x:c r="M663"/>
     </x:row>
     <x:row r="664">
       <x:c r="A664" s="36"/>
@@ -9849,6 +10523,7 @@
       <x:c r="J664" s="2"/>
       <x:c r="K664" s="2"/>
       <x:c r="L664" s="2"/>
+      <x:c r="M664"/>
     </x:row>
     <x:row r="665">
       <x:c r="A665" s="36"/>
@@ -9863,6 +10538,7 @@
       <x:c r="J665" s="2"/>
       <x:c r="K665" s="2"/>
       <x:c r="L665" s="2"/>
+      <x:c r="M665"/>
     </x:row>
     <x:row r="666">
       <x:c r="A666" s="36"/>
@@ -9877,6 +10553,7 @@
       <x:c r="J666" s="2"/>
       <x:c r="K666" s="2"/>
       <x:c r="L666" s="2"/>
+      <x:c r="M666"/>
     </x:row>
     <x:row r="667">
       <x:c r="A667" s="36"/>
@@ -9891,6 +10568,7 @@
       <x:c r="J667" s="2"/>
       <x:c r="K667" s="2"/>
       <x:c r="L667" s="2"/>
+      <x:c r="M667"/>
     </x:row>
     <x:row r="668">
       <x:c r="A668" s="36"/>
@@ -9905,6 +10583,7 @@
       <x:c r="J668" s="2"/>
       <x:c r="K668" s="2"/>
       <x:c r="L668" s="2"/>
+      <x:c r="M668"/>
     </x:row>
     <x:row r="669">
       <x:c r="A669" s="36"/>
@@ -9919,6 +10598,7 @@
       <x:c r="J669" s="2"/>
       <x:c r="K669" s="2"/>
       <x:c r="L669" s="2"/>
+      <x:c r="M669"/>
     </x:row>
     <x:row r="670">
       <x:c r="A670" s="36"/>
@@ -9933,6 +10613,7 @@
       <x:c r="J670" s="2"/>
       <x:c r="K670" s="2"/>
       <x:c r="L670" s="2"/>
+      <x:c r="M670"/>
     </x:row>
     <x:row r="671">
       <x:c r="A671" s="36"/>
@@ -9947,6 +10628,7 @@
       <x:c r="J671" s="2"/>
       <x:c r="K671" s="2"/>
       <x:c r="L671" s="2"/>
+      <x:c r="M671"/>
     </x:row>
     <x:row r="672">
       <x:c r="A672" s="36"/>
@@ -9961,6 +10643,7 @@
       <x:c r="J672" s="2"/>
       <x:c r="K672" s="2"/>
       <x:c r="L672" s="2"/>
+      <x:c r="M672"/>
     </x:row>
     <x:row r="673">
       <x:c r="A673" s="36"/>
@@ -9975,6 +10658,7 @@
       <x:c r="J673" s="2"/>
       <x:c r="K673" s="2"/>
       <x:c r="L673" s="2"/>
+      <x:c r="M673"/>
     </x:row>
     <x:row r="674">
       <x:c r="A674" s="36"/>
@@ -9989,6 +10673,7 @@
       <x:c r="J674" s="2"/>
       <x:c r="K674" s="2"/>
       <x:c r="L674" s="2"/>
+      <x:c r="M674"/>
     </x:row>
     <x:row r="675">
       <x:c r="A675" s="36"/>
@@ -10003,6 +10688,7 @@
       <x:c r="J675" s="2"/>
       <x:c r="K675" s="2"/>
       <x:c r="L675" s="2"/>
+      <x:c r="M675"/>
     </x:row>
     <x:row r="676">
       <x:c r="A676" s="36"/>
@@ -10017,6 +10703,7 @@
       <x:c r="J676" s="2"/>
       <x:c r="K676" s="2"/>
       <x:c r="L676" s="2"/>
+      <x:c r="M676"/>
     </x:row>
     <x:row r="677">
       <x:c r="A677" s="36"/>
@@ -10031,6 +10718,7 @@
       <x:c r="J677" s="2"/>
       <x:c r="K677" s="2"/>
       <x:c r="L677" s="2"/>
+      <x:c r="M677"/>
     </x:row>
     <x:row r="678">
       <x:c r="A678" s="36"/>
@@ -10045,6 +10733,7 @@
       <x:c r="J678" s="2"/>
       <x:c r="K678" s="2"/>
       <x:c r="L678" s="2"/>
+      <x:c r="M678"/>
     </x:row>
     <x:row r="679">
       <x:c r="A679" s="36"/>
@@ -10059,6 +10748,7 @@
       <x:c r="J679" s="2"/>
       <x:c r="K679" s="2"/>
       <x:c r="L679" s="2"/>
+      <x:c r="M679"/>
     </x:row>
     <x:row r="680">
       <x:c r="A680" s="36"/>
@@ -10073,6 +10763,7 @@
       <x:c r="J680" s="2"/>
       <x:c r="K680" s="2"/>
       <x:c r="L680" s="2"/>
+      <x:c r="M680"/>
     </x:row>
     <x:row r="681">
       <x:c r="A681" s="36"/>
@@ -10087,6 +10778,7 @@
       <x:c r="J681" s="2"/>
       <x:c r="K681" s="2"/>
       <x:c r="L681" s="2"/>
+      <x:c r="M681"/>
     </x:row>
     <x:row r="682">
       <x:c r="A682" s="36"/>
@@ -10101,6 +10793,7 @@
       <x:c r="J682" s="2"/>
       <x:c r="K682" s="2"/>
       <x:c r="L682" s="2"/>
+      <x:c r="M682"/>
     </x:row>
     <x:row r="683">
       <x:c r="A683" s="36"/>
@@ -10115,6 +10808,7 @@
       <x:c r="J683" s="2"/>
       <x:c r="K683" s="2"/>
       <x:c r="L683" s="2"/>
+      <x:c r="M683"/>
     </x:row>
     <x:row r="684">
       <x:c r="A684" s="36"/>
@@ -10129,6 +10823,7 @@
       <x:c r="J684" s="2"/>
       <x:c r="K684" s="2"/>
       <x:c r="L684" s="2"/>
+      <x:c r="M684"/>
     </x:row>
     <x:row r="685">
       <x:c r="A685" s="36"/>
@@ -10143,6 +10838,7 @@
       <x:c r="J685" s="2"/>
       <x:c r="K685" s="2"/>
       <x:c r="L685" s="2"/>
+      <x:c r="M685"/>
     </x:row>
     <x:row r="686">
       <x:c r="A686" s="36"/>
@@ -10157,6 +10853,7 @@
       <x:c r="J686" s="2"/>
       <x:c r="K686" s="2"/>
       <x:c r="L686" s="2"/>
+      <x:c r="M686"/>
     </x:row>
     <x:row r="687">
       <x:c r="A687" s="36"/>
@@ -10171,6 +10868,7 @@
       <x:c r="J687" s="2"/>
       <x:c r="K687" s="2"/>
       <x:c r="L687" s="2"/>
+      <x:c r="M687"/>
     </x:row>
     <x:row r="688">
       <x:c r="A688" s="36"/>
@@ -10185,6 +10883,7 @@
       <x:c r="J688" s="2"/>
       <x:c r="K688" s="2"/>
       <x:c r="L688" s="2"/>
+      <x:c r="M688"/>
     </x:row>
     <x:row r="689">
       <x:c r="A689" s="36"/>
@@ -10199,6 +10898,7 @@
       <x:c r="J689" s="2"/>
       <x:c r="K689" s="2"/>
       <x:c r="L689" s="2"/>
+      <x:c r="M689"/>
     </x:row>
     <x:row r="690">
       <x:c r="A690" s="36"/>
@@ -10213,6 +10913,7 @@
       <x:c r="J690" s="2"/>
       <x:c r="K690" s="2"/>
       <x:c r="L690" s="2"/>
+      <x:c r="M690"/>
     </x:row>
     <x:row r="691">
       <x:c r="A691" s="36"/>
@@ -10227,6 +10928,7 @@
       <x:c r="J691" s="2"/>
       <x:c r="K691" s="2"/>
       <x:c r="L691" s="2"/>
+      <x:c r="M691"/>
     </x:row>
     <x:row r="692">
       <x:c r="A692" s="36"/>
@@ -10241,6 +10943,7 @@
       <x:c r="J692" s="2"/>
       <x:c r="K692" s="2"/>
       <x:c r="L692" s="2"/>
+      <x:c r="M692"/>
     </x:row>
     <x:row r="693">
       <x:c r="A693" s="36"/>
@@ -10255,6 +10958,7 @@
       <x:c r="J693" s="2"/>
       <x:c r="K693" s="2"/>
       <x:c r="L693" s="2"/>
+      <x:c r="M693"/>
     </x:row>
     <x:row r="694">
       <x:c r="A694" s="36"/>
@@ -10269,6 +10973,7 @@
       <x:c r="J694" s="2"/>
       <x:c r="K694" s="2"/>
       <x:c r="L694" s="2"/>
+      <x:c r="M694"/>
     </x:row>
     <x:row r="695">
       <x:c r="A695" s="36"/>
@@ -10283,6 +10988,7 @@
       <x:c r="J695" s="2"/>
       <x:c r="K695" s="2"/>
       <x:c r="L695" s="2"/>
+      <x:c r="M695"/>
     </x:row>
     <x:row r="696">
       <x:c r="A696" s="36"/>
@@ -10297,6 +11003,7 @@
       <x:c r="J696" s="2"/>
       <x:c r="K696" s="2"/>
       <x:c r="L696" s="2"/>
+      <x:c r="M696"/>
     </x:row>
     <x:row r="697">
       <x:c r="A697" s="36"/>
@@ -10311,6 +11018,7 @@
       <x:c r="J697" s="2"/>
       <x:c r="K697" s="2"/>
       <x:c r="L697" s="2"/>
+      <x:c r="M697"/>
     </x:row>
     <x:row r="698">
       <x:c r="A698" s="36"/>
@@ -10325,6 +11033,7 @@
       <x:c r="J698" s="2"/>
       <x:c r="K698" s="2"/>
       <x:c r="L698" s="2"/>
+      <x:c r="M698"/>
     </x:row>
     <x:row r="699">
       <x:c r="A699" s="36"/>
@@ -10339,6 +11048,7 @@
       <x:c r="J699" s="2"/>
       <x:c r="K699" s="2"/>
       <x:c r="L699" s="2"/>
+      <x:c r="M699"/>
     </x:row>
     <x:row r="700">
       <x:c r="A700" s="36"/>
@@ -10353,6 +11063,7 @@
       <x:c r="J700" s="2"/>
       <x:c r="K700" s="2"/>
       <x:c r="L700" s="2"/>
+      <x:c r="M700"/>
     </x:row>
     <x:row r="701">
       <x:c r="A701" s="36"/>
@@ -10367,6 +11078,7 @@
       <x:c r="J701" s="2"/>
       <x:c r="K701" s="2"/>
       <x:c r="L701" s="2"/>
+      <x:c r="M701"/>
     </x:row>
     <x:row r="702">
       <x:c r="A702" s="36"/>
@@ -10381,6 +11093,7 @@
       <x:c r="J702" s="2"/>
       <x:c r="K702" s="2"/>
       <x:c r="L702" s="2"/>
+      <x:c r="M702"/>
     </x:row>
     <x:row r="703">
       <x:c r="A703" s="36"/>
@@ -10395,6 +11108,7 @@
       <x:c r="J703" s="2"/>
       <x:c r="K703" s="2"/>
       <x:c r="L703" s="2"/>
+      <x:c r="M703"/>
     </x:row>
     <x:row r="704">
       <x:c r="A704" s="36"/>
@@ -10409,6 +11123,7 @@
       <x:c r="J704" s="2"/>
       <x:c r="K704" s="2"/>
       <x:c r="L704" s="2"/>
+      <x:c r="M704"/>
     </x:row>
     <x:row r="705">
       <x:c r="A705" s="36"/>
@@ -10423,6 +11138,7 @@
       <x:c r="J705" s="2"/>
       <x:c r="K705" s="2"/>
       <x:c r="L705" s="2"/>
+      <x:c r="M705"/>
     </x:row>
     <x:row r="706">
       <x:c r="A706" s="36"/>
@@ -10437,6 +11153,7 @@
       <x:c r="J706" s="2"/>
       <x:c r="K706" s="2"/>
       <x:c r="L706" s="2"/>
+      <x:c r="M706"/>
     </x:row>
     <x:row r="707">
       <x:c r="A707" s="36"/>
@@ -10451,6 +11168,7 @@
       <x:c r="J707" s="2"/>
       <x:c r="K707" s="2"/>
       <x:c r="L707" s="2"/>
+      <x:c r="M707"/>
     </x:row>
     <x:row r="708">
       <x:c r="A708" s="36"/>
@@ -10465,6 +11183,7 @@
       <x:c r="J708" s="2"/>
       <x:c r="K708" s="2"/>
       <x:c r="L708" s="2"/>
+      <x:c r="M708"/>
     </x:row>
     <x:row r="709">
       <x:c r="A709" s="36"/>
@@ -10479,6 +11198,7 @@
       <x:c r="J709" s="2"/>
       <x:c r="K709" s="2"/>
       <x:c r="L709" s="2"/>
+      <x:c r="M709"/>
     </x:row>
     <x:row r="710">
       <x:c r="A710" s="36"/>
@@ -10493,6 +11213,7 @@
       <x:c r="J710" s="2"/>
       <x:c r="K710" s="2"/>
       <x:c r="L710" s="2"/>
+      <x:c r="M710"/>
     </x:row>
     <x:row r="711">
       <x:c r="A711" s="36"/>
@@ -10507,6 +11228,7 @@
       <x:c r="J711" s="2"/>
       <x:c r="K711" s="2"/>
       <x:c r="L711" s="2"/>
+      <x:c r="M711"/>
     </x:row>
     <x:row r="712">
       <x:c r="A712" s="36"/>
@@ -10521,6 +11243,7 @@
       <x:c r="J712" s="2"/>
       <x:c r="K712" s="2"/>
       <x:c r="L712" s="2"/>
+      <x:c r="M712"/>
     </x:row>
     <x:row r="713">
       <x:c r="A713" s="36"/>
@@ -10535,6 +11258,7 @@
       <x:c r="J713" s="2"/>
       <x:c r="K713" s="2"/>
       <x:c r="L713" s="2"/>
+      <x:c r="M713"/>
     </x:row>
     <x:row r="714">
       <x:c r="A714" s="36"/>
@@ -10549,6 +11273,7 @@
       <x:c r="J714" s="2"/>
       <x:c r="K714" s="2"/>
       <x:c r="L714" s="2"/>
+      <x:c r="M714"/>
     </x:row>
     <x:row r="715">
       <x:c r="A715" s="36"/>
@@ -10563,6 +11288,7 @@
       <x:c r="J715" s="2"/>
       <x:c r="K715" s="2"/>
       <x:c r="L715" s="2"/>
+      <x:c r="M715"/>
     </x:row>
     <x:row r="716">
       <x:c r="A716" s="36"/>
@@ -10577,6 +11303,7 @@
       <x:c r="J716" s="2"/>
       <x:c r="K716" s="2"/>
       <x:c r="L716" s="2"/>
+      <x:c r="M716"/>
     </x:row>
     <x:row r="717">
       <x:c r="A717" s="36"/>
@@ -10591,6 +11318,7 @@
       <x:c r="J717" s="2"/>
       <x:c r="K717" s="2"/>
       <x:c r="L717" s="2"/>
+      <x:c r="M717"/>
     </x:row>
     <x:row r="718">
       <x:c r="A718" s="36"/>
@@ -10605,6 +11333,7 @@
       <x:c r="J718" s="2"/>
       <x:c r="K718" s="2"/>
       <x:c r="L718" s="2"/>
+      <x:c r="M718"/>
     </x:row>
     <x:row r="719">
       <x:c r="A719" s="36"/>
@@ -10619,6 +11348,7 @@
       <x:c r="J719" s="2"/>
       <x:c r="K719" s="2"/>
       <x:c r="L719" s="2"/>
+      <x:c r="M719"/>
     </x:row>
     <x:row r="720">
       <x:c r="A720" s="36"/>
@@ -10633,6 +11363,7 @@
       <x:c r="J720" s="2"/>
       <x:c r="K720" s="2"/>
       <x:c r="L720" s="2"/>
+      <x:c r="M720"/>
     </x:row>
     <x:row r="721">
       <x:c r="A721" s="36"/>
@@ -10647,6 +11378,7 @@
       <x:c r="J721" s="2"/>
       <x:c r="K721" s="2"/>
       <x:c r="L721" s="2"/>
+      <x:c r="M721"/>
     </x:row>
     <x:row r="722">
       <x:c r="A722" s="36"/>
@@ -10661,6 +11393,7 @@
       <x:c r="J722" s="2"/>
       <x:c r="K722" s="2"/>
       <x:c r="L722" s="2"/>
+      <x:c r="M722"/>
     </x:row>
     <x:row r="723">
       <x:c r="A723" s="36"/>
@@ -10675,6 +11408,7 @@
       <x:c r="J723" s="2"/>
       <x:c r="K723" s="2"/>
       <x:c r="L723" s="2"/>
+      <x:c r="M723"/>
     </x:row>
     <x:row r="724">
       <x:c r="A724" s="36"/>
@@ -10689,6 +11423,7 @@
       <x:c r="J724" s="2"/>
       <x:c r="K724" s="2"/>
       <x:c r="L724" s="2"/>
+      <x:c r="M724"/>
     </x:row>
     <x:row r="725">
       <x:c r="A725" s="36"/>
@@ -10703,6 +11438,7 @@
       <x:c r="J725" s="2"/>
       <x:c r="K725" s="2"/>
       <x:c r="L725" s="2"/>
+      <x:c r="M725"/>
     </x:row>
     <x:row r="726">
       <x:c r="A726" s="36"/>
@@ -10717,6 +11453,7 @@
       <x:c r="J726" s="2"/>
       <x:c r="K726" s="2"/>
       <x:c r="L726" s="2"/>
+      <x:c r="M726"/>
     </x:row>
     <x:row r="727">
       <x:c r="A727" s="36"/>
@@ -10731,6 +11468,7 @@
       <x:c r="J727" s="2"/>
       <x:c r="K727" s="2"/>
       <x:c r="L727" s="2"/>
+      <x:c r="M727"/>
     </x:row>
     <x:row r="728">
       <x:c r="A728" s="36"/>
@@ -10745,6 +11483,7 @@
       <x:c r="J728" s="2"/>
       <x:c r="K728" s="2"/>
       <x:c r="L728" s="2"/>
+      <x:c r="M728"/>
     </x:row>
     <x:row r="729">
       <x:c r="A729" s="36"/>
@@ -10759,6 +11498,7 @@
       <x:c r="J729" s="2"/>
       <x:c r="K729" s="2"/>
       <x:c r="L729" s="2"/>
+      <x:c r="M729"/>
     </x:row>
     <x:row r="730">
       <x:c r="A730" s="36"/>
@@ -10773,6 +11513,7 @@
       <x:c r="J730" s="2"/>
       <x:c r="K730" s="2"/>
       <x:c r="L730" s="2"/>
+      <x:c r="M730"/>
     </x:row>
     <x:row r="731">
       <x:c r="A731" s="36"/>
@@ -10787,6 +11528,7 @@
       <x:c r="J731" s="2"/>
       <x:c r="K731" s="2"/>
       <x:c r="L731" s="2"/>
+      <x:c r="M731"/>
     </x:row>
     <x:row r="732">
       <x:c r="A732" s="36"/>
@@ -10801,6 +11543,7 @@
       <x:c r="J732" s="2"/>
       <x:c r="K732" s="2"/>
       <x:c r="L732" s="2"/>
+      <x:c r="M732"/>
     </x:row>
     <x:row r="733">
       <x:c r="A733" s="36"/>
@@ -10815,6 +11558,7 @@
       <x:c r="J733" s="2"/>
       <x:c r="K733" s="2"/>
       <x:c r="L733" s="2"/>
+      <x:c r="M733"/>
     </x:row>
     <x:row r="734">
       <x:c r="A734" s="36"/>
@@ -10829,6 +11573,7 @@
       <x:c r="J734" s="2"/>
       <x:c r="K734" s="2"/>
       <x:c r="L734" s="2"/>
+      <x:c r="M734"/>
     </x:row>
     <x:row r="735">
       <x:c r="A735" s="36"/>
@@ -10843,6 +11588,7 @@
       <x:c r="J735" s="2"/>
       <x:c r="K735" s="2"/>
       <x:c r="L735" s="2"/>
+      <x:c r="M735"/>
     </x:row>
     <x:row r="736">
       <x:c r="A736" s="36"/>
@@ -10857,6 +11603,7 @@
       <x:c r="J736" s="2"/>
       <x:c r="K736" s="2"/>
       <x:c r="L736" s="2"/>
+      <x:c r="M736"/>
     </x:row>
     <x:row r="737">
       <x:c r="A737" s="36"/>
@@ -10871,6 +11618,7 @@
       <x:c r="J737" s="2"/>
       <x:c r="K737" s="2"/>
       <x:c r="L737" s="2"/>
+      <x:c r="M737"/>
     </x:row>
     <x:row r="738">
       <x:c r="A738" s="36"/>
@@ -10885,6 +11633,7 @@
       <x:c r="J738" s="2"/>
       <x:c r="K738" s="2"/>
       <x:c r="L738" s="2"/>
+      <x:c r="M738"/>
     </x:row>
     <x:row r="739">
       <x:c r="A739" s="36"/>
@@ -10899,6 +11648,7 @@
       <x:c r="J739" s="2"/>
       <x:c r="K739" s="2"/>
       <x:c r="L739" s="2"/>
+      <x:c r="M739"/>
     </x:row>
     <x:row r="740">
       <x:c r="A740" s="36"/>
@@ -10913,6 +11663,7 @@
       <x:c r="J740" s="2"/>
       <x:c r="K740" s="2"/>
       <x:c r="L740" s="2"/>
+      <x:c r="M740"/>
     </x:row>
     <x:row r="741">
       <x:c r="A741" s="36"/>
@@ -10927,6 +11678,7 @@
       <x:c r="J741" s="2"/>
       <x:c r="K741" s="2"/>
       <x:c r="L741" s="2"/>
+      <x:c r="M741"/>
     </x:row>
     <x:row r="742">
       <x:c r="A742" s="36"/>
@@ -10941,6 +11693,7 @@
       <x:c r="J742" s="2"/>
       <x:c r="K742" s="2"/>
       <x:c r="L742" s="2"/>
+      <x:c r="M742"/>
     </x:row>
     <x:row r="743">
       <x:c r="A743" s="36"/>
@@ -10955,6 +11708,7 @@
       <x:c r="J743" s="2"/>
       <x:c r="K743" s="2"/>
       <x:c r="L743" s="2"/>
+      <x:c r="M743"/>
     </x:row>
     <x:row r="744">
       <x:c r="A744" s="36"/>
@@ -10969,6 +11723,7 @@
       <x:c r="J744" s="2"/>
       <x:c r="K744" s="2"/>
       <x:c r="L744" s="2"/>
+      <x:c r="M744"/>
     </x:row>
     <x:row r="745">
       <x:c r="A745" s="36"/>
@@ -10983,6 +11738,7 @@
       <x:c r="J745" s="2"/>
       <x:c r="K745" s="2"/>
       <x:c r="L745" s="2"/>
+      <x:c r="M745"/>
     </x:row>
     <x:row r="746">
       <x:c r="A746" s="36"/>
@@ -10997,6 +11753,7 @@
       <x:c r="J746" s="2"/>
       <x:c r="K746" s="2"/>
       <x:c r="L746" s="2"/>
+      <x:c r="M746"/>
     </x:row>
     <x:row r="747">
       <x:c r="A747" s="36"/>
@@ -11011,6 +11768,7 @@
       <x:c r="J747" s="2"/>
       <x:c r="K747" s="2"/>
       <x:c r="L747" s="2"/>
+      <x:c r="M747"/>
     </x:row>
     <x:row r="748">
       <x:c r="A748" s="36"/>
@@ -11025,6 +11783,7 @@
       <x:c r="J748" s="2"/>
       <x:c r="K748" s="2"/>
       <x:c r="L748" s="2"/>
+      <x:c r="M748"/>
     </x:row>
     <x:row r="749">
       <x:c r="A749" s="36"/>
@@ -11039,6 +11798,7 @@
       <x:c r="J749" s="2"/>
       <x:c r="K749" s="2"/>
       <x:c r="L749" s="2"/>
+      <x:c r="M749"/>
     </x:row>
     <x:row r="750">
       <x:c r="A750" s="36"/>
@@ -11053,6 +11813,7 @@
       <x:c r="J750" s="2"/>
       <x:c r="K750" s="2"/>
       <x:c r="L750" s="2"/>
+      <x:c r="M750"/>
     </x:row>
     <x:row r="751">
       <x:c r="A751" s="36"/>
@@ -11067,6 +11828,7 @@
       <x:c r="J751" s="2"/>
       <x:c r="K751" s="2"/>
       <x:c r="L751" s="2"/>
+      <x:c r="M751"/>
     </x:row>
     <x:row r="752">
       <x:c r="A752" s="36"/>
@@ -11081,6 +11843,7 @@
       <x:c r="J752" s="2"/>
       <x:c r="K752" s="2"/>
       <x:c r="L752" s="2"/>
+      <x:c r="M752"/>
     </x:row>
     <x:row r="753">
       <x:c r="A753" s="36"/>
@@ -11095,6 +11858,7 @@
       <x:c r="J753" s="2"/>
       <x:c r="K753" s="2"/>
       <x:c r="L753" s="2"/>
+      <x:c r="M753"/>
     </x:row>
     <x:row r="754">
       <x:c r="A754" s="36"/>
@@ -11109,6 +11873,7 @@
       <x:c r="J754" s="2"/>
       <x:c r="K754" s="2"/>
       <x:c r="L754" s="2"/>
+      <x:c r="M754"/>
     </x:row>
     <x:row r="755">
       <x:c r="A755" s="36"/>
@@ -11123,6 +11888,7 @@
       <x:c r="J755" s="2"/>
       <x:c r="K755" s="2"/>
       <x:c r="L755" s="2"/>
+      <x:c r="M755"/>
     </x:row>
     <x:row r="756">
       <x:c r="A756" s="36"/>
@@ -11137,6 +11903,7 @@
       <x:c r="J756" s="2"/>
       <x:c r="K756" s="2"/>
       <x:c r="L756" s="2"/>
+      <x:c r="M756"/>
     </x:row>
     <x:row r="757">
       <x:c r="A757" s="36"/>
@@ -11151,6 +11918,7 @@
       <x:c r="J757" s="2"/>
       <x:c r="K757" s="2"/>
       <x:c r="L757" s="2"/>
+      <x:c r="M757"/>
     </x:row>
     <x:row r="758">
       <x:c r="A758" s="36"/>
@@ -11165,6 +11933,7 @@
       <x:c r="J758" s="2"/>
       <x:c r="K758" s="2"/>
       <x:c r="L758" s="2"/>
+      <x:c r="M758"/>
     </x:row>
     <x:row r="759">
       <x:c r="A759" s="36"/>
@@ -11179,6 +11948,7 @@
       <x:c r="J759" s="2"/>
       <x:c r="K759" s="2"/>
       <x:c r="L759" s="2"/>
+      <x:c r="M759"/>
     </x:row>
     <x:row r="760">
       <x:c r="A760" s="36"/>
@@ -11193,6 +11963,7 @@
       <x:c r="J760" s="2"/>
       <x:c r="K760" s="2"/>
       <x:c r="L760" s="2"/>
+      <x:c r="M760"/>
     </x:row>
     <x:row r="761">
       <x:c r="A761" s="36"/>
@@ -11207,6 +11978,7 @@
       <x:c r="J761" s="2"/>
       <x:c r="K761" s="2"/>
       <x:c r="L761" s="2"/>
+      <x:c r="M761"/>
     </x:row>
     <x:row r="762">
       <x:c r="A762" s="36"/>
@@ -11221,6 +11993,7 @@
       <x:c r="J762" s="2"/>
       <x:c r="K762" s="2"/>
       <x:c r="L762" s="2"/>
+      <x:c r="M762"/>
     </x:row>
     <x:row r="763">
       <x:c r="A763" s="36"/>
@@ -11235,6 +12008,7 @@
       <x:c r="J763" s="2"/>
       <x:c r="K763" s="2"/>
       <x:c r="L763" s="2"/>
+      <x:c r="M763"/>
     </x:row>
     <x:row r="764">
       <x:c r="A764" s="36"/>
@@ -11249,6 +12023,7 @@
       <x:c r="J764" s="2"/>
       <x:c r="K764" s="2"/>
       <x:c r="L764" s="2"/>
+      <x:c r="M764"/>
     </x:row>
     <x:row r="765">
       <x:c r="A765" s="36"/>
@@ -11263,6 +12038,7 @@
       <x:c r="J765" s="2"/>
       <x:c r="K765" s="2"/>
       <x:c r="L765" s="2"/>
+      <x:c r="M765"/>
     </x:row>
     <x:row r="766">
       <x:c r="A766" s="36"/>
@@ -11277,6 +12053,7 @@
       <x:c r="J766" s="2"/>
       <x:c r="K766" s="2"/>
       <x:c r="L766" s="2"/>
+      <x:c r="M766"/>
     </x:row>
     <x:row r="767">
       <x:c r="A767" s="36"/>
@@ -11291,6 +12068,7 @@
       <x:c r="J767" s="2"/>
       <x:c r="K767" s="2"/>
       <x:c r="L767" s="2"/>
+      <x:c r="M767"/>
     </x:row>
     <x:row r="768">
       <x:c r="A768" s="36"/>
@@ -11305,6 +12083,7 @@
       <x:c r="J768" s="2"/>
       <x:c r="K768" s="2"/>
       <x:c r="L768" s="2"/>
+      <x:c r="M768"/>
     </x:row>
     <x:row r="769">
       <x:c r="A769" s="36"/>
@@ -11319,6 +12098,7 @@
       <x:c r="J769" s="2"/>
       <x:c r="K769" s="2"/>
       <x:c r="L769" s="2"/>
+      <x:c r="M769"/>
     </x:row>
     <x:row r="770">
       <x:c r="A770" s="36"/>
@@ -11333,6 +12113,7 @@
       <x:c r="J770" s="2"/>
       <x:c r="K770" s="2"/>
       <x:c r="L770" s="2"/>
+      <x:c r="M770"/>
     </x:row>
     <x:row r="771">
       <x:c r="A771" s="36"/>
@@ -11347,6 +12128,7 @@
       <x:c r="J771" s="2"/>
       <x:c r="K771" s="2"/>
       <x:c r="L771" s="2"/>
+      <x:c r="M771"/>
     </x:row>
     <x:row r="772">
       <x:c r="A772" s="36"/>
@@ -11361,6 +12143,7 @@
       <x:c r="J772" s="2"/>
       <x:c r="K772" s="2"/>
       <x:c r="L772" s="2"/>
+      <x:c r="M772"/>
     </x:row>
     <x:row r="773">
       <x:c r="A773" s="36"/>
@@ -11375,6 +12158,7 @@
       <x:c r="J773" s="2"/>
       <x:c r="K773" s="2"/>
       <x:c r="L773" s="2"/>
+      <x:c r="M773"/>
     </x:row>
     <x:row r="774">
       <x:c r="A774" s="36"/>
@@ -11389,6 +12173,7 @@
       <x:c r="J774" s="2"/>
       <x:c r="K774" s="2"/>
       <x:c r="L774" s="2"/>
+      <x:c r="M774"/>
     </x:row>
     <x:row r="775">
       <x:c r="A775" s="36"/>
@@ -11403,6 +12188,7 @@
       <x:c r="J775" s="2"/>
       <x:c r="K775" s="2"/>
       <x:c r="L775" s="2"/>
+      <x:c r="M775"/>
     </x:row>
     <x:row r="776">
       <x:c r="A776" s="36"/>
@@ -11417,6 +12203,7 @@
       <x:c r="J776" s="2"/>
       <x:c r="K776" s="2"/>
       <x:c r="L776" s="2"/>
+      <x:c r="M776"/>
     </x:row>
     <x:row r="777">
       <x:c r="A777" s="36"/>
@@ -11431,6 +12218,7 @@
       <x:c r="J777" s="2"/>
       <x:c r="K777" s="2"/>
       <x:c r="L777" s="2"/>
+      <x:c r="M777"/>
     </x:row>
     <x:row r="778">
       <x:c r="A778" s="36"/>
@@ -11445,6 +12233,7 @@
       <x:c r="J778" s="2"/>
       <x:c r="K778" s="2"/>
       <x:c r="L778" s="2"/>
+      <x:c r="M778"/>
     </x:row>
     <x:row r="779">
       <x:c r="A779" s="36"/>
@@ -11459,6 +12248,7 @@
       <x:c r="J779" s="2"/>
       <x:c r="K779" s="2"/>
       <x:c r="L779" s="2"/>
+      <x:c r="M779"/>
     </x:row>
     <x:row r="780">
       <x:c r="A780" s="36"/>
@@ -11473,6 +12263,7 @@
       <x:c r="J780" s="2"/>
       <x:c r="K780" s="2"/>
       <x:c r="L780" s="2"/>
+      <x:c r="M780"/>
     </x:row>
     <x:row r="781">
       <x:c r="A781" s="36"/>
@@ -11487,6 +12278,7 @@
       <x:c r="J781" s="2"/>
       <x:c r="K781" s="2"/>
       <x:c r="L781" s="2"/>
+      <x:c r="M781"/>
     </x:row>
     <x:row r="782">
       <x:c r="A782" s="36"/>
@@ -11501,6 +12293,7 @@
       <x:c r="J782" s="2"/>
       <x:c r="K782" s="2"/>
       <x:c r="L782" s="2"/>
+      <x:c r="M782"/>
     </x:row>
     <x:row r="783">
       <x:c r="A783" s="36"/>
@@ -11515,6 +12308,7 @@
       <x:c r="J783" s="2"/>
       <x:c r="K783" s="2"/>
       <x:c r="L783" s="2"/>
+      <x:c r="M783"/>
     </x:row>
     <x:row r="784">
       <x:c r="A784" s="36"/>
@@ -11529,6 +12323,7 @@
       <x:c r="J784" s="2"/>
       <x:c r="K784" s="2"/>
       <x:c r="L784" s="2"/>
+      <x:c r="M784"/>
     </x:row>
     <x:row r="785">
       <x:c r="A785" s="36"/>
@@ -11543,6 +12338,7 @@
       <x:c r="J785" s="2"/>
       <x:c r="K785" s="2"/>
       <x:c r="L785" s="2"/>
+      <x:c r="M785"/>
     </x:row>
     <x:row r="786">
       <x:c r="A786" s="36"/>
@@ -11557,6 +12353,7 @@
       <x:c r="J786" s="2"/>
       <x:c r="K786" s="2"/>
       <x:c r="L786" s="2"/>
+      <x:c r="M786"/>
     </x:row>
     <x:row r="787">
       <x:c r="A787" s="36"/>
@@ -11571,6 +12368,7 @@
       <x:c r="J787" s="2"/>
       <x:c r="K787" s="2"/>
       <x:c r="L787" s="2"/>
+      <x:c r="M787"/>
     </x:row>
     <x:row r="788">
       <x:c r="A788" s="36"/>
@@ -11585,6 +12383,7 @@
       <x:c r="J788" s="2"/>
       <x:c r="K788" s="2"/>
       <x:c r="L788" s="2"/>
+      <x:c r="M788"/>
     </x:row>
     <x:row r="789">
       <x:c r="A789" s="36"/>
@@ -11599,6 +12398,7 @@
       <x:c r="J789" s="2"/>
       <x:c r="K789" s="2"/>
       <x:c r="L789" s="2"/>
+      <x:c r="M789"/>
     </x:row>
     <x:row r="790">
       <x:c r="A790" s="36"/>
@@ -11613,6 +12413,7 @@
       <x:c r="J790" s="2"/>
       <x:c r="K790" s="2"/>
       <x:c r="L790" s="2"/>
+      <x:c r="M790"/>
     </x:row>
     <x:row r="791">
       <x:c r="A791" s="36"/>
@@ -11627,6 +12428,7 @@
       <x:c r="J791" s="2"/>
       <x:c r="K791" s="2"/>
       <x:c r="L791" s="2"/>
+      <x:c r="M791"/>
     </x:row>
     <x:row r="792">
       <x:c r="A792" s="36"/>
@@ -11641,6 +12443,7 @@
       <x:c r="J792" s="2"/>
       <x:c r="K792" s="2"/>
       <x:c r="L792" s="2"/>
+      <x:c r="M792"/>
     </x:row>
     <x:row r="793">
       <x:c r="A793" s="36"/>
@@ -11655,6 +12458,7 @@
       <x:c r="J793" s="2"/>
       <x:c r="K793" s="2"/>
       <x:c r="L793" s="2"/>
+      <x:c r="M793"/>
     </x:row>
     <x:row r="794">
       <x:c r="A794" s="36"/>
@@ -11669,6 +12473,7 @@
       <x:c r="J794" s="2"/>
       <x:c r="K794" s="2"/>
       <x:c r="L794" s="2"/>
+      <x:c r="M794"/>
     </x:row>
     <x:row r="795">
       <x:c r="A795" s="36"/>
@@ -11683,6 +12488,7 @@
       <x:c r="J795" s="2"/>
       <x:c r="K795" s="2"/>
       <x:c r="L795" s="2"/>
+      <x:c r="M795"/>
     </x:row>
     <x:row r="796">
       <x:c r="A796" s="36"/>
@@ -11697,6 +12503,7 @@
       <x:c r="J796" s="2"/>
       <x:c r="K796" s="2"/>
       <x:c r="L796" s="2"/>
+      <x:c r="M796"/>
     </x:row>
     <x:row r="797">
       <x:c r="A797" s="36"/>
@@ -11711,6 +12518,7 @@
       <x:c r="J797" s="2"/>
       <x:c r="K797" s="2"/>
       <x:c r="L797" s="2"/>
+      <x:c r="M797"/>
     </x:row>
     <x:row r="798">
       <x:c r="A798" s="36"/>
@@ -11725,6 +12533,7 @@
       <x:c r="J798" s="2"/>
       <x:c r="K798" s="2"/>
       <x:c r="L798" s="2"/>
+      <x:c r="M798"/>
     </x:row>
     <x:row r="799">
       <x:c r="A799" s="36"/>
@@ -11739,6 +12548,7 @@
       <x:c r="J799" s="2"/>
       <x:c r="K799" s="2"/>
       <x:c r="L799" s="2"/>
+      <x:c r="M799"/>
     </x:row>
     <x:row r="800">
       <x:c r="A800" s="36"/>
@@ -11753,6 +12563,7 @@
       <x:c r="J800" s="2"/>
       <x:c r="K800" s="2"/>
       <x:c r="L800" s="2"/>
+      <x:c r="M800"/>
     </x:row>
     <x:row r="801">
       <x:c r="A801" s="36"/>
@@ -11767,6 +12578,7 @@
       <x:c r="J801" s="2"/>
       <x:c r="K801" s="2"/>
       <x:c r="L801" s="2"/>
+      <x:c r="M801"/>
     </x:row>
     <x:row r="802">
       <x:c r="A802" s="36"/>
@@ -11781,6 +12593,7 @@
       <x:c r="J802" s="2"/>
       <x:c r="K802" s="2"/>
       <x:c r="L802" s="2"/>
+      <x:c r="M802"/>
     </x:row>
     <x:row r="803">
       <x:c r="A803" s="36"/>
@@ -11795,6 +12608,7 @@
       <x:c r="J803" s="2"/>
       <x:c r="K803" s="2"/>
       <x:c r="L803" s="2"/>
+      <x:c r="M803"/>
     </x:row>
     <x:row r="804">
       <x:c r="A804" s="36"/>
@@ -11809,6 +12623,7 @@
       <x:c r="J804" s="2"/>
       <x:c r="K804" s="2"/>
       <x:c r="L804" s="2"/>
+      <x:c r="M804"/>
     </x:row>
     <x:row r="805">
       <x:c r="A805" s="36"/>
@@ -11823,6 +12638,7 @@
       <x:c r="J805" s="2"/>
       <x:c r="K805" s="2"/>
       <x:c r="L805" s="2"/>
+      <x:c r="M805"/>
     </x:row>
     <x:row r="806">
       <x:c r="A806" s="36"/>
@@ -11837,6 +12653,7 @@
       <x:c r="J806" s="2"/>
       <x:c r="K806" s="2"/>
       <x:c r="L806" s="2"/>
+      <x:c r="M806"/>
     </x:row>
     <x:row r="807">
       <x:c r="A807" s="36"/>
@@ -11851,6 +12668,7 @@
       <x:c r="J807" s="2"/>
       <x:c r="K807" s="2"/>
       <x:c r="L807" s="2"/>
+      <x:c r="M807"/>
     </x:row>
     <x:row r="808">
       <x:c r="A808" s="36"/>
@@ -11865,6 +12683,7 @@
       <x:c r="J808" s="2"/>
       <x:c r="K808" s="2"/>
       <x:c r="L808" s="2"/>
+      <x:c r="M808"/>
     </x:row>
     <x:row r="809">
       <x:c r="A809" s="36"/>
@@ -11879,6 +12698,7 @@
       <x:c r="J809" s="2"/>
       <x:c r="K809" s="2"/>
       <x:c r="L809" s="2"/>
+      <x:c r="M809"/>
     </x:row>
     <x:row r="810">
       <x:c r="A810" s="36"/>
@@ -11893,6 +12713,7 @@
       <x:c r="J810" s="2"/>
       <x:c r="K810" s="2"/>
       <x:c r="L810" s="2"/>
+      <x:c r="M810"/>
     </x:row>
     <x:row r="811">
       <x:c r="A811" s="36"/>
@@ -11907,6 +12728,7 @@
       <x:c r="J811" s="2"/>
       <x:c r="K811" s="2"/>
       <x:c r="L811" s="2"/>
+      <x:c r="M811"/>
     </x:row>
     <x:row r="812">
       <x:c r="A812" s="36"/>
@@ -11921,6 +12743,7 @@
       <x:c r="J812" s="2"/>
       <x:c r="K812" s="2"/>
       <x:c r="L812" s="2"/>
+      <x:c r="M812"/>
     </x:row>
     <x:row r="813">
       <x:c r="A813" s="36"/>
@@ -11935,6 +12758,7 @@
       <x:c r="J813" s="2"/>
       <x:c r="K813" s="2"/>
       <x:c r="L813" s="2"/>
+      <x:c r="M813"/>
     </x:row>
     <x:row r="814">
       <x:c r="A814" s="36"/>
@@ -11949,6 +12773,7 @@
       <x:c r="J814" s="2"/>
       <x:c r="K814" s="2"/>
       <x:c r="L814" s="2"/>
+      <x:c r="M814"/>
     </x:row>
     <x:row r="815">
       <x:c r="A815" s="36"/>
@@ -11963,6 +12788,7 @@
       <x:c r="J815" s="2"/>
       <x:c r="K815" s="2"/>
       <x:c r="L815" s="2"/>
+      <x:c r="M815"/>
     </x:row>
     <x:row r="816">
       <x:c r="A816" s="36"/>
@@ -11977,6 +12803,7 @@
       <x:c r="J816" s="2"/>
       <x:c r="K816" s="2"/>
       <x:c r="L816" s="2"/>
+      <x:c r="M816"/>
     </x:row>
     <x:row r="817">
       <x:c r="A817" s="36"/>
@@ -11991,6 +12818,7 @@
       <x:c r="J817" s="2"/>
       <x:c r="K817" s="2"/>
       <x:c r="L817" s="2"/>
+      <x:c r="M817"/>
     </x:row>
     <x:row r="818">
       <x:c r="A818" s="36"/>
@@ -12005,6 +12833,7 @@
       <x:c r="J818" s="2"/>
       <x:c r="K818" s="2"/>
       <x:c r="L818" s="2"/>
+      <x:c r="M818"/>
     </x:row>
     <x:row r="819">
       <x:c r="A819" s="36"/>
@@ -12019,6 +12848,7 @@
       <x:c r="J819" s="2"/>
       <x:c r="K819" s="2"/>
       <x:c r="L819" s="2"/>
+      <x:c r="M819"/>
     </x:row>
     <x:row r="820">
       <x:c r="A820" s="36"/>
@@ -12033,6 +12863,7 @@
       <x:c r="J820" s="2"/>
       <x:c r="K820" s="2"/>
       <x:c r="L820" s="2"/>
+      <x:c r="M820"/>
     </x:row>
     <x:row r="821">
       <x:c r="A821" s="36"/>
@@ -12047,6 +12878,7 @@
       <x:c r="J821" s="2"/>
       <x:c r="K821" s="2"/>
       <x:c r="L821" s="2"/>
+      <x:c r="M821"/>
     </x:row>
     <x:row r="822">
       <x:c r="A822" s="36"/>
@@ -12061,6 +12893,7 @@
       <x:c r="J822" s="2"/>
       <x:c r="K822" s="2"/>
       <x:c r="L822" s="2"/>
+      <x:c r="M822"/>
     </x:row>
     <x:row r="823">
       <x:c r="A823" s="36"/>
@@ -12075,6 +12908,7 @@
       <x:c r="J823" s="2"/>
       <x:c r="K823" s="2"/>
       <x:c r="L823" s="2"/>
+      <x:c r="M823"/>
     </x:row>
     <x:row r="824">
       <x:c r="A824" s="36"/>
@@ -12089,6 +12923,7 @@
       <x:c r="J824" s="2"/>
       <x:c r="K824" s="2"/>
       <x:c r="L824" s="2"/>
+      <x:c r="M824"/>
     </x:row>
     <x:row r="825">
       <x:c r="A825" s="36"/>
@@ -12103,6 +12938,7 @@
       <x:c r="J825" s="2"/>
       <x:c r="K825" s="2"/>
       <x:c r="L825" s="2"/>
+      <x:c r="M825"/>
     </x:row>
     <x:row r="826">
       <x:c r="A826" s="36"/>
@@ -12117,6 +12953,7 @@
       <x:c r="J826" s="2"/>
       <x:c r="K826" s="2"/>
       <x:c r="L826" s="2"/>
+      <x:c r="M826"/>
     </x:row>
     <x:row r="827">
       <x:c r="A827" s="36"/>
@@ -12131,6 +12968,7 @@
       <x:c r="J827" s="2"/>
       <x:c r="K827" s="2"/>
       <x:c r="L827" s="2"/>
+      <x:c r="M827"/>
     </x:row>
     <x:row r="828">
       <x:c r="A828" s="36"/>
@@ -12145,6 +12983,7 @@
       <x:c r="J828" s="2"/>
       <x:c r="K828" s="2"/>
       <x:c r="L828" s="2"/>
+      <x:c r="M828"/>
     </x:row>
     <x:row r="829">
       <x:c r="A829" s="36"/>
@@ -12159,6 +12998,7 @@
       <x:c r="J829" s="2"/>
       <x:c r="K829" s="2"/>
       <x:c r="L829" s="2"/>
+      <x:c r="M829"/>
     </x:row>
     <x:row r="830">
       <x:c r="A830" s="36"/>
@@ -12173,6 +13013,7 @@
       <x:c r="J830" s="2"/>
       <x:c r="K830" s="2"/>
       <x:c r="L830" s="2"/>
+      <x:c r="M830"/>
     </x:row>
     <x:row r="831">
       <x:c r="A831" s="36"/>
@@ -12187,6 +13028,7 @@
       <x:c r="J831" s="2"/>
       <x:c r="K831" s="2"/>
       <x:c r="L831" s="2"/>
+      <x:c r="M831"/>
     </x:row>
     <x:row r="832">
       <x:c r="A832" s="36"/>
@@ -12201,6 +13043,7 @@
       <x:c r="J832" s="2"/>
       <x:c r="K832" s="2"/>
       <x:c r="L832" s="2"/>
+      <x:c r="M832"/>
     </x:row>
     <x:row r="833">
       <x:c r="A833" s="36"/>
@@ -12215,6 +13058,7 @@
       <x:c r="J833" s="2"/>
       <x:c r="K833" s="2"/>
       <x:c r="L833" s="2"/>
+      <x:c r="M833"/>
     </x:row>
     <x:row r="834">
       <x:c r="A834" s="36"/>
@@ -12229,6 +13073,7 @@
       <x:c r="J834" s="2"/>
       <x:c r="K834" s="2"/>
       <x:c r="L834" s="2"/>
+      <x:c r="M834"/>
     </x:row>
     <x:row r="835">
       <x:c r="A835" s="36"/>
@@ -12243,6 +13088,7 @@
       <x:c r="J835" s="2"/>
       <x:c r="K835" s="2"/>
       <x:c r="L835" s="2"/>
+      <x:c r="M835"/>
     </x:row>
     <x:row r="836">
       <x:c r="A836" s="36"/>
@@ -12257,6 +13103,7 @@
       <x:c r="J836" s="2"/>
       <x:c r="K836" s="2"/>
       <x:c r="L836" s="2"/>
+      <x:c r="M836"/>
     </x:row>
     <x:row r="837">
       <x:c r="A837" s="36"/>
@@ -12271,6 +13118,7 @@
       <x:c r="J837" s="2"/>
       <x:c r="K837" s="2"/>
       <x:c r="L837" s="2"/>
+      <x:c r="M837"/>
     </x:row>
     <x:row r="838">
       <x:c r="A838" s="36"/>
@@ -12285,6 +13133,7 @@
       <x:c r="J838" s="2"/>
       <x:c r="K838" s="2"/>
       <x:c r="L838" s="2"/>
+      <x:c r="M838"/>
     </x:row>
     <x:row r="839">
       <x:c r="A839" s="36"/>
@@ -12299,6 +13148,7 @@
       <x:c r="J839" s="2"/>
       <x:c r="K839" s="2"/>
       <x:c r="L839" s="2"/>
+      <x:c r="M839"/>
     </x:row>
     <x:row r="840">
       <x:c r="A840" s="36"/>
@@ -12313,6 +13163,7 @@
       <x:c r="J840" s="2"/>
       <x:c r="K840" s="2"/>
       <x:c r="L840" s="2"/>
+      <x:c r="M840"/>
     </x:row>
     <x:row r="841">
       <x:c r="A841" s="36"/>
@@ -12327,6 +13178,7 @@
       <x:c r="J841" s="2"/>
       <x:c r="K841" s="2"/>
       <x:c r="L841" s="2"/>
+      <x:c r="M841"/>
     </x:row>
     <x:row r="842">
       <x:c r="A842" s="36"/>
@@ -12341,6 +13193,7 @@
       <x:c r="J842" s="2"/>
       <x:c r="K842" s="2"/>
       <x:c r="L842" s="2"/>
+      <x:c r="M842"/>
     </x:row>
     <x:row r="843">
       <x:c r="A843" s="36"/>
@@ -12355,6 +13208,7 @@
       <x:c r="J843" s="2"/>
       <x:c r="K843" s="2"/>
       <x:c r="L843" s="2"/>
+      <x:c r="M843"/>
     </x:row>
     <x:row r="844">
       <x:c r="A844" s="36"/>
@@ -12369,6 +13223,7 @@
       <x:c r="J844" s="2"/>
       <x:c r="K844" s="2"/>
       <x:c r="L844" s="2"/>
+      <x:c r="M844"/>
     </x:row>
     <x:row r="845">
       <x:c r="A845" s="36"/>
@@ -12383,6 +13238,7 @@
       <x:c r="J845" s="2"/>
       <x:c r="K845" s="2"/>
       <x:c r="L845" s="2"/>
+      <x:c r="M845"/>
     </x:row>
     <x:row r="846">
       <x:c r="A846" s="36"/>
@@ -12397,6 +13253,7 @@
       <x:c r="J846" s="2"/>
       <x:c r="K846" s="2"/>
       <x:c r="L846" s="2"/>
+      <x:c r="M846"/>
     </x:row>
     <x:row r="847">
       <x:c r="A847" s="36"/>
@@ -12411,6 +13268,7 @@
       <x:c r="J847" s="2"/>
       <x:c r="K847" s="2"/>
       <x:c r="L847" s="2"/>
+      <x:c r="M847"/>
     </x:row>
     <x:row r="848">
       <x:c r="A848" s="36"/>
@@ -12425,6 +13283,7 @@
       <x:c r="J848" s="2"/>
       <x:c r="K848" s="2"/>
       <x:c r="L848" s="2"/>
+      <x:c r="M848"/>
     </x:row>
     <x:row r="849">
       <x:c r="A849" s="36"/>
@@ -12439,6 +13298,7 @@
       <x:c r="J849" s="2"/>
       <x:c r="K849" s="2"/>
       <x:c r="L849" s="2"/>
+      <x:c r="M849"/>
     </x:row>
     <x:row r="850">
       <x:c r="A850" s="36"/>
@@ -12453,6 +13313,7 @@
       <x:c r="J850" s="2"/>
       <x:c r="K850" s="2"/>
       <x:c r="L850" s="2"/>
+      <x:c r="M850"/>
     </x:row>
     <x:row r="851">
       <x:c r="A851" s="36"/>
@@ -12467,6 +13328,7 @@
       <x:c r="J851" s="2"/>
       <x:c r="K851" s="2"/>
       <x:c r="L851" s="2"/>
+      <x:c r="M851"/>
     </x:row>
     <x:row r="852">
       <x:c r="A852" s="36"/>
@@ -12481,6 +13343,7 @@
       <x:c r="J852" s="2"/>
       <x:c r="K852" s="2"/>
       <x:c r="L852" s="2"/>
+      <x:c r="M852"/>
     </x:row>
     <x:row r="853">
       <x:c r="A853" s="36"/>
@@ -12495,6 +13358,7 @@
       <x:c r="J853" s="2"/>
       <x:c r="K853" s="2"/>
       <x:c r="L853" s="2"/>
+      <x:c r="M853"/>
     </x:row>
     <x:row r="854">
       <x:c r="A854" s="36"/>
@@ -12509,6 +13373,7 @@
       <x:c r="J854" s="2"/>
       <x:c r="K854" s="2"/>
       <x:c r="L854" s="2"/>
+      <x:c r="M854"/>
     </x:row>
     <x:row r="855">
       <x:c r="A855" s="36"/>
@@ -12523,6 +13388,7 @@
       <x:c r="J855" s="2"/>
       <x:c r="K855" s="2"/>
       <x:c r="L855" s="2"/>
+      <x:c r="M855"/>
     </x:row>
     <x:row r="856">
       <x:c r="A856" s="36"/>
@@ -12537,6 +13403,7 @@
       <x:c r="J856" s="2"/>
       <x:c r="K856" s="2"/>
       <x:c r="L856" s="2"/>
+      <x:c r="M856"/>
     </x:row>
     <x:row r="857">
       <x:c r="A857" s="36"/>
@@ -12551,6 +13418,7 @@
       <x:c r="J857" s="2"/>
       <x:c r="K857" s="2"/>
       <x:c r="L857" s="2"/>
+      <x:c r="M857"/>
     </x:row>
     <x:row r="858">
       <x:c r="A858" s="36"/>
@@ -12565,6 +13433,7 @@
       <x:c r="J858" s="2"/>
       <x:c r="K858" s="2"/>
       <x:c r="L858" s="2"/>
+      <x:c r="M858"/>
     </x:row>
     <x:row r="859">
       <x:c r="A859" s="36"/>
@@ -12579,6 +13448,7 @@
       <x:c r="J859" s="2"/>
       <x:c r="K859" s="2"/>
       <x:c r="L859" s="2"/>
+      <x:c r="M859"/>
     </x:row>
     <x:row r="860">
       <x:c r="A860" s="36"/>
@@ -12593,6 +13463,7 @@
       <x:c r="J860" s="2"/>
       <x:c r="K860" s="2"/>
       <x:c r="L860" s="2"/>
+      <x:c r="M860"/>
     </x:row>
     <x:row r="861">
       <x:c r="A861" s="36"/>
@@ -12607,6 +13478,7 @@
       <x:c r="J861" s="2"/>
       <x:c r="K861" s="2"/>
       <x:c r="L861" s="2"/>
+      <x:c r="M861"/>
     </x:row>
     <x:row r="862">
       <x:c r="A862" s="36"/>
@@ -12621,6 +13493,7 @@
       <x:c r="J862" s="2"/>
       <x:c r="K862" s="2"/>
       <x:c r="L862" s="2"/>
+      <x:c r="M862"/>
     </x:row>
     <x:row r="863">
       <x:c r="A863" s="36"/>
@@ -12635,6 +13508,7 @@
       <x:c r="J863" s="2"/>
       <x:c r="K863" s="2"/>
       <x:c r="L863" s="2"/>
+      <x:c r="M863"/>
     </x:row>
     <x:row r="864">
       <x:c r="A864" s="36"/>
@@ -12649,6 +13523,7 @@
       <x:c r="J864" s="2"/>
       <x:c r="K864" s="2"/>
       <x:c r="L864" s="2"/>
+      <x:c r="M864"/>
     </x:row>
     <x:row r="865">
       <x:c r="A865" s="36"/>
@@ -12663,6 +13538,7 @@
       <x:c r="J865" s="2"/>
       <x:c r="K865" s="2"/>
       <x:c r="L865" s="2"/>
+      <x:c r="M865"/>
     </x:row>
     <x:row r="866">
       <x:c r="A866" s="36"/>
@@ -12677,6 +13553,7 @@
       <x:c r="J866" s="2"/>
       <x:c r="K866" s="2"/>
       <x:c r="L866" s="2"/>
+      <x:c r="M866"/>
     </x:row>
     <x:row r="867">
       <x:c r="A867" s="36"/>
@@ -12691,6 +13568,7 @@
       <x:c r="J867" s="2"/>
       <x:c r="K867" s="2"/>
       <x:c r="L867" s="2"/>
+      <x:c r="M867"/>
     </x:row>
     <x:row r="868">
       <x:c r="A868" s="36"/>
@@ -12705,6 +13583,7 @@
       <x:c r="J868" s="2"/>
       <x:c r="K868" s="2"/>
       <x:c r="L868" s="2"/>
+      <x:c r="M868"/>
     </x:row>
     <x:row r="869">
       <x:c r="A869" s="36"/>
@@ -12719,6 +13598,7 @@
       <x:c r="J869" s="2"/>
       <x:c r="K869" s="2"/>
       <x:c r="L869" s="2"/>
+      <x:c r="M869"/>
     </x:row>
     <x:row r="870">
       <x:c r="A870" s="36"/>
@@ -12733,6 +13613,7 @@
       <x:c r="J870" s="2"/>
       <x:c r="K870" s="2"/>
       <x:c r="L870" s="2"/>
+      <x:c r="M870"/>
     </x:row>
     <x:row r="871">
       <x:c r="A871" s="36"/>
@@ -12747,6 +13628,7 @@
       <x:c r="J871" s="2"/>
       <x:c r="K871" s="2"/>
       <x:c r="L871" s="2"/>
+      <x:c r="M871"/>
     </x:row>
     <x:row r="872">
       <x:c r="A872" s="36"/>
@@ -12761,6 +13643,7 @@
       <x:c r="J872" s="2"/>
       <x:c r="K872" s="2"/>
       <x:c r="L872" s="2"/>
+      <x:c r="M872"/>
     </x:row>
     <x:row r="873">
       <x:c r="A873" s="36"/>
@@ -12775,6 +13658,7 @@
       <x:c r="J873" s="2"/>
       <x:c r="K873" s="2"/>
       <x:c r="L873" s="2"/>
+      <x:c r="M873"/>
     </x:row>
     <x:row r="874">
       <x:c r="A874" s="36"/>
@@ -12789,6 +13673,7 @@
       <x:c r="J874" s="2"/>
       <x:c r="K874" s="2"/>
       <x:c r="L874" s="2"/>
+      <x:c r="M874"/>
     </x:row>
     <x:row r="875">
       <x:c r="A875" s="36"/>
@@ -12803,6 +13688,7 @@
       <x:c r="J875" s="2"/>
       <x:c r="K875" s="2"/>
       <x:c r="L875" s="2"/>
+      <x:c r="M875"/>
     </x:row>
     <x:row r="876">
       <x:c r="A876" s="36"/>
@@ -12817,6 +13703,7 @@
       <x:c r="J876" s="2"/>
       <x:c r="K876" s="2"/>
       <x:c r="L876" s="2"/>
+      <x:c r="M876"/>
     </x:row>
     <x:row r="877">
       <x:c r="A877" s="36"/>
@@ -12831,6 +13718,7 @@
       <x:c r="J877" s="2"/>
       <x:c r="K877" s="2"/>
       <x:c r="L877" s="2"/>
+      <x:c r="M877"/>
     </x:row>
     <x:row r="878">
       <x:c r="A878" s="36"/>
@@ -12845,6 +13733,7 @@
       <x:c r="J878" s="2"/>
       <x:c r="K878" s="2"/>
       <x:c r="L878" s="2"/>
+      <x:c r="M878"/>
     </x:row>
     <x:row r="879">
       <x:c r="A879" s="36"/>
@@ -12859,6 +13748,7 @@
       <x:c r="J879" s="2"/>
       <x:c r="K879" s="2"/>
       <x:c r="L879" s="2"/>
+      <x:c r="M879"/>
     </x:row>
     <x:row r="880">
       <x:c r="A880" s="36"/>
@@ -12873,6 +13763,7 @@
       <x:c r="J880" s="2"/>
       <x:c r="K880" s="2"/>
       <x:c r="L880" s="2"/>
+      <x:c r="M880"/>
     </x:row>
     <x:row r="881">
       <x:c r="A881" s="36"/>
@@ -12887,6 +13778,7 @@
       <x:c r="J881" s="2"/>
       <x:c r="K881" s="2"/>
       <x:c r="L881" s="2"/>
+      <x:c r="M881"/>
     </x:row>
     <x:row r="882">
       <x:c r="A882" s="36"/>
@@ -12901,6 +13793,7 @@
       <x:c r="J882" s="2"/>
       <x:c r="K882" s="2"/>
       <x:c r="L882" s="2"/>
+      <x:c r="M882"/>
     </x:row>
     <x:row r="883">
       <x:c r="A883" s="36"/>
@@ -12915,6 +13808,7 @@
       <x:c r="J883" s="2"/>
       <x:c r="K883" s="2"/>
       <x:c r="L883" s="2"/>
+      <x:c r="M883"/>
     </x:row>
     <x:row r="884">
       <x:c r="A884" s="36"/>
@@ -12929,6 +13823,7 @@
       <x:c r="J884" s="2"/>
       <x:c r="K884" s="2"/>
       <x:c r="L884" s="2"/>
+      <x:c r="M884"/>
     </x:row>
     <x:row r="885">
       <x:c r="A885" s="36"/>
@@ -12943,6 +13838,7 @@
       <x:c r="J885" s="2"/>
       <x:c r="K885" s="2"/>
       <x:c r="L885" s="2"/>
+      <x:c r="M885"/>
     </x:row>
     <x:row r="886">
       <x:c r="A886" s="36"/>
@@ -12957,6 +13853,7 @@
       <x:c r="J886" s="2"/>
       <x:c r="K886" s="2"/>
       <x:c r="L886" s="2"/>
+      <x:c r="M886"/>
     </x:row>
     <x:row r="887">
       <x:c r="A887" s="36"/>
@@ -12971,6 +13868,7 @@
       <x:c r="J887" s="2"/>
       <x:c r="K887" s="2"/>
       <x:c r="L887" s="2"/>
+      <x:c r="M887"/>
     </x:row>
     <x:row r="888">
       <x:c r="A888" s="36"/>
@@ -12985,6 +13883,7 @@
       <x:c r="J888" s="2"/>
       <x:c r="K888" s="2"/>
       <x:c r="L888" s="2"/>
+      <x:c r="M888"/>
     </x:row>
     <x:row r="889">
       <x:c r="A889" s="36"/>
@@ -12999,6 +13898,7 @@
       <x:c r="J889" s="2"/>
       <x:c r="K889" s="2"/>
       <x:c r="L889" s="2"/>
+      <x:c r="M889"/>
     </x:row>
     <x:row r="890">
       <x:c r="A890" s="36"/>
@@ -13013,6 +13913,7 @@
       <x:c r="J890" s="2"/>
       <x:c r="K890" s="2"/>
       <x:c r="L890" s="2"/>
+      <x:c r="M890"/>
     </x:row>
     <x:row r="891">
       <x:c r="A891" s="36"/>
@@ -13027,6 +13928,7 @@
       <x:c r="J891" s="2"/>
       <x:c r="K891" s="2"/>
       <x:c r="L891" s="2"/>
+      <x:c r="M891"/>
     </x:row>
     <x:row r="892">
       <x:c r="A892" s="36"/>
@@ -13041,6 +13943,7 @@
       <x:c r="J892" s="2"/>
       <x:c r="K892" s="2"/>
       <x:c r="L892" s="2"/>
+      <x:c r="M892"/>
     </x:row>
     <x:row r="893">
       <x:c r="A893" s="36"/>
@@ -13055,6 +13958,7 @@
       <x:c r="J893" s="2"/>
       <x:c r="K893" s="2"/>
       <x:c r="L893" s="2"/>
+      <x:c r="M893"/>
     </x:row>
     <x:row r="894">
       <x:c r="A894" s="36"/>
@@ -13069,6 +13973,7 @@
       <x:c r="J894" s="2"/>
       <x:c r="K894" s="2"/>
       <x:c r="L894" s="2"/>
+      <x:c r="M894"/>
     </x:row>
     <x:row r="895">
       <x:c r="A895" s="36"/>
@@ -13083,6 +13988,7 @@
       <x:c r="J895" s="2"/>
       <x:c r="K895" s="2"/>
       <x:c r="L895" s="2"/>
+      <x:c r="M895"/>
     </x:row>
     <x:row r="896">
       <x:c r="A896" s="36"/>
@@ -13097,6 +14003,7 @@
       <x:c r="J896" s="2"/>
       <x:c r="K896" s="2"/>
       <x:c r="L896" s="2"/>
+      <x:c r="M896"/>
     </x:row>
     <x:row r="897">
       <x:c r="A897" s="36"/>
@@ -13111,6 +14018,7 @@
       <x:c r="J897" s="2"/>
       <x:c r="K897" s="2"/>
       <x:c r="L897" s="2"/>
+      <x:c r="M897"/>
     </x:row>
     <x:row r="898">
       <x:c r="A898" s="36"/>
@@ -13125,6 +14033,7 @@
       <x:c r="J898" s="2"/>
       <x:c r="K898" s="2"/>
       <x:c r="L898" s="2"/>
+      <x:c r="M898"/>
     </x:row>
     <x:row r="899">
       <x:c r="A899" s="36"/>
@@ -13139,6 +14048,7 @@
       <x:c r="J899" s="2"/>
       <x:c r="K899" s="2"/>
       <x:c r="L899" s="2"/>
+      <x:c r="M899"/>
     </x:row>
     <x:row r="900">
       <x:c r="A900" s="36"/>
@@ -13153,6 +14063,7 @@
       <x:c r="J900" s="2"/>
       <x:c r="K900" s="2"/>
       <x:c r="L900" s="2"/>
+      <x:c r="M900"/>
     </x:row>
     <x:row r="901">
       <x:c r="A901" s="36"/>
@@ -13167,6 +14078,7 @@
       <x:c r="J901" s="2"/>
       <x:c r="K901" s="2"/>
       <x:c r="L901" s="2"/>
+      <x:c r="M901"/>
     </x:row>
     <x:row r="902">
       <x:c r="A902" s="36"/>
@@ -13181,6 +14093,7 @@
       <x:c r="J902" s="2"/>
       <x:c r="K902" s="2"/>
       <x:c r="L902" s="2"/>
+      <x:c r="M902"/>
     </x:row>
     <x:row r="903">
       <x:c r="A903" s="36"/>
@@ -13195,6 +14108,7 @@
       <x:c r="J903" s="2"/>
       <x:c r="K903" s="2"/>
       <x:c r="L903" s="2"/>
+      <x:c r="M903"/>
     </x:row>
     <x:row r="904">
       <x:c r="A904" s="36"/>
@@ -13209,6 +14123,7 @@
       <x:c r="J904" s="2"/>
       <x:c r="K904" s="2"/>
       <x:c r="L904" s="2"/>
+      <x:c r="M904"/>
     </x:row>
     <x:row r="905">
       <x:c r="A905" s="36"/>
@@ -13223,6 +14138,7 @@
       <x:c r="J905" s="2"/>
       <x:c r="K905" s="2"/>
       <x:c r="L905" s="2"/>
+      <x:c r="M905"/>
     </x:row>
     <x:row r="906">
       <x:c r="A906" s="36"/>
@@ -13237,6 +14153,7 @@
       <x:c r="J906" s="2"/>
       <x:c r="K906" s="2"/>
       <x:c r="L906" s="2"/>
+      <x:c r="M906"/>
     </x:row>
     <x:row r="907">
       <x:c r="A907" s="36"/>
@@ -13251,6 +14168,7 @@
       <x:c r="J907" s="2"/>
       <x:c r="K907" s="2"/>
       <x:c r="L907" s="2"/>
+      <x:c r="M907"/>
     </x:row>
     <x:row r="908">
       <x:c r="A908" s="36"/>
@@ -13265,6 +14183,7 @@
       <x:c r="J908" s="2"/>
       <x:c r="K908" s="2"/>
       <x:c r="L908" s="2"/>
+      <x:c r="M908"/>
     </x:row>
     <x:row r="909">
       <x:c r="A909" s="36"/>
@@ -13279,6 +14198,7 @@
       <x:c r="J909" s="2"/>
       <x:c r="K909" s="2"/>
       <x:c r="L909" s="2"/>
+      <x:c r="M909"/>
     </x:row>
     <x:row r="910">
       <x:c r="A910" s="36"/>
@@ -13293,6 +14213,7 @@
       <x:c r="J910" s="2"/>
       <x:c r="K910" s="2"/>
       <x:c r="L910" s="2"/>
+      <x:c r="M910"/>
     </x:row>
     <x:row r="911">
       <x:c r="A911" s="36"/>
@@ -13307,6 +14228,7 @@
       <x:c r="J911" s="2"/>
       <x:c r="K911" s="2"/>
       <x:c r="L911" s="2"/>
+      <x:c r="M911"/>
     </x:row>
     <x:row r="912">
       <x:c r="A912" s="36"/>
@@ -13321,6 +14243,7 @@
       <x:c r="J912" s="2"/>
       <x:c r="K912" s="2"/>
       <x:c r="L912" s="2"/>
+      <x:c r="M912"/>
     </x:row>
     <x:row r="913">
       <x:c r="A913" s="36"/>
@@ -13335,6 +14258,7 @@
       <x:c r="J913" s="2"/>
       <x:c r="K913" s="2"/>
       <x:c r="L913" s="2"/>
+      <x:c r="M913"/>
     </x:row>
     <x:row r="914">
       <x:c r="A914" s="36"/>
@@ -13349,6 +14273,7 @@
       <x:c r="J914" s="2"/>
       <x:c r="K914" s="2"/>
       <x:c r="L914" s="2"/>
+      <x:c r="M914"/>
     </x:row>
     <x:row r="915">
       <x:c r="A915" s="36"/>
@@ -13363,6 +14288,7 @@
       <x:c r="J915" s="2"/>
       <x:c r="K915" s="2"/>
       <x:c r="L915" s="2"/>
+      <x:c r="M915"/>
     </x:row>
     <x:row r="916">
       <x:c r="A916" s="36"/>
@@ -13377,6 +14303,7 @@
       <x:c r="J916" s="2"/>
       <x:c r="K916" s="2"/>
       <x:c r="L916" s="2"/>
+      <x:c r="M916"/>
     </x:row>
     <x:row r="917">
       <x:c r="A917" s="36"/>
@@ -13391,6 +14318,7 @@
       <x:c r="J917" s="2"/>
       <x:c r="K917" s="2"/>
       <x:c r="L917" s="2"/>
+      <x:c r="M917"/>
     </x:row>
     <x:row r="918">
       <x:c r="A918" s="36"/>
@@ -13405,6 +14333,7 @@
       <x:c r="J918" s="2"/>
       <x:c r="K918" s="2"/>
       <x:c r="L918" s="2"/>
+      <x:c r="M918"/>
     </x:row>
     <x:row r="919">
       <x:c r="A919" s="36"/>
@@ -13419,6 +14348,7 @@
       <x:c r="J919" s="2"/>
       <x:c r="K919" s="2"/>
       <x:c r="L919" s="2"/>
+      <x:c r="M919"/>
     </x:row>
     <x:row r="920">
       <x:c r="A920" s="36"/>
@@ -13433,6 +14363,7 @@
       <x:c r="J920" s="2"/>
       <x:c r="K920" s="2"/>
       <x:c r="L920" s="2"/>
+      <x:c r="M920"/>
     </x:row>
     <x:row r="921">
       <x:c r="A921" s="36"/>
@@ -13447,6 +14378,7 @@
       <x:c r="J921" s="2"/>
       <x:c r="K921" s="2"/>
       <x:c r="L921" s="2"/>
+      <x:c r="M921"/>
     </x:row>
     <x:row r="922">
       <x:c r="A922" s="36"/>
@@ -13461,6 +14393,7 @@
       <x:c r="J922" s="2"/>
       <x:c r="K922" s="2"/>
       <x:c r="L922" s="2"/>
+      <x:c r="M922"/>
     </x:row>
     <x:row r="923">
       <x:c r="A923" s="36"/>
@@ -13475,6 +14408,7 @@
       <x:c r="J923" s="2"/>
       <x:c r="K923" s="2"/>
       <x:c r="L923" s="2"/>
+      <x:c r="M923"/>
     </x:row>
     <x:row r="924">
       <x:c r="A924" s="36"/>
@@ -13489,6 +14423,7 @@
       <x:c r="J924" s="2"/>
       <x:c r="K924" s="2"/>
       <x:c r="L924" s="2"/>
+      <x:c r="M924"/>
     </x:row>
     <x:row r="925">
       <x:c r="A925" s="36"/>
@@ -13503,6 +14438,7 @@
       <x:c r="J925" s="2"/>
       <x:c r="K925" s="2"/>
       <x:c r="L925" s="2"/>
+      <x:c r="M925"/>
     </x:row>
     <x:row r="926">
       <x:c r="A926" s="36"/>
@@ -13517,6 +14453,7 @@
       <x:c r="J926" s="2"/>
       <x:c r="K926" s="2"/>
       <x:c r="L926" s="2"/>
+      <x:c r="M926"/>
     </x:row>
     <x:row r="927">
       <x:c r="A927" s="36"/>
@@ -13531,6 +14468,7 @@
       <x:c r="J927" s="2"/>
       <x:c r="K927" s="2"/>
       <x:c r="L927" s="2"/>
+      <x:c r="M927"/>
     </x:row>
     <x:row r="928">
       <x:c r="A928" s="36"/>
@@ -13545,6 +14483,7 @@
       <x:c r="J928" s="2"/>
       <x:c r="K928" s="2"/>
       <x:c r="L928" s="2"/>
+      <x:c r="M928"/>
     </x:row>
     <x:row r="929">
       <x:c r="A929" s="36"/>
@@ -13559,6 +14498,7 @@
       <x:c r="J929" s="2"/>
       <x:c r="K929" s="2"/>
       <x:c r="L929" s="2"/>
+      <x:c r="M929"/>
     </x:row>
     <x:row r="930">
       <x:c r="A930" s="36"/>
@@ -13573,6 +14513,7 @@
       <x:c r="J930" s="2"/>
       <x:c r="K930" s="2"/>
       <x:c r="L930" s="2"/>
+      <x:c r="M930"/>
     </x:row>
     <x:row r="931">
       <x:c r="A931" s="36"/>
@@ -13587,6 +14528,7 @@
       <x:c r="J931" s="2"/>
       <x:c r="K931" s="2"/>
       <x:c r="L931" s="2"/>
+      <x:c r="M931"/>
     </x:row>
     <x:row r="932">
       <x:c r="A932" s="36"/>
@@ -13601,6 +14543,7 @@
       <x:c r="J932" s="2"/>
       <x:c r="K932" s="2"/>
       <x:c r="L932" s="2"/>
+      <x:c r="M932"/>
     </x:row>
     <x:row r="933">
       <x:c r="A933" s="36"/>
@@ -13615,6 +14558,7 @@
       <x:c r="J933" s="2"/>
       <x:c r="K933" s="2"/>
       <x:c r="L933" s="2"/>
+      <x:c r="M933"/>
     </x:row>
     <x:row r="934">
       <x:c r="A934" s="36"/>
@@ -13629,6 +14573,7 @@
       <x:c r="J934" s="2"/>
       <x:c r="K934" s="2"/>
       <x:c r="L934" s="2"/>
+      <x:c r="M934"/>
     </x:row>
     <x:row r="935">
       <x:c r="A935" s="36"/>
@@ -13643,6 +14588,7 @@
       <x:c r="J935" s="2"/>
       <x:c r="K935" s="2"/>
       <x:c r="L935" s="2"/>
+      <x:c r="M935"/>
     </x:row>
     <x:row r="936">
       <x:c r="A936" s="36"/>
@@ -13657,6 +14603,7 @@
       <x:c r="J936" s="2"/>
       <x:c r="K936" s="2"/>
       <x:c r="L936" s="2"/>
+      <x:c r="M936"/>
     </x:row>
     <x:row r="937">
       <x:c r="A937" s="36"/>
@@ -13671,6 +14618,7 @@
       <x:c r="J937" s="2"/>
       <x:c r="K937" s="2"/>
       <x:c r="L937" s="2"/>
+      <x:c r="M937"/>
     </x:row>
     <x:row r="938">
       <x:c r="A938" s="36"/>
@@ -13685,6 +14633,7 @@
       <x:c r="J938" s="2"/>
       <x:c r="K938" s="2"/>
       <x:c r="L938" s="2"/>
+      <x:c r="M938"/>
     </x:row>
     <x:row r="939">
       <x:c r="A939" s="36"/>
@@ -13699,6 +14648,7 @@
       <x:c r="J939" s="2"/>
       <x:c r="K939" s="2"/>
       <x:c r="L939" s="2"/>
+      <x:c r="M939"/>
     </x:row>
     <x:row r="940">
       <x:c r="A940" s="36"/>
@@ -13713,6 +14663,7 @@
       <x:c r="J940" s="2"/>
       <x:c r="K940" s="2"/>
       <x:c r="L940" s="2"/>
+      <x:c r="M940"/>
     </x:row>
     <x:row r="941">
       <x:c r="A941" s="36"/>
@@ -13727,6 +14678,7 @@
       <x:c r="J941" s="2"/>
       <x:c r="K941" s="2"/>
       <x:c r="L941" s="2"/>
+      <x:c r="M941"/>
     </x:row>
     <x:row r="942">
       <x:c r="A942" s="36"/>
@@ -13741,6 +14693,7 @@
       <x:c r="J942" s="2"/>
       <x:c r="K942" s="2"/>
       <x:c r="L942" s="2"/>
+      <x:c r="M942"/>
     </x:row>
     <x:row r="943">
       <x:c r="A943" s="36"/>
@@ -13755,6 +14708,7 @@
       <x:c r="J943" s="2"/>
       <x:c r="K943" s="2"/>
       <x:c r="L943" s="2"/>
+      <x:c r="M943"/>
     </x:row>
     <x:row r="944">
       <x:c r="A944" s="36"/>
@@ -13769,6 +14723,7 @@
       <x:c r="J944" s="2"/>
       <x:c r="K944" s="2"/>
       <x:c r="L944" s="2"/>
+      <x:c r="M944"/>
     </x:row>
     <x:row r="945">
       <x:c r="A945" s="36"/>
@@ -13783,6 +14738,7 @@
       <x:c r="J945" s="2"/>
       <x:c r="K945" s="2"/>
       <x:c r="L945" s="2"/>
+      <x:c r="M945"/>
     </x:row>
     <x:row r="946">
       <x:c r="A946" s="36"/>
@@ -13797,6 +14753,7 @@
       <x:c r="J946" s="2"/>
       <x:c r="K946" s="2"/>
       <x:c r="L946" s="2"/>
+      <x:c r="M946"/>
     </x:row>
     <x:row r="947">
       <x:c r="A947" s="36"/>
@@ -13811,6 +14768,7 @@
       <x:c r="J947" s="2"/>
       <x:c r="K947" s="2"/>
       <x:c r="L947" s="2"/>
+      <x:c r="M947"/>
     </x:row>
     <x:row r="948">
       <x:c r="A948" s="36"/>
@@ -13825,6 +14783,7 @@
       <x:c r="J948" s="2"/>
       <x:c r="K948" s="2"/>
       <x:c r="L948" s="2"/>
+      <x:c r="M948"/>
     </x:row>
     <x:row r="949">
       <x:c r="A949" s="36"/>
@@ -13839,6 +14798,7 @@
       <x:c r="J949" s="2"/>
       <x:c r="K949" s="2"/>
       <x:c r="L949" s="2"/>
+      <x:c r="M949"/>
     </x:row>
     <x:row r="950">
       <x:c r="A950" s="36"/>
@@ -13853,6 +14813,7 @@
       <x:c r="J950" s="2"/>
       <x:c r="K950" s="2"/>
       <x:c r="L950" s="2"/>
+      <x:c r="M950"/>
     </x:row>
     <x:row r="951">
       <x:c r="A951" s="36"/>
@@ -13867,6 +14828,7 @@
       <x:c r="J951" s="2"/>
       <x:c r="K951" s="2"/>
       <x:c r="L951" s="2"/>
+      <x:c r="M951"/>
     </x:row>
     <x:row r="952">
       <x:c r="A952" s="36"/>
@@ -13881,6 +14843,7 @@
       <x:c r="J952" s="2"/>
       <x:c r="K952" s="2"/>
       <x:c r="L952" s="2"/>
+      <x:c r="M952"/>
     </x:row>
     <x:row r="953">
       <x:c r="A953" s="36"/>
@@ -13895,6 +14858,7 @@
       <x:c r="J953" s="2"/>
       <x:c r="K953" s="2"/>
       <x:c r="L953" s="2"/>
+      <x:c r="M953"/>
     </x:row>
     <x:row r="954">
       <x:c r="A954" s="36"/>
@@ -13909,6 +14873,7 @@
       <x:c r="J954" s="2"/>
       <x:c r="K954" s="2"/>
       <x:c r="L954" s="2"/>
+      <x:c r="M954"/>
     </x:row>
     <x:row r="955">
       <x:c r="A955" s="36"/>
@@ -13923,6 +14888,7 @@
       <x:c r="J955" s="2"/>
       <x:c r="K955" s="2"/>
       <x:c r="L955" s="2"/>
+      <x:c r="M955"/>
     </x:row>
     <x:row r="956">
       <x:c r="A956" s="36"/>
@@ -13937,6 +14903,7 @@
       <x:c r="J956" s="2"/>
       <x:c r="K956" s="2"/>
       <x:c r="L956" s="2"/>
+      <x:c r="M956"/>
     </x:row>
     <x:row r="957">
       <x:c r="A957" s="36"/>
@@ -13951,6 +14918,7 @@
       <x:c r="J957" s="2"/>
       <x:c r="K957" s="2"/>
       <x:c r="L957" s="2"/>
+      <x:c r="M957"/>
     </x:row>
     <x:row r="958">
       <x:c r="A958" s="36"/>
@@ -13965,6 +14933,7 @@
       <x:c r="J958" s="2"/>
       <x:c r="K958" s="2"/>
       <x:c r="L958" s="2"/>
+      <x:c r="M958"/>
     </x:row>
     <x:row r="959">
       <x:c r="A959" s="36"/>
@@ -13979,6 +14948,7 @@
       <x:c r="J959" s="2"/>
       <x:c r="K959" s="2"/>
       <x:c r="L959" s="2"/>
+      <x:c r="M959"/>
     </x:row>
     <x:row r="960">
       <x:c r="A960" s="36"/>
@@ -13993,6 +14963,7 @@
       <x:c r="J960" s="2"/>
       <x:c r="K960" s="2"/>
       <x:c r="L960" s="2"/>
+      <x:c r="M960"/>
     </x:row>
     <x:row r="961">
       <x:c r="A961" s="36"/>
@@ -14007,6 +14978,7 @@
       <x:c r="J961" s="2"/>
       <x:c r="K961" s="2"/>
       <x:c r="L961" s="2"/>
+      <x:c r="M961"/>
     </x:row>
     <x:row r="962">
       <x:c r="A962" s="36"/>
@@ -14021,6 +14993,7 @@
       <x:c r="J962" s="2"/>
       <x:c r="K962" s="2"/>
       <x:c r="L962" s="2"/>
+      <x:c r="M962"/>
     </x:row>
     <x:row r="963">
       <x:c r="A963" s="36"/>
@@ -14035,6 +15008,7 @@
       <x:c r="J963" s="2"/>
       <x:c r="K963" s="2"/>
       <x:c r="L963" s="2"/>
+      <x:c r="M963"/>
     </x:row>
     <x:row r="964">
       <x:c r="A964" s="36"/>
@@ -14049,6 +15023,7 @@
       <x:c r="J964" s="2"/>
       <x:c r="K964" s="2"/>
       <x:c r="L964" s="2"/>
+      <x:c r="M964"/>
     </x:row>
     <x:row r="965">
       <x:c r="A965" s="36"/>
@@ -14063,6 +15038,7 @@
       <x:c r="J965" s="2"/>
       <x:c r="K965" s="2"/>
       <x:c r="L965" s="2"/>
+      <x:c r="M965"/>
     </x:row>
     <x:row r="966">
       <x:c r="A966" s="36"/>
@@ -14077,6 +15053,7 @@
       <x:c r="J966" s="2"/>
       <x:c r="K966" s="2"/>
       <x:c r="L966" s="2"/>
+      <x:c r="M966"/>
     </x:row>
     <x:row r="967">
       <x:c r="A967" s="36"/>
@@ -14091,6 +15068,7 @@
       <x:c r="J967" s="2"/>
       <x:c r="K967" s="2"/>
       <x:c r="L967" s="2"/>
+      <x:c r="M967"/>
     </x:row>
     <x:row r="968">
       <x:c r="A968" s="36"/>
@@ -14105,6 +15083,7 @@
       <x:c r="J968" s="2"/>
       <x:c r="K968" s="2"/>
       <x:c r="L968" s="2"/>
+      <x:c r="M968"/>
     </x:row>
     <x:row r="969">
       <x:c r="A969" s="36"/>
@@ -14119,6 +15098,7 @@
       <x:c r="J969" s="2"/>
       <x:c r="K969" s="2"/>
       <x:c r="L969" s="2"/>
+      <x:c r="M969"/>
     </x:row>
     <x:row r="970">
       <x:c r="A970" s="36"/>
@@ -14133,6 +15113,7 @@
       <x:c r="J970" s="2"/>
       <x:c r="K970" s="2"/>
       <x:c r="L970" s="2"/>
+      <x:c r="M970"/>
     </x:row>
     <x:row r="971">
       <x:c r="A971" s="36"/>
@@ -14147,6 +15128,7 @@
       <x:c r="J971" s="2"/>
       <x:c r="K971" s="2"/>
       <x:c r="L971" s="2"/>
+      <x:c r="M971"/>
     </x:row>
     <x:row r="972">
       <x:c r="A972" s="36"/>
@@ -14161,6 +15143,7 @@
       <x:c r="J972" s="2"/>
       <x:c r="K972" s="2"/>
       <x:c r="L972" s="2"/>
+      <x:c r="M972"/>
     </x:row>
     <x:row r="973">
       <x:c r="A973" s="36"/>
@@ -14175,6 +15158,7 @@
       <x:c r="J973" s="2"/>
       <x:c r="K973" s="2"/>
       <x:c r="L973" s="2"/>
+      <x:c r="M973"/>
     </x:row>
     <x:row r="974">
       <x:c r="A974" s="36"/>
@@ -14189,6 +15173,7 @@
       <x:c r="J974" s="2"/>
       <x:c r="K974" s="2"/>
       <x:c r="L974" s="2"/>
+      <x:c r="M974"/>
     </x:row>
     <x:row r="975">
       <x:c r="A975" s="36"/>
@@ -14203,6 +15188,7 @@
       <x:c r="J975" s="2"/>
       <x:c r="K975" s="2"/>
       <x:c r="L975" s="2"/>
+      <x:c r="M975"/>
     </x:row>
     <x:row r="976">
       <x:c r="A976" s="36"/>
@@ -14217,6 +15203,7 @@
       <x:c r="J976" s="2"/>
       <x:c r="K976" s="2"/>
       <x:c r="L976" s="2"/>
+      <x:c r="M976"/>
     </x:row>
     <x:row r="977">
       <x:c r="A977" s="36"/>
@@ -14231,6 +15218,7 @@
       <x:c r="J977" s="2"/>
       <x:c r="K977" s="2"/>
       <x:c r="L977" s="2"/>
+      <x:c r="M977"/>
     </x:row>
     <x:row r="978">
       <x:c r="A978" s="36"/>
@@ -14245,6 +15233,7 @@
       <x:c r="J978" s="2"/>
       <x:c r="K978" s="2"/>
       <x:c r="L978" s="2"/>
+      <x:c r="M978"/>
     </x:row>
     <x:row r="979">
       <x:c r="A979" s="36"/>
@@ -14259,6 +15248,7 @@
       <x:c r="J979" s="2"/>
       <x:c r="K979" s="2"/>
       <x:c r="L979" s="2"/>
+      <x:c r="M979"/>
     </x:row>
     <x:row r="980">
       <x:c r="A980" s="36"/>
@@ -14273,6 +15263,7 @@
       <x:c r="J980" s="2"/>
       <x:c r="K980" s="2"/>
       <x:c r="L980" s="2"/>
+      <x:c r="M980"/>
     </x:row>
     <x:row r="981">
       <x:c r="A981" s="36"/>
@@ -14287,6 +15278,7 @@
       <x:c r="J981" s="2"/>
       <x:c r="K981" s="2"/>
       <x:c r="L981" s="2"/>
+      <x:c r="M981"/>
     </x:row>
     <x:row r="982">
       <x:c r="A982" s="36"/>
@@ -14301,6 +15293,7 @@
       <x:c r="J982" s="2"/>
       <x:c r="K982" s="2"/>
       <x:c r="L982" s="2"/>
+      <x:c r="M982"/>
     </x:row>
     <x:row r="983">
       <x:c r="A983" s="36"/>
@@ -14315,6 +15308,7 @@
       <x:c r="J983" s="2"/>
       <x:c r="K983" s="2"/>
       <x:c r="L983" s="2"/>
+      <x:c r="M983"/>
     </x:row>
     <x:row r="984">
       <x:c r="A984" s="36"/>
@@ -14329,6 +15323,7 @@
       <x:c r="J984" s="2"/>
       <x:c r="K984" s="2"/>
       <x:c r="L984" s="2"/>
+      <x:c r="M984"/>
     </x:row>
     <x:row r="985">
       <x:c r="A985" s="36"/>
@@ -14343,6 +15338,7 @@
       <x:c r="J985" s="2"/>
       <x:c r="K985" s="2"/>
       <x:c r="L985" s="2"/>
+      <x:c r="M985"/>
     </x:row>
     <x:row r="986">
       <x:c r="A986" s="36"/>
@@ -14357,6 +15353,7 @@
       <x:c r="J986" s="2"/>
       <x:c r="K986" s="2"/>
       <x:c r="L986" s="2"/>
+      <x:c r="M986"/>
     </x:row>
     <x:row r="987">
       <x:c r="A987" s="36"/>
@@ -14371,6 +15368,7 @@
       <x:c r="J987" s="2"/>
       <x:c r="K987" s="2"/>
       <x:c r="L987" s="2"/>
+      <x:c r="M987"/>
     </x:row>
     <x:row r="988">
       <x:c r="A988" s="36"/>
@@ -14385,6 +15383,7 @@
       <x:c r="J988" s="2"/>
       <x:c r="K988" s="2"/>
       <x:c r="L988" s="2"/>
+      <x:c r="M988"/>
     </x:row>
     <x:row r="989">
       <x:c r="A989" s="36"/>
@@ -14399,6 +15398,7 @@
       <x:c r="J989" s="2"/>
       <x:c r="K989" s="2"/>
       <x:c r="L989" s="2"/>
+      <x:c r="M989"/>
     </x:row>
     <x:row r="990">
       <x:c r="A990" s="36"/>
@@ -14413,6 +15413,7 @@
       <x:c r="J990" s="2"/>
       <x:c r="K990" s="2"/>
       <x:c r="L990" s="2"/>
+      <x:c r="M990"/>
     </x:row>
     <x:row r="991">
       <x:c r="A991" s="36"/>
@@ -14427,6 +15428,7 @@
       <x:c r="J991" s="2"/>
       <x:c r="K991" s="2"/>
       <x:c r="L991" s="2"/>
+      <x:c r="M991"/>
     </x:row>
     <x:row r="992">
       <x:c r="A992" s="36"/>
@@ -14441,6 +15443,7 @@
       <x:c r="J992" s="2"/>
       <x:c r="K992" s="2"/>
       <x:c r="L992" s="2"/>
+      <x:c r="M992"/>
     </x:row>
     <x:row r="993">
       <x:c r="A993" s="36"/>
@@ -14455,6 +15458,7 @@
       <x:c r="J993" s="2"/>
       <x:c r="K993" s="2"/>
       <x:c r="L993" s="2"/>
+      <x:c r="M993"/>
     </x:row>
     <x:row r="994">
       <x:c r="A994" s="36"/>
@@ -14469,6 +15473,7 @@
       <x:c r="J994" s="2"/>
       <x:c r="K994" s="2"/>
       <x:c r="L994" s="2"/>
+      <x:c r="M994"/>
     </x:row>
     <x:row r="995">
       <x:c r="A995" s="36"/>
@@ -14483,6 +15488,7 @@
       <x:c r="J995" s="2"/>
       <x:c r="K995" s="2"/>
       <x:c r="L995" s="2"/>
+      <x:c r="M995"/>
     </x:row>
     <x:row r="996">
       <x:c r="A996" s="36"/>
@@ -14497,6 +15503,7 @@
       <x:c r="J996" s="2"/>
       <x:c r="K996" s="2"/>
       <x:c r="L996" s="2"/>
+      <x:c r="M996"/>
     </x:row>
     <x:row r="997">
       <x:c r="A997" s="36"/>
@@ -14511,6 +15518,7 @@
       <x:c r="J997" s="2"/>
       <x:c r="K997" s="2"/>
       <x:c r="L997" s="2"/>
+      <x:c r="M997"/>
     </x:row>
     <x:row r="998">
       <x:c r="A998" s="36"/>
@@ -14525,6 +15533,7 @@
       <x:c r="J998" s="2"/>
       <x:c r="K998" s="2"/>
       <x:c r="L998" s="2"/>
+      <x:c r="M998"/>
     </x:row>
     <x:row r="999">
       <x:c r="A999" s="36"/>
@@ -14539,6 +15548,7 @@
       <x:c r="J999" s="2"/>
       <x:c r="K999" s="2"/>
       <x:c r="L999" s="2"/>
+      <x:c r="M999"/>
     </x:row>
     <x:row r="1000">
       <x:c r="A1000" s="36"/>
@@ -14553,6 +15563,7 @@
       <x:c r="J1000" s="2"/>
       <x:c r="K1000" s="2"/>
       <x:c r="L1000" s="2"/>
+      <x:c r="M1000"/>
     </x:row>
     <x:row r="1001">
       <x:c r="A1001" s="36"/>
@@ -14567,6 +15578,7 @@
       <x:c r="J1001" s="2"/>
       <x:c r="K1001" s="2"/>
       <x:c r="L1001" s="2"/>
+      <x:c r="M1001"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -14594,6 +15606,7 @@
     <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -14633,6 +15646,9 @@
       <x:c r="L1" s="22" t="str">
         <x:v>IsActive</x:v>
       </x:c>
+      <x:c r="M1" t="str">
+        <x:v>PermitNumber</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
@@ -14671,6 +15687,9 @@
       <x:c r="L2" s="2" t="str">
         <x:v>TRUE</x:v>
       </x:c>
+      <x:c r="M2" t="str">
+        <x:v>325642135</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
@@ -14707,6 +15726,9 @@
       <x:c r="L3" s="2" t="str">
         <x:v>TRUE</x:v>
       </x:c>
+      <x:c r="M3" t="str">
+        <x:v>325642136</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
@@ -14721,6 +15743,7 @@
       <x:c r="J4" s="2"/>
       <x:c r="K4" s="2"/>
       <x:c r="L4" s="2"/>
+      <x:c r="M4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="39" t="str">
@@ -14737,6 +15760,292 @@
       <x:c r="J5" s="39"/>
       <x:c r="K5" s="39"/>
       <x:c r="L5" s="39"/>
+      <x:c r="M5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="M6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="M7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="M8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="M9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="M10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="M11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="M12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="M13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="M14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="M15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="M16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="M17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="M18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="M19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="M20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="M21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="M22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="M23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="M24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="M25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="M26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="M27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="M28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="M29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="M30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="M31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="M32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="M33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="M34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="M35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="M36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="M37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="M38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="M39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="M40"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="M41"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="M42"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="M43"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="M44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="M45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="M46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="M47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="M48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="M49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="M50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="M51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="M52"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="M53"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="M54"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="M55"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="M56"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="M57"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="M58"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="M59"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="M60"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="M61"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="M62"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="M63"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="M64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="M65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="M66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="M67"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="M68"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="M69"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="M70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="M71"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="M72"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="M73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="M74"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="M75"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="M76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="M77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="M78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="M79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="M80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="M81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="M82"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="M83"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="M84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="M85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="M86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="M87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="M88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="M89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="M90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="M91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="M92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="M93"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="M94"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="M95"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="M96"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="M97"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="M98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="M99"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="M100"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/src/HTX586CONTRACT.Web/wwwroot/templates/Template_Import_Vehicle_HTX586.xlsx
+++ b/src/HTX586CONTRACT.Web/wwwroot/templates/Template_Import_Vehicle_HTX586.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="1" r:id="Ra8d864bed6a14110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_VEHICLE" sheetId="2" r:id="Rf6c93ac23b484d17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VI_DU" sheetId="3" r:id="R04e6cf2243e14ece"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="1" r:id="R7aa2d6d1b7044c02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_VEHICLE" sheetId="2" r:id="R3b4e94a9c4834015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VI_DU" sheetId="3" r:id="Rde19266b98074f5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,7 +57,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -89,6 +89,11 @@
         <x:fgColor rgb="FFFEF3C7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -107,7 +112,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -211,6 +216,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -502,12 +519,12 @@
         <x:v>PlateNumber phải duy nhất trong hệ thống. SeatCount là số nguyên từ 1 đến 100.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="34" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B19" t="str">
-        <x:v>PermitNumber (Số phù hiệu) là bắt buộc và được dùng để sinh số hợp đồng chính thức khi hoàn tất.</x:v>
+      <x:c r="B19" s="2" t="str">
+        <x:v>PermitNumber (Số phù hiệu) không bắt buộc khi import Xe. Có thể để trống; tuy nhiên hệ thống sẽ không cho phép tạo Hợp đồng cho xe đó cho đến khi cập nhật Số phù hiệu.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -576,7 +593,7 @@
       <x:c r="L1" s="24" t="str">
         <x:v>IsActive</x:v>
       </x:c>
-      <x:c r="M1" t="str">
+      <x:c r="M1" s="45" t="str">
         <x:v>PermitNumber</x:v>
       </x:c>
     </x:row>
@@ -15726,9 +15743,7 @@
       <x:c r="L3" s="2" t="str">
         <x:v>TRUE</x:v>
       </x:c>
-      <x:c r="M3" t="str">
-        <x:v>325642136</x:v>
-      </x:c>
+      <x:c r="M3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
@@ -15745,9 +15760,9 @@
       <x:c r="L4" s="2"/>
       <x:c r="M4"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="39" t="str">
-        <x:v>Ví dụ dòng 2: có Chủ xe. Dòng 3: tạo xe chưa gán Chủ xe.</x:v>
+        <x:v>Ví dụ dòng 2: có Chủ xe + Số phù hiệu. Dòng 3: chưa gán Chủ xe và để trống PermitNumber; vẫn import được nhưng chưa thể tạo Hợp đồng cho đến khi bổ sung Số phù hiệu.</x:v>
       </x:c>
       <x:c r="B5" s="39"/>
       <x:c r="C5" s="39"/>
@@ -15760,7 +15775,7 @@
       <x:c r="J5" s="39"/>
       <x:c r="K5" s="39"/>
       <x:c r="L5" s="39"/>
-      <x:c r="M5"/>
+      <x:c r="M5" s="2"/>
     </x:row>
     <x:row r="6">
       <x:c r="M6"/>
